--- a/reports/Master_Report.xlsx
+++ b/reports/Master_Report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="608">
   <si>
     <t>Execution Date</t>
   </si>
@@ -47,7 +47,7 @@
     <t>Execution Duration</t>
   </si>
   <si>
-    <t>6/15/2026, 4:53:59 PM</t>
+    <t>6/15/2026, 5:27:13 PM</t>
   </si>
   <si>
     <t>Selenium (Web E2E)</t>
@@ -59,18 +59,21 @@
     <t>N/A</t>
   </si>
   <si>
+    <t>96.97%</t>
+  </si>
+  <si>
+    <t>00:02:15</t>
+  </si>
+  <si>
+    <t>Security (Vulnerabilities)</t>
+  </si>
+  <si>
+    <t>Backend API Scanner</t>
+  </si>
+  <si>
     <t>96.67%</t>
   </si>
   <si>
-    <t>00:02:15</t>
-  </si>
-  <si>
-    <t>Security (Vulnerabilities)</t>
-  </si>
-  <si>
-    <t>Backend API Scanner</t>
-  </si>
-  <si>
     <t>00:00:10</t>
   </si>
   <si>
@@ -92,6 +95,9 @@
     <t>Multi-Platform</t>
   </si>
   <si>
+    <t>96.77%</t>
+  </si>
+  <si>
     <t>00:08:37</t>
   </si>
   <si>
@@ -128,13 +134,13 @@
     <t>TC_SEL_001 - Verify registration page load</t>
   </si>
   <si>
-    <t>4:48:59 PM</t>
-  </si>
-  <si>
-    <t>4:49:03 PM</t>
-  </si>
-  <si>
-    <t>2.36s</t>
+    <t>5:21:43 PM</t>
+  </si>
+  <si>
+    <t>5:21:47 PM</t>
+  </si>
+  <si>
+    <t>1.66s</t>
   </si>
   <si>
     <t>TC_SEL_002</t>
@@ -143,721 +149,757 @@
     <t>TC_SEL_002 - Verify successful user registration</t>
   </si>
   <si>
-    <t>4:49:09 PM</t>
-  </si>
-  <si>
-    <t>4:49:13 PM</t>
+    <t>5:21:53 PM</t>
+  </si>
+  <si>
+    <t>5:21:57 PM</t>
+  </si>
+  <si>
+    <t>1.90s</t>
+  </si>
+  <si>
+    <t>TC_SEL_003</t>
+  </si>
+  <si>
+    <t>TC_SEL_003 - Verify registration validation with existing email</t>
+  </si>
+  <si>
+    <t>5:22:03 PM</t>
+  </si>
+  <si>
+    <t>5:22:07 PM</t>
+  </si>
+  <si>
+    <t>2.53s</t>
+  </si>
+  <si>
+    <t>TC_SEL_004</t>
+  </si>
+  <si>
+    <t>TC_SEL_004 - Verify registration invalid password constraints</t>
+  </si>
+  <si>
+    <t>5:22:13 PM</t>
+  </si>
+  <si>
+    <t>5:22:17 PM</t>
+  </si>
+  <si>
+    <t>2.39s</t>
+  </si>
+  <si>
+    <t>TC_SEL_005</t>
+  </si>
+  <si>
+    <t>TC_SEL_005 - Verify login page load</t>
+  </si>
+  <si>
+    <t>5:22:23 PM</t>
+  </si>
+  <si>
+    <t>5:22:27 PM</t>
+  </si>
+  <si>
+    <t>1.86s</t>
+  </si>
+  <si>
+    <t>TC_SEL_006</t>
+  </si>
+  <si>
+    <t>TC_SEL_006 - Verify successful login with valid credentials</t>
+  </si>
+  <si>
+    <t>5:22:33 PM</t>
+  </si>
+  <si>
+    <t>5:22:37 PM</t>
+  </si>
+  <si>
+    <t>2.76s</t>
+  </si>
+  <si>
+    <t>TC_SEL_007</t>
+  </si>
+  <si>
+    <t>TC_SEL_007 - Verify login error warning with invalid credentials</t>
+  </si>
+  <si>
+    <t>5:22:43 PM</t>
+  </si>
+  <si>
+    <t>5:22:47 PM</t>
+  </si>
+  <si>
+    <t>1.61s</t>
+  </si>
+  <si>
+    <t>TC_SEL_008</t>
+  </si>
+  <si>
+    <t>TC_SEL_008 - Verify forgot password page load</t>
+  </si>
+  <si>
+    <t>5:22:53 PM</t>
+  </si>
+  <si>
+    <t>5:22:57 PM</t>
+  </si>
+  <si>
+    <t>2.96s</t>
+  </si>
+  <si>
+    <t>TC_SEL_009</t>
+  </si>
+  <si>
+    <t>TC_SEL_009 - Verify forgot password email submission</t>
+  </si>
+  <si>
+    <t>5:23:03 PM</t>
+  </si>
+  <si>
+    <t>5:23:07 PM</t>
+  </si>
+  <si>
+    <t>2.33s</t>
+  </si>
+  <si>
+    <t>TC_SEL_010</t>
+  </si>
+  <si>
+    <t>Transactions</t>
+  </si>
+  <si>
+    <t>TC_SEL_010 - Verify dashboard load and initial welcome metrics</t>
+  </si>
+  <si>
+    <t>5:23:13 PM</t>
+  </si>
+  <si>
+    <t>5:23:17 PM</t>
+  </si>
+  <si>
+    <t>2.63s</t>
+  </si>
+  <si>
+    <t>TC_SEL_011</t>
+  </si>
+  <si>
+    <t>TC_SEL_011 - Verify add income transaction</t>
+  </si>
+  <si>
+    <t>5:23:23 PM</t>
+  </si>
+  <si>
+    <t>5:23:27 PM</t>
+  </si>
+  <si>
+    <t>2.10s</t>
+  </si>
+  <si>
+    <t>TC_SEL_012</t>
+  </si>
+  <si>
+    <t>TC_SEL_012 - Verify add expense transaction</t>
+  </si>
+  <si>
+    <t>5:23:33 PM</t>
+  </si>
+  <si>
+    <t>5:23:37 PM</t>
+  </si>
+  <si>
+    <t>2.80s</t>
+  </si>
+  <si>
+    <t>TC_SEL_013</t>
+  </si>
+  <si>
+    <t>TC_SEL_013 - Verify transaction field input sanitization</t>
+  </si>
+  <si>
+    <t>5:23:43 PM</t>
+  </si>
+  <si>
+    <t>5:23:47 PM</t>
+  </si>
+  <si>
+    <t>1.37s</t>
+  </si>
+  <si>
+    <t>TC_SEL_014</t>
+  </si>
+  <si>
+    <t>TC_SEL_014 - Verify edit transaction title</t>
+  </si>
+  <si>
+    <t>5:23:53 PM</t>
+  </si>
+  <si>
+    <t>5:23:57 PM</t>
+  </si>
+  <si>
+    <t>TC_SEL_015</t>
+  </si>
+  <si>
+    <t>TC_SEL_015 - Verify edit transaction amount and category updates</t>
+  </si>
+  <si>
+    <t>5:24:03 PM</t>
+  </si>
+  <si>
+    <t>5:24:07 PM</t>
+  </si>
+  <si>
+    <t>2.67s</t>
+  </si>
+  <si>
+    <t>TC_SEL_016</t>
+  </si>
+  <si>
+    <t>TC_SEL_016 - Verify transaction deletion and balance recalculation</t>
+  </si>
+  <si>
+    <t>5:24:13 PM</t>
+  </si>
+  <si>
+    <t>5:24:17 PM</t>
+  </si>
+  <si>
+    <t>2.13s</t>
+  </si>
+  <si>
+    <t>TC_SEL_017</t>
+  </si>
+  <si>
+    <t>TC_SEL_017 - Verify search transaction by keyword</t>
+  </si>
+  <si>
+    <t>5:24:23 PM</t>
+  </si>
+  <si>
+    <t>5:24:27 PM</t>
+  </si>
+  <si>
+    <t>2.24s</t>
+  </si>
+  <si>
+    <t>TC_SEL_018</t>
+  </si>
+  <si>
+    <t>TC_SEL_018 - Verify filter transactions by category</t>
+  </si>
+  <si>
+    <t>5:24:33 PM</t>
+  </si>
+  <si>
+    <t>5:24:37 PM</t>
+  </si>
+  <si>
+    <t>1.34s</t>
+  </si>
+  <si>
+    <t>TC_SEL_019</t>
+  </si>
+  <si>
+    <t>TC_SEL_019 - Verify filter transactions by date ranges</t>
+  </si>
+  <si>
+    <t>5:24:43 PM</t>
+  </si>
+  <si>
+    <t>5:24:47 PM</t>
+  </si>
+  <si>
+    <t>1.79s</t>
+  </si>
+  <si>
+    <t>TC_SEL_020</t>
+  </si>
+  <si>
+    <t>TC_SEL_020 - Verify sort transactions by date ascending/descending</t>
+  </si>
+  <si>
+    <t>5:24:53 PM</t>
+  </si>
+  <si>
+    <t>5:24:57 PM</t>
+  </si>
+  <si>
+    <t>1.03s</t>
+  </si>
+  <si>
+    <t>TC_SEL_021</t>
+  </si>
+  <si>
+    <t>TC_SEL_021 - Verify sort transactions by amount ascending/descending</t>
+  </si>
+  <si>
+    <t>5:25:03 PM</t>
+  </si>
+  <si>
+    <t>5:25:07 PM</t>
+  </si>
+  <si>
+    <t>1.94s</t>
+  </si>
+  <si>
+    <t>TC_SEL_022</t>
+  </si>
+  <si>
+    <t>Budget</t>
+  </si>
+  <si>
+    <t>TC_SEL_022 - Verify monthly budget creation and save button</t>
+  </si>
+  <si>
+    <t>5:25:13 PM</t>
+  </si>
+  <si>
+    <t>5:25:17 PM</t>
+  </si>
+  <si>
+    <t>TC_SEL_023</t>
+  </si>
+  <si>
+    <t>TC_SEL_023 - Verify budget progress bar updates on transactions</t>
+  </si>
+  <si>
+    <t>5:25:23 PM</t>
+  </si>
+  <si>
+    <t>5:25:27 PM</t>
+  </si>
+  <si>
+    <t>2.79s</t>
+  </si>
+  <si>
+    <t>TC_SEL_024</t>
+  </si>
+  <si>
+    <t>Reports</t>
+  </si>
+  <si>
+    <t>TC_SEL_024 - Verify monthly PDF report generation</t>
+  </si>
+  <si>
+    <t>5:25:33 PM</t>
+  </si>
+  <si>
+    <t>5:25:37 PM</t>
+  </si>
+  <si>
+    <t>1.58s</t>
+  </si>
+  <si>
+    <t>TC_SEL_025</t>
+  </si>
+  <si>
+    <t>TC_SEL_025 - Verify charts render correctly in reports view</t>
+  </si>
+  <si>
+    <t>5:25:43 PM</t>
+  </si>
+  <si>
+    <t>5:25:47 PM</t>
+  </si>
+  <si>
+    <t>2.48s</t>
+  </si>
+  <si>
+    <t>TC_SEL_026</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>TC_SEL_026 - Verify profile details update</t>
+  </si>
+  <si>
+    <t>5:25:53 PM</t>
+  </si>
+  <si>
+    <t>5:25:57 PM</t>
+  </si>
+  <si>
+    <t>TC_SEL_027</t>
+  </si>
+  <si>
+    <t>TC_SEL_027 - Verify password update functionality</t>
+  </si>
+  <si>
+    <t>5:26:03 PM</t>
+  </si>
+  <si>
+    <t>5:26:07 PM</t>
+  </si>
+  <si>
+    <t>1.88s</t>
+  </si>
+  <si>
+    <t>TC_SEL_028</t>
+  </si>
+  <si>
+    <t>TC_SEL_028 - Verify currency settings updates</t>
+  </si>
+  <si>
+    <t>5:26:13 PM</t>
+  </si>
+  <si>
+    <t>5:26:17 PM</t>
+  </si>
+  <si>
+    <t>2.85s</t>
+  </si>
+  <si>
+    <t>TC_SEL_029</t>
+  </si>
+  <si>
+    <t>TC_SEL_029 - Verify session persistence on page refresh</t>
+  </si>
+  <si>
+    <t>5:26:23 PM</t>
+  </si>
+  <si>
+    <t>5:26:27 PM</t>
+  </si>
+  <si>
+    <t>TC_SEL_030</t>
+  </si>
+  <si>
+    <t>TC_SEL_030 - Verify successful user logout and redirection</t>
+  </si>
+  <si>
+    <t>5:26:33 PM</t>
+  </si>
+  <si>
+    <t>5:26:37 PM</t>
+  </si>
+  <si>
+    <t>2.92s</t>
+  </si>
+  <si>
+    <t>TC_SEL_031</t>
+  </si>
+  <si>
+    <t>TC_SEL_031 - Verify currency settings updates in layout</t>
+  </si>
+  <si>
+    <t>5:26:43 PM</t>
+  </si>
+  <si>
+    <t>5:26:47 PM</t>
+  </si>
+  <si>
+    <t>2.38s</t>
+  </si>
+  <si>
+    <t>TC_SEL_032</t>
+  </si>
+  <si>
+    <t>TC_SEL_032 - Verify monthly budget limit notifications triggers</t>
+  </si>
+  <si>
+    <t>5:26:53 PM</t>
+  </si>
+  <si>
+    <t>5:26:57 PM</t>
   </si>
   <si>
     <t>2.78s</t>
   </si>
   <si>
-    <t>TC_SEL_003</t>
-  </si>
-  <si>
-    <t>TC_SEL_003 - Verify registration validation with existing email</t>
-  </si>
-  <si>
-    <t>4:49:19 PM</t>
-  </si>
-  <si>
-    <t>4:49:23 PM</t>
-  </si>
-  <si>
-    <t>1.30s</t>
-  </si>
-  <si>
-    <t>TC_SEL_004</t>
-  </si>
-  <si>
-    <t>TC_SEL_004 - Verify registration invalid password constraints</t>
-  </si>
-  <si>
-    <t>4:49:29 PM</t>
-  </si>
-  <si>
-    <t>4:49:33 PM</t>
-  </si>
-  <si>
-    <t>1.82s</t>
-  </si>
-  <si>
-    <t>TC_SEL_005</t>
-  </si>
-  <si>
-    <t>TC_SEL_005 - Verify login page load</t>
-  </si>
-  <si>
-    <t>4:49:39 PM</t>
-  </si>
-  <si>
-    <t>4:49:43 PM</t>
+    <t>TC_SEL_033</t>
+  </si>
+  <si>
+    <t>TC_SEL_033 - Verify monthly PDF report download functionality</t>
+  </si>
+  <si>
+    <t>5:27:03 PM</t>
+  </si>
+  <si>
+    <t>5:27:07 PM</t>
+  </si>
+  <si>
+    <t>5.12s</t>
+  </si>
+  <si>
+    <t>TC_SEC_001</t>
+  </si>
+  <si>
+    <t>Auth Injection</t>
+  </si>
+  <si>
+    <t>TC_SEC_001 - Verify SQL injection prevention in Login email field</t>
+  </si>
+  <si>
+    <t>5:23:16 PM</t>
+  </si>
+  <si>
+    <t>0.84s</t>
+  </si>
+  <si>
+    <t>TC_SEC_002</t>
+  </si>
+  <si>
+    <t>TC_SEC_002 - Verify SQL injection prevention in Login password field</t>
+  </si>
+  <si>
+    <t>5:23:21 PM</t>
+  </si>
+  <si>
+    <t>5:23:24 PM</t>
+  </si>
+  <si>
+    <t>0.61s</t>
+  </si>
+  <si>
+    <t>TC_SEC_003</t>
+  </si>
+  <si>
+    <t>TC_SEC_003 - Verify SQL injection prevention in register input fields</t>
+  </si>
+  <si>
+    <t>5:23:29 PM</t>
+  </si>
+  <si>
+    <t>5:23:32 PM</t>
+  </si>
+  <si>
+    <t>1.50s</t>
+  </si>
+  <si>
+    <t>TC_SEC_004</t>
+  </si>
+  <si>
+    <t>CSRF Prevention</t>
+  </si>
+  <si>
+    <t>TC_SEC_004 - Verify HTML / Script tag sanitization in transaction title input</t>
+  </si>
+  <si>
+    <t>5:23:40 PM</t>
+  </si>
+  <si>
+    <t>1.60s</t>
+  </si>
+  <si>
+    <t>TC_SEC_005</t>
+  </si>
+  <si>
+    <t>TC_SEC_005 - Verify sanitization of script tags in transaction category input</t>
+  </si>
+  <si>
+    <t>5:23:45 PM</t>
+  </si>
+  <si>
+    <t>5:23:48 PM</t>
+  </si>
+  <si>
+    <t>1.93s</t>
+  </si>
+  <si>
+    <t>TC_SEC_006</t>
+  </si>
+  <si>
+    <t>TC_SEC_006 - Verify anti-CSRF token verification on POST transactions endpoint</t>
+  </si>
+  <si>
+    <t>5:23:56 PM</t>
+  </si>
+  <si>
+    <t>1.97s</t>
+  </si>
+  <si>
+    <t>TC_SEC_007</t>
+  </si>
+  <si>
+    <t>TC_SEC_007 - Verify anti-CSRF token verification on DELETE budget endpoint</t>
+  </si>
+  <si>
+    <t>5:24:01 PM</t>
+  </si>
+  <si>
+    <t>5:24:04 PM</t>
+  </si>
+  <si>
+    <t>TC_SEC_008</t>
+  </si>
+  <si>
+    <t>JWT Validation</t>
+  </si>
+  <si>
+    <t>TC_SEC_008 - Verify JWT token validation with incorrect signatures</t>
+  </si>
+  <si>
+    <t>5:24:09 PM</t>
+  </si>
+  <si>
+    <t>5:24:12 PM</t>
+  </si>
+  <si>
+    <t>1.63s</t>
+  </si>
+  <si>
+    <t>TC_SEC_009</t>
+  </si>
+  <si>
+    <t>TC_SEC_009 - Verify JWT token expiration enforcement</t>
+  </si>
+  <si>
+    <t>5:24:20 PM</t>
+  </si>
+  <si>
+    <t>TC_SEC_010</t>
+  </si>
+  <si>
+    <t>TC_SEC_010 - Verify session timeout redirection after inactivity</t>
+  </si>
+  <si>
+    <t>5:24:25 PM</t>
+  </si>
+  <si>
+    <t>5:24:28 PM</t>
   </si>
   <si>
     <t>1.26s</t>
   </si>
   <si>
-    <t>TC_SEL_006</t>
-  </si>
-  <si>
-    <t>TC_SEL_006 - Verify successful login with valid credentials</t>
-  </si>
-  <si>
-    <t>4:49:49 PM</t>
-  </si>
-  <si>
-    <t>4:49:53 PM</t>
-  </si>
-  <si>
-    <t>1.59s</t>
-  </si>
-  <si>
-    <t>TC_SEL_007</t>
-  </si>
-  <si>
-    <t>TC_SEL_007 - Verify login error warning with invalid credentials</t>
-  </si>
-  <si>
-    <t>4:49:59 PM</t>
-  </si>
-  <si>
-    <t>4:50:03 PM</t>
-  </si>
-  <si>
-    <t>2.15s</t>
-  </si>
-  <si>
-    <t>TC_SEL_008</t>
-  </si>
-  <si>
-    <t>TC_SEL_008 - Verify forgot password page load</t>
-  </si>
-  <si>
-    <t>4:50:09 PM</t>
-  </si>
-  <si>
-    <t>4:50:13 PM</t>
-  </si>
-  <si>
-    <t>2.69s</t>
-  </si>
-  <si>
-    <t>TC_SEL_009</t>
-  </si>
-  <si>
-    <t>TC_SEL_009 - Verify forgot password email submission</t>
-  </si>
-  <si>
-    <t>4:50:19 PM</t>
-  </si>
-  <si>
-    <t>4:50:23 PM</t>
-  </si>
-  <si>
-    <t>2.32s</t>
-  </si>
-  <si>
-    <t>TC_SEL_010</t>
-  </si>
-  <si>
-    <t>Transactions</t>
-  </si>
-  <si>
-    <t>TC_SEL_010 - Verify dashboard load and initial welcome metrics</t>
-  </si>
-  <si>
-    <t>4:50:29 PM</t>
-  </si>
-  <si>
-    <t>4:50:33 PM</t>
-  </si>
-  <si>
-    <t>1.19s</t>
-  </si>
-  <si>
-    <t>TC_SEL_011</t>
-  </si>
-  <si>
-    <t>TC_SEL_011 - Verify add income transaction</t>
-  </si>
-  <si>
-    <t>4:50:39 PM</t>
-  </si>
-  <si>
-    <t>4:50:43 PM</t>
-  </si>
-  <si>
-    <t>1.85s</t>
-  </si>
-  <si>
-    <t>TC_SEL_012</t>
-  </si>
-  <si>
-    <t>TC_SEL_012 - Verify add expense transaction</t>
-  </si>
-  <si>
-    <t>4:50:49 PM</t>
-  </si>
-  <si>
-    <t>4:50:53 PM</t>
-  </si>
-  <si>
-    <t>TC_SEL_013</t>
-  </si>
-  <si>
-    <t>TC_SEL_013 - Verify transaction field input sanitization</t>
-  </si>
-  <si>
-    <t>4:50:59 PM</t>
-  </si>
-  <si>
-    <t>4:51:03 PM</t>
-  </si>
-  <si>
-    <t>2.42s</t>
-  </si>
-  <si>
-    <t>TC_SEL_014</t>
-  </si>
-  <si>
-    <t>TC_SEL_014 - Verify edit transaction title</t>
-  </si>
-  <si>
-    <t>4:51:09 PM</t>
-  </si>
-  <si>
-    <t>4:51:13 PM</t>
-  </si>
-  <si>
-    <t>1.81s</t>
-  </si>
-  <si>
-    <t>TC_SEL_015</t>
-  </si>
-  <si>
-    <t>TC_SEL_015 - Verify edit transaction amount and category updates</t>
-  </si>
-  <si>
-    <t>4:51:19 PM</t>
-  </si>
-  <si>
-    <t>4:51:23 PM</t>
-  </si>
-  <si>
-    <t>TC_SEL_016</t>
-  </si>
-  <si>
-    <t>TC_SEL_016 - Verify transaction deletion and balance recalculation</t>
-  </si>
-  <si>
-    <t>4:51:29 PM</t>
-  </si>
-  <si>
-    <t>4:51:33 PM</t>
-  </si>
-  <si>
-    <t>2.82s</t>
-  </si>
-  <si>
-    <t>TC_SEL_017</t>
-  </si>
-  <si>
-    <t>TC_SEL_017 - Verify search transaction by keyword</t>
-  </si>
-  <si>
-    <t>4:51:39 PM</t>
-  </si>
-  <si>
-    <t>4:51:43 PM</t>
-  </si>
-  <si>
-    <t>2.18s</t>
-  </si>
-  <si>
-    <t>TC_SEL_018</t>
-  </si>
-  <si>
-    <t>TC_SEL_018 - Verify filter transactions by category</t>
-  </si>
-  <si>
-    <t>4:51:49 PM</t>
-  </si>
-  <si>
-    <t>4:51:53 PM</t>
+    <t>TC_SEC_011</t>
+  </si>
+  <si>
+    <t>Access Control</t>
+  </si>
+  <si>
+    <t>TC_SEC_011 - Verify input length validations on transaction title</t>
+  </si>
+  <si>
+    <t>5:24:36 PM</t>
+  </si>
+  <si>
+    <t>TC_SEC_012</t>
+  </si>
+  <si>
+    <t>TC_SEC_012 - Verify negative amount validation on transaction entries</t>
+  </si>
+  <si>
+    <t>5:24:41 PM</t>
+  </si>
+  <si>
+    <t>5:24:44 PM</t>
   </si>
   <si>
     <t>1.41s</t>
   </si>
   <si>
-    <t>TC_SEL_019</t>
-  </si>
-  <si>
-    <t>TC_SEL_019 - Verify filter transactions by date ranges</t>
-  </si>
-  <si>
-    <t>4:51:59 PM</t>
-  </si>
-  <si>
-    <t>4:52:03 PM</t>
-  </si>
-  <si>
-    <t>2.83s</t>
-  </si>
-  <si>
-    <t>TC_SEL_020</t>
-  </si>
-  <si>
-    <t>TC_SEL_020 - Verify sort transactions by date ascending/descending</t>
-  </si>
-  <si>
-    <t>4:52:09 PM</t>
-  </si>
-  <si>
-    <t>4:52:13 PM</t>
-  </si>
-  <si>
-    <t>1.33s</t>
-  </si>
-  <si>
-    <t>TC_SEL_021</t>
-  </si>
-  <si>
-    <t>TC_SEL_021 - Verify sort transactions by amount ascending/descending</t>
-  </si>
-  <si>
-    <t>4:52:19 PM</t>
-  </si>
-  <si>
-    <t>4:52:23 PM</t>
-  </si>
-  <si>
-    <t>2.62s</t>
-  </si>
-  <si>
-    <t>TC_SEL_022</t>
-  </si>
-  <si>
-    <t>Budget</t>
-  </si>
-  <si>
-    <t>TC_SEL_022 - Verify monthly budget creation and save button</t>
-  </si>
-  <si>
-    <t>4:52:29 PM</t>
-  </si>
-  <si>
-    <t>4:52:33 PM</t>
-  </si>
-  <si>
-    <t>2.06s</t>
-  </si>
-  <si>
-    <t>TC_SEL_023</t>
-  </si>
-  <si>
-    <t>TC_SEL_023 - Verify budget progress bar updates on transactions</t>
-  </si>
-  <si>
-    <t>4:52:39 PM</t>
-  </si>
-  <si>
-    <t>4:52:43 PM</t>
-  </si>
-  <si>
-    <t>2.88s</t>
-  </si>
-  <si>
-    <t>TC_SEL_024</t>
-  </si>
-  <si>
-    <t>Reports</t>
-  </si>
-  <si>
-    <t>TC_SEL_024 - Verify monthly PDF report generation</t>
-  </si>
-  <si>
-    <t>4:52:49 PM</t>
-  </si>
-  <si>
-    <t>4:52:53 PM</t>
-  </si>
-  <si>
-    <t>1.16s</t>
-  </si>
-  <si>
-    <t>TC_SEL_025</t>
-  </si>
-  <si>
-    <t>TC_SEL_025 - Verify charts render correctly in reports view</t>
-  </si>
-  <si>
-    <t>4:52:59 PM</t>
-  </si>
-  <si>
-    <t>4:53:03 PM</t>
-  </si>
-  <si>
-    <t>2.72s</t>
-  </si>
-  <si>
-    <t>TC_SEL_026</t>
-  </si>
-  <si>
-    <t>Profile</t>
-  </si>
-  <si>
-    <t>TC_SEL_026 - Verify profile details update</t>
-  </si>
-  <si>
-    <t>4:53:09 PM</t>
-  </si>
-  <si>
-    <t>4:53:13 PM</t>
-  </si>
-  <si>
-    <t>TC_SEL_027</t>
-  </si>
-  <si>
-    <t>TC_SEL_027 - Verify password update functionality</t>
-  </si>
-  <si>
-    <t>4:53:19 PM</t>
-  </si>
-  <si>
-    <t>4:53:23 PM</t>
-  </si>
-  <si>
-    <t>2.71s</t>
-  </si>
-  <si>
-    <t>TC_SEL_028</t>
-  </si>
-  <si>
-    <t>TC_SEL_028 - Verify currency settings updates</t>
-  </si>
-  <si>
-    <t>4:53:29 PM</t>
-  </si>
-  <si>
-    <t>4:53:33 PM</t>
-  </si>
-  <si>
-    <t>2.37s</t>
-  </si>
-  <si>
-    <t>TC_SEL_029</t>
-  </si>
-  <si>
-    <t>TC_SEL_029 - Verify session persistence on page refresh</t>
-  </si>
-  <si>
-    <t>4:53:39 PM</t>
-  </si>
-  <si>
-    <t>4:53:43 PM</t>
-  </si>
-  <si>
-    <t>2.02s</t>
-  </si>
-  <si>
-    <t>TC_SEL_030</t>
-  </si>
-  <si>
-    <t>TC_SEL_030 - Verify successful user logout and redirection</t>
-  </si>
-  <si>
-    <t>4:53:49 PM</t>
-  </si>
-  <si>
-    <t>4:53:53 PM</t>
-  </si>
-  <si>
-    <t>5.12s</t>
-  </si>
-  <si>
-    <t>TC_SEC_001</t>
-  </si>
-  <si>
-    <t>Auth Injection</t>
-  </si>
-  <si>
-    <t>TC_SEC_001 - Verify SQL injection prevention in Login email field</t>
-  </si>
-  <si>
-    <t>4:50:02 PM</t>
-  </si>
-  <si>
-    <t>0.55s</t>
-  </si>
-  <si>
-    <t>TC_SEC_002</t>
-  </si>
-  <si>
-    <t>TC_SEC_002 - Verify SQL injection prevention in Login password field</t>
-  </si>
-  <si>
-    <t>4:50:07 PM</t>
-  </si>
-  <si>
-    <t>4:50:10 PM</t>
-  </si>
-  <si>
-    <t>1.43s</t>
-  </si>
-  <si>
-    <t>TC_SEC_003</t>
-  </si>
-  <si>
-    <t>TC_SEC_003 - Verify SQL injection prevention in register input fields</t>
-  </si>
-  <si>
-    <t>4:50:15 PM</t>
-  </si>
-  <si>
-    <t>4:50:18 PM</t>
-  </si>
-  <si>
-    <t>1.21s</t>
-  </si>
-  <si>
-    <t>TC_SEC_004</t>
-  </si>
-  <si>
-    <t>CSRF Prevention</t>
-  </si>
-  <si>
-    <t>TC_SEC_004 - Verify HTML / Script tag sanitization in transaction title input</t>
-  </si>
-  <si>
-    <t>4:50:26 PM</t>
-  </si>
-  <si>
-    <t>0.76s</t>
-  </si>
-  <si>
-    <t>TC_SEC_005</t>
-  </si>
-  <si>
-    <t>TC_SEC_005 - Verify sanitization of script tags in transaction category input</t>
-  </si>
-  <si>
-    <t>4:50:31 PM</t>
-  </si>
-  <si>
-    <t>4:50:34 PM</t>
-  </si>
-  <si>
-    <t>1.08s</t>
-  </si>
-  <si>
-    <t>TC_SEC_006</t>
-  </si>
-  <si>
-    <t>TC_SEC_006 - Verify anti-CSRF token verification on POST transactions endpoint</t>
-  </si>
-  <si>
-    <t>4:50:42 PM</t>
-  </si>
-  <si>
-    <t>0.80s</t>
-  </si>
-  <si>
-    <t>TC_SEC_007</t>
-  </si>
-  <si>
-    <t>TC_SEC_007 - Verify anti-CSRF token verification on DELETE budget endpoint</t>
-  </si>
-  <si>
-    <t>4:50:47 PM</t>
-  </si>
-  <si>
-    <t>4:50:50 PM</t>
-  </si>
-  <si>
-    <t>1.23s</t>
-  </si>
-  <si>
-    <t>TC_SEC_008</t>
-  </si>
-  <si>
-    <t>JWT Validation</t>
-  </si>
-  <si>
-    <t>TC_SEC_008 - Verify JWT token validation with incorrect signatures</t>
-  </si>
-  <si>
-    <t>4:50:55 PM</t>
-  </si>
-  <si>
-    <t>4:50:58 PM</t>
-  </si>
-  <si>
-    <t>1.53s</t>
-  </si>
-  <si>
-    <t>TC_SEC_009</t>
-  </si>
-  <si>
-    <t>TC_SEC_009 - Verify JWT token expiration enforcement</t>
-  </si>
-  <si>
-    <t>4:51:06 PM</t>
-  </si>
-  <si>
-    <t>1.28s</t>
-  </si>
-  <si>
-    <t>TC_SEC_010</t>
-  </si>
-  <si>
-    <t>TC_SEC_010 - Verify session timeout redirection after inactivity</t>
-  </si>
-  <si>
-    <t>4:51:11 PM</t>
-  </si>
-  <si>
-    <t>4:51:14 PM</t>
+    <t>TC_SEC_013</t>
+  </si>
+  <si>
+    <t>TC_SEC_013 - Verify non-numeric input rejection on budget amounts</t>
+  </si>
+  <si>
+    <t>5:24:49 PM</t>
+  </si>
+  <si>
+    <t>5:24:52 PM</t>
+  </si>
+  <si>
+    <t>0.91s</t>
+  </si>
+  <si>
+    <t>TC_SEC_014</t>
+  </si>
+  <si>
+    <t>TC_SEC_014 - Verify authorization checks for transaction deletion</t>
+  </si>
+  <si>
+    <t>5:25:00 PM</t>
+  </si>
+  <si>
+    <t>1.22s</t>
+  </si>
+  <si>
+    <t>TC_SEC_015</t>
+  </si>
+  <si>
+    <t>TC_SEC_015 - Verify access control: guest user cannot access dashboard API</t>
+  </si>
+  <si>
+    <t>5:25:05 PM</t>
+  </si>
+  <si>
+    <t>5:25:08 PM</t>
+  </si>
+  <si>
+    <t>0.57s</t>
+  </si>
+  <si>
+    <t>TC_SEC_016</t>
+  </si>
+  <si>
+    <t>TC_SEC_016 - Verify access control: user cannot view other users transactions</t>
+  </si>
+  <si>
+    <t>5:25:16 PM</t>
+  </si>
+  <si>
+    <t>1.15s</t>
+  </si>
+  <si>
+    <t>TC_SEC_017</t>
+  </si>
+  <si>
+    <t>TC_SEC_017 - Verify password hash complexity strength check</t>
+  </si>
+  <si>
+    <t>5:25:21 PM</t>
+  </si>
+  <si>
+    <t>5:25:24 PM</t>
+  </si>
+  <si>
+    <t>0.58s</t>
+  </si>
+  <si>
+    <t>TC_SEC_018</t>
+  </si>
+  <si>
+    <t>TC_SEC_018 - Verify file upload size validations</t>
+  </si>
+  <si>
+    <t>5:25:29 PM</t>
+  </si>
+  <si>
+    <t>5:25:32 PM</t>
+  </si>
+  <si>
+    <t>0.86s</t>
+  </si>
+  <si>
+    <t>TC_SEC_019</t>
+  </si>
+  <si>
+    <t>TC_SEC_019 - Verify file upload extension whitelist block (.sh, .exe, .js)</t>
+  </si>
+  <si>
+    <t>5:25:40 PM</t>
   </si>
   <si>
     <t>1.95s</t>
   </si>
   <si>
-    <t>TC_SEC_011</t>
-  </si>
-  <si>
-    <t>Access Control</t>
-  </si>
-  <si>
-    <t>TC_SEC_011 - Verify input length validations on transaction title</t>
-  </si>
-  <si>
-    <t>4:51:22 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_012</t>
-  </si>
-  <si>
-    <t>TC_SEC_012 - Verify negative amount validation on transaction entries</t>
-  </si>
-  <si>
-    <t>4:51:27 PM</t>
-  </si>
-  <si>
-    <t>4:51:30 PM</t>
-  </si>
-  <si>
-    <t>0.81s</t>
-  </si>
-  <si>
-    <t>TC_SEC_013</t>
-  </si>
-  <si>
-    <t>TC_SEC_013 - Verify non-numeric input rejection on budget amounts</t>
-  </si>
-  <si>
-    <t>4:51:35 PM</t>
-  </si>
-  <si>
-    <t>4:51:38 PM</t>
-  </si>
-  <si>
-    <t>1.06s</t>
-  </si>
-  <si>
-    <t>TC_SEC_014</t>
-  </si>
-  <si>
-    <t>TC_SEC_014 - Verify authorization checks for transaction deletion</t>
-  </si>
-  <si>
-    <t>4:51:46 PM</t>
-  </si>
-  <si>
-    <t>1.14s</t>
-  </si>
-  <si>
-    <t>TC_SEC_015</t>
-  </si>
-  <si>
-    <t>TC_SEC_015 - Verify access control: guest user cannot access dashboard API</t>
-  </si>
-  <si>
-    <t>4:51:51 PM</t>
-  </si>
-  <si>
-    <t>4:51:54 PM</t>
-  </si>
-  <si>
-    <t>1.50s</t>
-  </si>
-  <si>
-    <t>TC_SEC_016</t>
-  </si>
-  <si>
-    <t>TC_SEC_016 - Verify access control: user cannot view other users transactions</t>
-  </si>
-  <si>
-    <t>4:52:02 PM</t>
-  </si>
-  <si>
-    <t>1.92s</t>
-  </si>
-  <si>
-    <t>TC_SEC_017</t>
-  </si>
-  <si>
-    <t>TC_SEC_017 - Verify password hash complexity strength check</t>
-  </si>
-  <si>
-    <t>4:52:07 PM</t>
-  </si>
-  <si>
-    <t>4:52:10 PM</t>
-  </si>
-  <si>
-    <t>1.67s</t>
-  </si>
-  <si>
-    <t>TC_SEC_018</t>
-  </si>
-  <si>
-    <t>TC_SEC_018 - Verify file upload size validations</t>
-  </si>
-  <si>
-    <t>4:52:15 PM</t>
-  </si>
-  <si>
-    <t>4:52:18 PM</t>
-  </si>
-  <si>
-    <t>0.87s</t>
-  </si>
-  <si>
-    <t>TC_SEC_019</t>
-  </si>
-  <si>
-    <t>TC_SEC_019 - Verify file upload extension whitelist block (.sh, .exe, .js)</t>
-  </si>
-  <si>
-    <t>4:52:26 PM</t>
-  </si>
-  <si>
-    <t>1.05s</t>
-  </si>
-  <si>
     <t>TC_SEC_020</t>
   </si>
   <si>
     <t>TC_SEC_020 - Verify API authorization on budgets edit endpoint</t>
   </si>
   <si>
-    <t>4:52:31 PM</t>
-  </si>
-  <si>
-    <t>4:52:34 PM</t>
-  </si>
-  <si>
-    <t>1.12s</t>
+    <t>5:25:45 PM</t>
+  </si>
+  <si>
+    <t>5:25:48 PM</t>
+  </si>
+  <si>
+    <t>1.36s</t>
   </si>
   <si>
     <t>TC_SEC_021</t>
@@ -869,7 +911,7 @@
     <t>TC_SEC_021 - Verify CORS policy matches trusted domains only</t>
   </si>
   <si>
-    <t>4:52:42 PM</t>
+    <t>5:25:56 PM</t>
   </si>
   <si>
     <t>TC_SEC_022</t>
@@ -878,13 +920,10 @@
     <t>TC_SEC_022 - Verify X-Frame-Options: SAMEORIGIN header presence</t>
   </si>
   <si>
-    <t>4:52:47 PM</t>
-  </si>
-  <si>
-    <t>4:52:50 PM</t>
-  </si>
-  <si>
-    <t>1.20s</t>
+    <t>5:26:01 PM</t>
+  </si>
+  <si>
+    <t>5:26:04 PM</t>
   </si>
   <si>
     <t>TC_SEC_023</t>
@@ -893,13 +932,10 @@
     <t>TC_SEC_023 - Verify X-Content-Type-Options: nosniff header presence</t>
   </si>
   <si>
-    <t>4:52:55 PM</t>
-  </si>
-  <si>
-    <t>4:52:58 PM</t>
-  </si>
-  <si>
-    <t>1.38s</t>
+    <t>5:26:09 PM</t>
+  </si>
+  <si>
+    <t>5:26:12 PM</t>
   </si>
   <si>
     <t>TC_SEC_024</t>
@@ -908,7 +944,7 @@
     <t>TC_SEC_024 - Verify Strict-Transport-Security header presence</t>
   </si>
   <si>
-    <t>4:53:06 PM</t>
+    <t>5:26:20 PM</t>
   </si>
   <si>
     <t>TC_SEC_025</t>
@@ -917,13 +953,13 @@
     <t>TC_SEC_025 - Verify Content-Security-Policy header presence</t>
   </si>
   <si>
-    <t>4:53:11 PM</t>
-  </si>
-  <si>
-    <t>4:53:14 PM</t>
-  </si>
-  <si>
-    <t>1.88s</t>
+    <t>5:26:25 PM</t>
+  </si>
+  <si>
+    <t>5:26:28 PM</t>
+  </si>
+  <si>
+    <t>0.69s</t>
   </si>
   <si>
     <t>TC_SEC_026</t>
@@ -932,7 +968,7 @@
     <t>TC_SEC_026 - Verify secure cookie attributes (HttpOnly, Secure)</t>
   </si>
   <si>
-    <t>4:53:22 PM</t>
+    <t>5:26:36 PM</t>
   </si>
   <si>
     <t>TC_SEC_027</t>
@@ -941,13 +977,13 @@
     <t>TC_SEC_027 - Verify rate limiting protection on authentication endpoints</t>
   </si>
   <si>
-    <t>4:53:27 PM</t>
-  </si>
-  <si>
-    <t>4:53:30 PM</t>
-  </si>
-  <si>
-    <t>1.47s</t>
+    <t>5:26:41 PM</t>
+  </si>
+  <si>
+    <t>5:26:44 PM</t>
+  </si>
+  <si>
+    <t>0.59s</t>
   </si>
   <si>
     <t>TC_SEC_028</t>
@@ -956,13 +992,10 @@
     <t>TC_SEC_028 - Verify dependency vulnerabilities with npm audit</t>
   </si>
   <si>
-    <t>4:53:35 PM</t>
-  </si>
-  <si>
-    <t>4:53:38 PM</t>
-  </si>
-  <si>
-    <t>0.62s</t>
+    <t>5:26:49 PM</t>
+  </si>
+  <si>
+    <t>5:26:52 PM</t>
   </si>
   <si>
     <t>TC_SEC_029</t>
@@ -971,10 +1004,10 @@
     <t>TC_SEC_029 - Verify OWASP ZAP active scanning summary</t>
   </si>
   <si>
-    <t>4:53:46 PM</t>
-  </si>
-  <si>
-    <t>0.72s</t>
+    <t>5:27:00 PM</t>
+  </si>
+  <si>
+    <t>1.07s</t>
   </si>
   <si>
     <t>TC_SEC_030</t>
@@ -983,10 +1016,10 @@
     <t>TC_SEC_030 - Verify TLS version compliance checking</t>
   </si>
   <si>
-    <t>4:53:51 PM</t>
-  </si>
-  <si>
-    <t>4:53:54 PM</t>
+    <t>5:27:05 PM</t>
+  </si>
+  <si>
+    <t>5:27:08 PM</t>
   </si>
   <si>
     <t>8.50s</t>
@@ -1001,13 +1034,10 @@
     <t>TC_APP_001 - Verify App Launch activity loads successfully</t>
   </si>
   <si>
-    <t>4:47:59 PM</t>
-  </si>
-  <si>
-    <t>4:48:05 PM</t>
-  </si>
-  <si>
-    <t>3.31s</t>
+    <t>5:21:13 PM</t>
+  </si>
+  <si>
+    <t>5:21:19 PM</t>
   </si>
   <si>
     <t>TC_APP_002</t>
@@ -1016,10 +1046,13 @@
     <t>TC_APP_002 - Verify splash screen transition duration</t>
   </si>
   <si>
-    <t>4:48:11 PM</t>
-  </si>
-  <si>
-    <t>4:48:17 PM</t>
+    <t>5:21:25 PM</t>
+  </si>
+  <si>
+    <t>5:21:31 PM</t>
+  </si>
+  <si>
+    <t>2.28s</t>
   </si>
   <si>
     <t>TC_APP_003</t>
@@ -1028,13 +1061,10 @@
     <t>TC_APP_003 - Verify registration page display inside app</t>
   </si>
   <si>
-    <t>4:48:23 PM</t>
-  </si>
-  <si>
-    <t>4:48:29 PM</t>
-  </si>
-  <si>
-    <t>3.43s</t>
+    <t>5:21:37 PM</t>
+  </si>
+  <si>
+    <t>3.32s</t>
   </si>
   <si>
     <t>TC_APP_004</t>
@@ -1043,13 +1073,13 @@
     <t>TC_APP_004 - Verify new account registration via mobile form</t>
   </si>
   <si>
-    <t>4:48:35 PM</t>
-  </si>
-  <si>
-    <t>4:48:41 PM</t>
-  </si>
-  <si>
-    <t>4.36s</t>
+    <t>5:21:49 PM</t>
+  </si>
+  <si>
+    <t>5:21:55 PM</t>
+  </si>
+  <si>
+    <t>4.92s</t>
   </si>
   <si>
     <t>TC_APP_005</t>
@@ -1058,13 +1088,10 @@
     <t>TC_APP_005 - Verify app displays validation errors on registration</t>
   </si>
   <si>
-    <t>4:48:47 PM</t>
-  </si>
-  <si>
-    <t>4:48:53 PM</t>
-  </si>
-  <si>
-    <t>4.02s</t>
+    <t>5:22:01 PM</t>
+  </si>
+  <si>
+    <t>3.57s</t>
   </si>
   <si>
     <t>TC_APP_006</t>
@@ -1073,10 +1100,10 @@
     <t>TC_APP_006 - Verify Login screen load and fields check</t>
   </si>
   <si>
-    <t>4:49:05 PM</t>
-  </si>
-  <si>
-    <t>2.56s</t>
+    <t>5:22:19 PM</t>
+  </si>
+  <si>
+    <t>4.58s</t>
   </si>
   <si>
     <t>TC_APP_007</t>
@@ -1085,13 +1112,13 @@
     <t>TC_APP_007 - Verify successful authentication with valid credentials</t>
   </si>
   <si>
-    <t>4:49:11 PM</t>
-  </si>
-  <si>
-    <t>4:49:17 PM</t>
-  </si>
-  <si>
-    <t>3.58s</t>
+    <t>5:22:25 PM</t>
+  </si>
+  <si>
+    <t>5:22:31 PM</t>
+  </si>
+  <si>
+    <t>4.24s</t>
   </si>
   <si>
     <t>TC_APP_008</t>
@@ -1100,7 +1127,7 @@
     <t>TC_APP_008 - Verify authentication rejection and toast notification</t>
   </si>
   <si>
-    <t>4.81s</t>
+    <t>2.22s</t>
   </si>
   <si>
     <t>TC_APP_009</t>
@@ -1112,13 +1139,10 @@
     <t>TC_APP_009 - Verify dashboard page layout and toolbar items</t>
   </si>
   <si>
-    <t>4:49:35 PM</t>
-  </si>
-  <si>
-    <t>4:49:41 PM</t>
-  </si>
-  <si>
-    <t>3.39s</t>
+    <t>5:22:49 PM</t>
+  </si>
+  <si>
+    <t>5:22:55 PM</t>
   </si>
   <si>
     <t>TC_APP_010</t>
@@ -1127,10 +1151,10 @@
     <t>TC_APP_010 - Verify scroll and swipe in navigation drawer</t>
   </si>
   <si>
-    <t>4:49:47 PM</t>
-  </si>
-  <si>
-    <t>2.13s</t>
+    <t>5:23:01 PM</t>
+  </si>
+  <si>
+    <t>3.93s</t>
   </si>
   <si>
     <t>TC_APP_011</t>
@@ -1139,10 +1163,10 @@
     <t>TC_APP_011 - Verify add income input dialog form</t>
   </si>
   <si>
-    <t>4:50:05 PM</t>
-  </si>
-  <si>
-    <t>4.49s</t>
+    <t>5:23:19 PM</t>
+  </si>
+  <si>
+    <t>4.69s</t>
   </si>
   <si>
     <t>TC_APP_012</t>
@@ -1151,10 +1175,13 @@
     <t>TC_APP_012 - Verify add income form submission and balance update</t>
   </si>
   <si>
-    <t>4:50:11 PM</t>
-  </si>
-  <si>
-    <t>4:50:17 PM</t>
+    <t>5:23:25 PM</t>
+  </si>
+  <si>
+    <t>5:23:31 PM</t>
+  </si>
+  <si>
+    <t>3.17s</t>
   </si>
   <si>
     <t>TC_APP_013</t>
@@ -1163,7 +1190,7 @@
     <t>TC_APP_013 - Verify add expense input dialog form</t>
   </si>
   <si>
-    <t>4.99s</t>
+    <t>2.98s</t>
   </si>
   <si>
     <t>TC_APP_014</t>
@@ -1172,13 +1199,13 @@
     <t>TC_APP_014 - Verify add expense form submission and balance update</t>
   </si>
   <si>
-    <t>4:50:35 PM</t>
-  </si>
-  <si>
-    <t>4:50:41 PM</t>
-  </si>
-  <si>
-    <t>3.83s</t>
+    <t>5:23:49 PM</t>
+  </si>
+  <si>
+    <t>5:23:55 PM</t>
+  </si>
+  <si>
+    <t>3.37s</t>
   </si>
   <si>
     <t>TC_APP_015</t>
@@ -1187,7 +1214,7 @@
     <t>TC_APP_015 - Verify edit transaction activity opens with details pre-filled</t>
   </si>
   <si>
-    <t>2.53s</t>
+    <t>3.08s</t>
   </si>
   <si>
     <t>TC_APP_016</t>
@@ -1196,10 +1223,10 @@
     <t>TC_APP_016 - Verify transaction title update and save action</t>
   </si>
   <si>
-    <t>4:51:05 PM</t>
-  </si>
-  <si>
-    <t>3.80s</t>
+    <t>5:24:19 PM</t>
+  </si>
+  <si>
+    <t>2.50s</t>
   </si>
   <si>
     <t>TC_APP_017</t>
@@ -1208,7 +1235,10 @@
     <t>TC_APP_017 - Verify transaction deletion click and alert dialog confirmation</t>
   </si>
   <si>
-    <t>4:51:17 PM</t>
+    <t>5:24:31 PM</t>
+  </si>
+  <si>
+    <t>4.19s</t>
   </si>
   <si>
     <t>TC_APP_018</t>
@@ -1229,10 +1259,10 @@
     <t>TC_APP_019 - Verify budget warning alerts are displayed when budget exceeded</t>
   </si>
   <si>
-    <t>4:51:41 PM</t>
-  </si>
-  <si>
-    <t>4.97s</t>
+    <t>5:24:55 PM</t>
+  </si>
+  <si>
+    <t>3.03s</t>
   </si>
   <si>
     <t>TC_APP_020</t>
@@ -1241,10 +1271,7 @@
     <t>TC_APP_020 - Verify notification channel registers correctly in Android OS</t>
   </si>
   <si>
-    <t>4:51:47 PM</t>
-  </si>
-  <si>
-    <t>3.89s</t>
+    <t>5:25:01 PM</t>
   </si>
   <si>
     <t>TC_APP_021</t>
@@ -1253,10 +1280,10 @@
     <t>TC_APP_021 - Verify app local push notification triggers on budget thresholds</t>
   </si>
   <si>
-    <t>4:52:05 PM</t>
-  </si>
-  <si>
-    <t>3.74s</t>
+    <t>5:25:19 PM</t>
+  </si>
+  <si>
+    <t>3.90s</t>
   </si>
   <si>
     <t>TC_APP_022</t>
@@ -1268,13 +1295,13 @@
     <t>TC_APP_022 - Verify profile update form saves new username</t>
   </si>
   <si>
-    <t>4:52:11 PM</t>
-  </si>
-  <si>
-    <t>4:52:17 PM</t>
-  </si>
-  <si>
-    <t>4.70s</t>
+    <t>5:25:25 PM</t>
+  </si>
+  <si>
+    <t>5:25:31 PM</t>
+  </si>
+  <si>
+    <t>4.23s</t>
   </si>
   <si>
     <t>TC_APP_023</t>
@@ -1283,7 +1310,7 @@
     <t>TC_APP_023 - Verify profile image upload simulation</t>
   </si>
   <si>
-    <t>2.74s</t>
+    <t>3.96s</t>
   </si>
   <si>
     <t>TC_APP_024</t>
@@ -1292,13 +1319,13 @@
     <t>TC_APP_024 - Verify change password form validation checks</t>
   </si>
   <si>
-    <t>4:52:35 PM</t>
-  </si>
-  <si>
-    <t>4:52:41 PM</t>
-  </si>
-  <si>
-    <t>3.00s</t>
+    <t>5:25:49 PM</t>
+  </si>
+  <si>
+    <t>5:25:55 PM</t>
+  </si>
+  <si>
+    <t>4.76s</t>
   </si>
   <si>
     <t>TC_APP_025</t>
@@ -1307,7 +1334,7 @@
     <t>TC_APP_025 - Verify successful change password submission</t>
   </si>
   <si>
-    <t>3.08s</t>
+    <t>2.41s</t>
   </si>
   <si>
     <t>TC_APP_026</t>
@@ -1316,43 +1343,40 @@
     <t>TC_APP_026 - Verify dark theme toggle works on main dashboard screen</t>
   </si>
   <si>
-    <t>4:53:05 PM</t>
+    <t>5:26:19 PM</t>
+  </si>
+  <si>
+    <t>TC_APP_027</t>
+  </si>
+  <si>
+    <t>TC_APP_027 - Verify app recovers UI states on device rotation (portrait/landscape)</t>
+  </si>
+  <si>
+    <t>5:26:31 PM</t>
+  </si>
+  <si>
+    <t>3.24s</t>
+  </si>
+  <si>
+    <t>TC_APP_028</t>
+  </si>
+  <si>
+    <t>TC_APP_028 - Verify session recovery on backgrounding and restoring app</t>
   </si>
   <si>
     <t>3.94s</t>
   </si>
   <si>
-    <t>TC_APP_027</t>
-  </si>
-  <si>
-    <t>TC_APP_027 - Verify app recovers UI states on device rotation (portrait/landscape)</t>
-  </si>
-  <si>
-    <t>4:53:17 PM</t>
-  </si>
-  <si>
-    <t>2.07s</t>
-  </si>
-  <si>
-    <t>TC_APP_028</t>
-  </si>
-  <si>
-    <t>TC_APP_028 - Verify session recovery on backgrounding and restoring app</t>
-  </si>
-  <si>
-    <t>4.79s</t>
-  </si>
-  <si>
     <t>TC_APP_029</t>
   </si>
   <si>
     <t>TC_APP_029 - Verify logout button click asks confirmation</t>
   </si>
   <si>
-    <t>4:53:41 PM</t>
-  </si>
-  <si>
-    <t>3.38s</t>
+    <t>5:26:55 PM</t>
+  </si>
+  <si>
+    <t>4.13s</t>
   </si>
   <si>
     <t>TC_APP_030</t>
@@ -1361,7 +1385,7 @@
     <t>TC_APP_030 - Verify successful logout clears local cache database</t>
   </si>
   <si>
-    <t>4:53:47 PM</t>
+    <t>5:27:01 PM</t>
   </si>
   <si>
     <t>12.40s</t>
@@ -1379,13 +1403,13 @@
     <t>Activity Name</t>
   </si>
   <si>
-    <t>AssertionError: expected "/dashboard" to equal "/landing"</t>
+    <t>AssertionError: expected "/reports" to equal "/download"</t>
   </si>
   <si>
     <t>./screenshots/selenium_logout_failure.png</t>
   </si>
   <si>
-    <t>Dashboard Settings View</t>
+    <t>Dashboard Reports View</t>
   </si>
   <si>
     <t>VulnerabilityWarning: Server accepts TLSv1.0 / TLSv1.1 connections</t>
@@ -1418,7 +1442,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>2026-06-15T11:23:59.295Z</t>
+    <t>2026-06-15T11:57:13.568Z</t>
   </si>
   <si>
     <t>Execution of TC_SEL_001</t>
@@ -1517,13 +1541,22 @@
     <t>Execution of TC_SEL_030</t>
   </si>
   <si>
+    <t>Execution of TC_SEL_031</t>
+  </si>
+  <si>
+    <t>Execution of TC_SEL_032</t>
+  </si>
+  <si>
+    <t>Execution of TC_SEL_033</t>
+  </si>
+  <si>
     <t>FAILED</t>
   </si>
   <si>
     <t>Element not interactable / button click intercepted</t>
   </si>
   <si>
-    <t>2026-06-15T11:23:59.334Z</t>
+    <t>2026-06-15T11:57:13.606Z</t>
   </si>
   <si>
     <t>Execution of TC_SEC_001</t>
@@ -1622,7 +1655,7 @@
     <t>Audit found TLS 1.0 support enabled on test server endpoint</t>
   </si>
   <si>
-    <t>2026-06-15T11:23:59.335Z</t>
+    <t>2026-06-15T11:57:13.607Z</t>
   </si>
   <si>
     <t>Execution of TC_APP_001</t>
@@ -2304,10 +2337,10 @@
         <v>13</v>
       </c>
       <c r="E2" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F2" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G2" s="2">
         <v>1</v>
@@ -2348,10 +2381,10 @@
         <v>0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -2359,13 +2392,13 @@
         <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" s="2">
         <v>30</v>
@@ -2380,10 +2413,10 @@
         <v>0</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2391,19 +2424,19 @@
         <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="3">
+        <v>93</v>
+      </c>
+      <c r="F5" s="3">
         <v>90</v>
-      </c>
-      <c r="F5" s="3">
-        <v>87</v>
       </c>
       <c r="G5" s="3">
         <v>3</v>
@@ -2412,10 +2445,10 @@
         <v>0</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2426,7 +2459,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -2440,39 +2473,39 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>12</v>
@@ -2481,24 +2514,24 @@
         <v>5</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>12</v>
@@ -2507,24 +2540,24 @@
         <v>5</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>12</v>
@@ -2533,24 +2566,24 @@
         <v>5</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>12</v>
@@ -2559,24 +2592,24 @@
         <v>5</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>12</v>
@@ -2585,24 +2618,24 @@
         <v>5</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>12</v>
@@ -2611,24 +2644,24 @@
         <v>5</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>12</v>
@@ -2637,24 +2670,24 @@
         <v>5</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>12</v>
@@ -2663,24 +2696,24 @@
         <v>5</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>12</v>
@@ -2689,24 +2722,24 @@
         <v>5</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>12</v>
@@ -2715,24 +2748,24 @@
         <v>5</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>12</v>
@@ -2741,24 +2774,24 @@
         <v>5</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>12</v>
@@ -2767,24 +2800,24 @@
         <v>5</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>12</v>
@@ -2793,24 +2826,24 @@
         <v>5</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>12</v>
@@ -2819,24 +2852,24 @@
         <v>5</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>12</v>
@@ -2845,24 +2878,24 @@
         <v>5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>39</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>12</v>
@@ -2871,24 +2904,24 @@
         <v>5</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>12</v>
@@ -2897,24 +2930,24 @@
         <v>5</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>12</v>
@@ -2923,24 +2956,24 @@
         <v>5</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>12</v>
@@ -2949,24 +2982,24 @@
         <v>5</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>12</v>
@@ -2975,24 +3008,24 @@
         <v>5</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>12</v>
@@ -3001,24 +3034,24 @@
         <v>5</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>12</v>
@@ -3027,24 +3060,24 @@
         <v>5</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>144</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>12</v>
@@ -3053,24 +3086,24 @@
         <v>5</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>12</v>
@@ -3079,24 +3112,24 @@
         <v>5</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>12</v>
@@ -3105,24 +3138,24 @@
         <v>5</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>12</v>
@@ -3131,24 +3164,24 @@
         <v>5</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>12</v>
@@ -3157,24 +3190,24 @@
         <v>5</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>12</v>
@@ -3183,24 +3216,24 @@
         <v>5</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>12</v>
@@ -3209,128 +3242,128 @@
         <v>5</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>6</v>
+      <c r="E31" s="5" t="s">
+        <v>5</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>188</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>67</v>
+        <v>189</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>6</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>17</v>
@@ -3339,24 +3372,24 @@
         <v>5</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>17</v>
@@ -3365,24 +3398,24 @@
         <v>5</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>17</v>
@@ -3391,24 +3424,24 @@
         <v>5</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>88</v>
+        <v>214</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>17</v>
@@ -3417,24 +3450,24 @@
         <v>5</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>217</v>
+        <v>96</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>17</v>
@@ -3443,24 +3476,24 @@
         <v>5</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>17</v>
@@ -3469,24 +3502,24 @@
         <v>5</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>17</v>
@@ -3495,13 +3528,13 @@
         <v>5</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>234</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -3521,24 +3554,24 @@
         <v>5</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>107</v>
+        <v>238</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>190</v>
+        <v>240</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>236</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>17</v>
@@ -3547,13 +3580,13 @@
         <v>5</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>241</v>
+        <v>115</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>243</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -3587,10 +3620,10 @@
         <v>249</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>17</v>
@@ -3599,13 +3632,13 @@
         <v>5</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>252</v>
+        <v>211</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -3613,7 +3646,7 @@
         <v>253</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>254</v>
@@ -3639,7 +3672,7 @@
         <v>258</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>259</v>
@@ -3651,24 +3684,24 @@
         <v>5</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>126</v>
+        <v>260</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>17</v>
@@ -3677,7 +3710,7 @@
         <v>5</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>264</v>
+        <v>135</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>265</v>
@@ -3691,7 +3724,7 @@
         <v>267</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>268</v>
@@ -3717,7 +3750,7 @@
         <v>272</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>273</v>
@@ -3729,7 +3762,7 @@
         <v>5</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>274</v>
@@ -3743,7 +3776,7 @@
         <v>276</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>277</v>
@@ -3769,10 +3802,10 @@
         <v>281</v>
       </c>
       <c r="B52" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>282</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>283</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>17</v>
@@ -3781,24 +3814,24 @@
         <v>5</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>147</v>
+        <v>283</v>
       </c>
       <c r="G52" s="4" t="s">
         <v>284</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>155</v>
+        <v>285</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>282</v>
+        <v>250</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>17</v>
@@ -3807,7 +3840,7 @@
         <v>5</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>287</v>
+        <v>156</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>288</v>
@@ -3821,7 +3854,7 @@
         <v>290</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>282</v>
+        <v>250</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>291</v>
@@ -3847,10 +3880,10 @@
         <v>295</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>17</v>
@@ -3859,24 +3892,24 @@
         <v>5</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>280</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>17</v>
@@ -3885,13 +3918,13 @@
         <v>5</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>302</v>
+        <v>262</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -3899,7 +3932,7 @@
         <v>303</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>304</v>
@@ -3911,24 +3944,24 @@
         <v>5</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>168</v>
+        <v>305</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>271</v>
+        <v>172</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>17</v>
@@ -3937,24 +3970,24 @@
         <v>5</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>308</v>
+        <v>176</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>309</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>310</v>
+        <v>257</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>311</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>312</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>17</v>
@@ -3963,24 +3996,24 @@
         <v>5</v>
       </c>
       <c r="F59" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="G59" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="G59" s="4" t="s">
+      <c r="H59" s="4" t="s">
         <v>314</v>
-      </c>
-      <c r="H59" s="4" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C60" s="4" t="s">
         <v>316</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>317</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>17</v>
@@ -3989,819 +4022,897 @@
         <v>5</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>319</v>
+        <v>61</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E61" s="6" t="s">
-        <v>6</v>
+      <c r="E61" s="5" t="s">
+        <v>5</v>
       </c>
       <c r="F61" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="H61" s="4" t="s">
         <v>322</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="G62" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="C62" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>329</v>
-      </c>
       <c r="H62" s="4" t="s">
-        <v>330</v>
+        <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>326</v>
+        <v>296</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>333</v>
+        <v>195</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>74</v>
+        <v>330</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="H64" s="4" t="s">
         <v>335</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="H64" s="4" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="G65" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="B65" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>343</v>
-      </c>
       <c r="H65" s="4" t="s">
-        <v>344</v>
+        <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="H66" s="4" t="s">
         <v>345</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="H66" s="4" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>37</v>
+        <v>348</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>352</v>
+        <v>39</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="H68" s="4" t="s">
         <v>354</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="H68" s="4" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E69" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>48</v>
+        <v>357</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="H70" s="4" t="s">
         <v>362</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="H70" s="4" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>363</v>
+        <v>337</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E71" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>63</v>
+        <v>366</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>363</v>
+        <v>337</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E72" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>374</v>
+        <v>69</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E73" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>79</v>
+        <v>162</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E74" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>78</v>
+        <v>378</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="H75" s="4" t="s">
         <v>383</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="H76" s="4" t="s">
         <v>388</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H77" s="4" t="s">
         <v>391</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="H77" s="4" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="G78" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="B78" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="C78" s="4" t="s">
+      <c r="H78" s="4" t="s">
         <v>396</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="B79" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="C79" s="4" t="s">
+      <c r="D79" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="H79" s="4" t="s">
         <v>399</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C80" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="D80" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G80" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="H80" s="4" t="s">
         <v>403</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="H80" s="4" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="G81" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="B81" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="C81" s="4" t="s">
+      <c r="H81" s="4" t="s">
         <v>407</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="H81" s="4" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="H82" s="4" t="s">
         <v>410</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="H82" s="4" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="G83" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="H83" s="4" t="s">
         <v>415</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="H83" s="4" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>137</v>
+        <v>418</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>422</v>
+        <v>76</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>425</v>
+        <v>145</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="H86" s="4" t="s">
         <v>428</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>429</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H86" s="4" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="H87" s="4" t="s">
         <v>431</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="H87" s="4" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G88" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="B88" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="C88" s="4" t="s">
+      <c r="H88" s="4" t="s">
         <v>436</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="H89" s="4" t="s">
         <v>439</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F89" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="G89" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="G90" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="B90" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="G90" s="4" t="s">
-        <v>444</v>
-      </c>
       <c r="H90" s="4" t="s">
-        <v>445</v>
+        <v>428</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="H91" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="B91" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="C91" s="4" t="s">
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="D91" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E91" s="6" t="s">
+      <c r="B92" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E94" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F91" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="G91" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>449</v>
+      <c r="F94" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -4825,33 +4936,33 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>12</v>
@@ -4860,18 +4971,18 @@
         <v>13</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>17</v>
@@ -4880,27 +4991,27 @@
         <v>13</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -4911,7 +5022,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -4923,1549 +5034,1600 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>478</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>499</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>500</v>
+        <v>507</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>477</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>501</v>
+        <v>478</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>502</v>
+        <v>475</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>504</v>
+        <v>478</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>502</v>
+        <v>475</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>504</v>
+        <v>478</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>502</v>
+        <v>475</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>506</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>469</v>
+        <v>510</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>511</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>235</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C43" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="E43" s="4" t="s">
         <v>515</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>244</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>249</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>258</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>267</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>272</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>276</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>281</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>290</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>295</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>303</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>533</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>500</v>
+        <v>541</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>477</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>534</v>
+        <v>515</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>535</v>
+        <v>513</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>537</v>
+        <v>515</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>535</v>
+        <v>513</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>537</v>
+        <v>515</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>535</v>
+        <v>513</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>469</v>
+        <v>544</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>511</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C73" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="E73" s="4" t="s">
         <v>548</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>566</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>500</v>
+        <v>574</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>477</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>567</v>
+        <v>548</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>578</v>
       </c>
     </row>
   </sheetData>
@@ -6487,172 +6649,172 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>568</v>
+        <v>579</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>569</v>
+        <v>580</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>570</v>
+        <v>581</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>571</v>
+        <v>582</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>572</v>
+        <v>583</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>573</v>
+        <v>584</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>575</v>
+        <v>586</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>576</v>
+        <v>587</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>577</v>
+        <v>588</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>580</v>
+        <v>591</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>581</v>
+        <v>592</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>582</v>
+        <v>593</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>585</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>586</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>587</v>
+        <v>598</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>588</v>
+        <v>599</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>589</v>
+        <v>600</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>590</v>
+        <v>601</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>591</v>
+        <v>602</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>592</v>
+        <v>603</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>575</v>
+        <v>586</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>593</v>
+        <v>604</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>594</v>
+        <v>605</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>595</v>
+        <v>606</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>596</v>
+        <v>607</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Master_Report.xlsx
+++ b/reports/Master_Report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="612">
   <si>
     <t>Execution Date</t>
   </si>
@@ -47,7 +47,7 @@
     <t>Execution Duration</t>
   </si>
   <si>
-    <t>6/15/2026, 5:27:13 PM</t>
+    <t>6/15/2026, 5:34:55 PM</t>
   </si>
   <si>
     <t>Selenium (Web E2E)</t>
@@ -86,6 +86,9 @@
     <t>13.0</t>
   </si>
   <si>
+    <t>100.00%</t>
+  </si>
+  <si>
     <t>00:06:12</t>
   </si>
   <si>
@@ -95,7 +98,7 @@
     <t>Multi-Platform</t>
   </si>
   <si>
-    <t>96.77%</t>
+    <t>97.85%</t>
   </si>
   <si>
     <t>00:08:37</t>
@@ -134,13 +137,13 @@
     <t>TC_SEL_001 - Verify registration page load</t>
   </si>
   <si>
-    <t>5:21:43 PM</t>
-  </si>
-  <si>
-    <t>5:21:47 PM</t>
-  </si>
-  <si>
-    <t>1.66s</t>
+    <t>5:29:25 PM</t>
+  </si>
+  <si>
+    <t>5:29:29 PM</t>
+  </si>
+  <si>
+    <t>1.37s</t>
   </si>
   <si>
     <t>TC_SEL_002</t>
@@ -149,13 +152,13 @@
     <t>TC_SEL_002 - Verify successful user registration</t>
   </si>
   <si>
-    <t>5:21:53 PM</t>
-  </si>
-  <si>
-    <t>5:21:57 PM</t>
-  </si>
-  <si>
-    <t>1.90s</t>
+    <t>5:29:35 PM</t>
+  </si>
+  <si>
+    <t>5:29:39 PM</t>
+  </si>
+  <si>
+    <t>2.60s</t>
   </si>
   <si>
     <t>TC_SEL_003</t>
@@ -164,838 +167,853 @@
     <t>TC_SEL_003 - Verify registration validation with existing email</t>
   </si>
   <si>
-    <t>5:22:03 PM</t>
-  </si>
-  <si>
-    <t>5:22:07 PM</t>
+    <t>5:29:45 PM</t>
+  </si>
+  <si>
+    <t>5:29:49 PM</t>
+  </si>
+  <si>
+    <t>2.76s</t>
+  </si>
+  <si>
+    <t>TC_SEL_004</t>
+  </si>
+  <si>
+    <t>TC_SEL_004 - Verify registration invalid password constraints</t>
+  </si>
+  <si>
+    <t>5:29:55 PM</t>
+  </si>
+  <si>
+    <t>5:29:59 PM</t>
+  </si>
+  <si>
+    <t>1.21s</t>
+  </si>
+  <si>
+    <t>TC_SEL_005</t>
+  </si>
+  <si>
+    <t>TC_SEL_005 - Verify login page load</t>
+  </si>
+  <si>
+    <t>5:30:05 PM</t>
+  </si>
+  <si>
+    <t>5:30:09 PM</t>
+  </si>
+  <si>
+    <t>2.82s</t>
+  </si>
+  <si>
+    <t>TC_SEL_006</t>
+  </si>
+  <si>
+    <t>TC_SEL_006 - Verify successful login with valid credentials</t>
+  </si>
+  <si>
+    <t>5:30:15 PM</t>
+  </si>
+  <si>
+    <t>5:30:19 PM</t>
+  </si>
+  <si>
+    <t>2.10s</t>
+  </si>
+  <si>
+    <t>TC_SEL_007</t>
+  </si>
+  <si>
+    <t>TC_SEL_007 - Verify login error warning with invalid credentials</t>
+  </si>
+  <si>
+    <t>5:30:25 PM</t>
+  </si>
+  <si>
+    <t>5:30:29 PM</t>
+  </si>
+  <si>
+    <t>2.34s</t>
+  </si>
+  <si>
+    <t>TC_SEL_008</t>
+  </si>
+  <si>
+    <t>TC_SEL_008 - Verify forgot password page load</t>
+  </si>
+  <si>
+    <t>5:30:35 PM</t>
+  </si>
+  <si>
+    <t>5:30:39 PM</t>
+  </si>
+  <si>
+    <t>1.24s</t>
+  </si>
+  <si>
+    <t>TC_SEL_009</t>
+  </si>
+  <si>
+    <t>TC_SEL_009 - Verify forgot password email submission</t>
+  </si>
+  <si>
+    <t>5:30:45 PM</t>
+  </si>
+  <si>
+    <t>5:30:49 PM</t>
+  </si>
+  <si>
+    <t>TC_SEL_010</t>
+  </si>
+  <si>
+    <t>Transactions</t>
+  </si>
+  <si>
+    <t>TC_SEL_010 - Verify dashboard load and initial welcome metrics</t>
+  </si>
+  <si>
+    <t>5:30:55 PM</t>
+  </si>
+  <si>
+    <t>5:30:59 PM</t>
+  </si>
+  <si>
+    <t>1.85s</t>
+  </si>
+  <si>
+    <t>TC_SEL_011</t>
+  </si>
+  <si>
+    <t>TC_SEL_011 - Verify add income transaction</t>
+  </si>
+  <si>
+    <t>5:31:05 PM</t>
+  </si>
+  <si>
+    <t>5:31:09 PM</t>
+  </si>
+  <si>
+    <t>1.23s</t>
+  </si>
+  <si>
+    <t>TC_SEL_012</t>
+  </si>
+  <si>
+    <t>TC_SEL_012 - Verify add expense transaction</t>
+  </si>
+  <si>
+    <t>5:31:15 PM</t>
+  </si>
+  <si>
+    <t>5:31:19 PM</t>
+  </si>
+  <si>
+    <t>TC_SEL_013</t>
+  </si>
+  <si>
+    <t>TC_SEL_013 - Verify transaction field input sanitization</t>
+  </si>
+  <si>
+    <t>5:31:25 PM</t>
+  </si>
+  <si>
+    <t>5:31:29 PM</t>
+  </si>
+  <si>
+    <t>1.48s</t>
+  </si>
+  <si>
+    <t>TC_SEL_014</t>
+  </si>
+  <si>
+    <t>TC_SEL_014 - Verify edit transaction title</t>
+  </si>
+  <si>
+    <t>5:31:35 PM</t>
+  </si>
+  <si>
+    <t>5:31:39 PM</t>
+  </si>
+  <si>
+    <t>2.81s</t>
+  </si>
+  <si>
+    <t>TC_SEL_015</t>
+  </si>
+  <si>
+    <t>TC_SEL_015 - Verify edit transaction amount and category updates</t>
+  </si>
+  <si>
+    <t>5:31:45 PM</t>
+  </si>
+  <si>
+    <t>5:31:49 PM</t>
+  </si>
+  <si>
+    <t>2.72s</t>
+  </si>
+  <si>
+    <t>TC_SEL_016</t>
+  </si>
+  <si>
+    <t>TC_SEL_016 - Verify transaction deletion and balance recalculation</t>
+  </si>
+  <si>
+    <t>5:31:55 PM</t>
+  </si>
+  <si>
+    <t>5:31:59 PM</t>
+  </si>
+  <si>
+    <t>1.70s</t>
+  </si>
+  <si>
+    <t>TC_SEL_017</t>
+  </si>
+  <si>
+    <t>TC_SEL_017 - Verify search transaction by keyword</t>
+  </si>
+  <si>
+    <t>5:32:05 PM</t>
+  </si>
+  <si>
+    <t>5:32:09 PM</t>
+  </si>
+  <si>
+    <t>1.16s</t>
+  </si>
+  <si>
+    <t>TC_SEL_018</t>
+  </si>
+  <si>
+    <t>TC_SEL_018 - Verify filter transactions by category</t>
+  </si>
+  <si>
+    <t>5:32:15 PM</t>
+  </si>
+  <si>
+    <t>5:32:19 PM</t>
+  </si>
+  <si>
+    <t>2.27s</t>
+  </si>
+  <si>
+    <t>TC_SEL_019</t>
+  </si>
+  <si>
+    <t>TC_SEL_019 - Verify filter transactions by date ranges</t>
+  </si>
+  <si>
+    <t>5:32:25 PM</t>
+  </si>
+  <si>
+    <t>5:32:29 PM</t>
+  </si>
+  <si>
+    <t>2.02s</t>
+  </si>
+  <si>
+    <t>TC_SEL_020</t>
+  </si>
+  <si>
+    <t>TC_SEL_020 - Verify sort transactions by date ascending/descending</t>
+  </si>
+  <si>
+    <t>5:32:35 PM</t>
+  </si>
+  <si>
+    <t>5:32:39 PM</t>
+  </si>
+  <si>
+    <t>1.63s</t>
+  </si>
+  <si>
+    <t>TC_SEL_021</t>
+  </si>
+  <si>
+    <t>TC_SEL_021 - Verify sort transactions by amount ascending/descending</t>
+  </si>
+  <si>
+    <t>5:32:45 PM</t>
+  </si>
+  <si>
+    <t>5:32:49 PM</t>
+  </si>
+  <si>
+    <t>2.24s</t>
+  </si>
+  <si>
+    <t>TC_SEL_022</t>
+  </si>
+  <si>
+    <t>Budget</t>
+  </si>
+  <si>
+    <t>TC_SEL_022 - Verify monthly budget creation and save button</t>
+  </si>
+  <si>
+    <t>5:32:55 PM</t>
+  </si>
+  <si>
+    <t>5:32:59 PM</t>
+  </si>
+  <si>
+    <t>2.96s</t>
+  </si>
+  <si>
+    <t>TC_SEL_023</t>
+  </si>
+  <si>
+    <t>TC_SEL_023 - Verify budget progress bar updates on transactions</t>
+  </si>
+  <si>
+    <t>5:33:05 PM</t>
+  </si>
+  <si>
+    <t>5:33:09 PM</t>
+  </si>
+  <si>
+    <t>1.81s</t>
+  </si>
+  <si>
+    <t>TC_SEL_024</t>
+  </si>
+  <si>
+    <t>Reports</t>
+  </si>
+  <si>
+    <t>TC_SEL_024 - Verify monthly PDF report generation</t>
+  </si>
+  <si>
+    <t>5:33:15 PM</t>
+  </si>
+  <si>
+    <t>5:33:19 PM</t>
+  </si>
+  <si>
+    <t>2.66s</t>
+  </si>
+  <si>
+    <t>TC_SEL_025</t>
+  </si>
+  <si>
+    <t>TC_SEL_025 - Verify charts render correctly in reports view</t>
+  </si>
+  <si>
+    <t>5:33:25 PM</t>
+  </si>
+  <si>
+    <t>5:33:29 PM</t>
+  </si>
+  <si>
+    <t>2.59s</t>
+  </si>
+  <si>
+    <t>TC_SEL_026</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>TC_SEL_026 - Verify profile details update</t>
+  </si>
+  <si>
+    <t>5:33:35 PM</t>
+  </si>
+  <si>
+    <t>5:33:39 PM</t>
+  </si>
+  <si>
+    <t>TC_SEL_027</t>
+  </si>
+  <si>
+    <t>TC_SEL_027 - Verify password update functionality</t>
+  </si>
+  <si>
+    <t>5:33:45 PM</t>
+  </si>
+  <si>
+    <t>5:33:49 PM</t>
+  </si>
+  <si>
+    <t>1.27s</t>
+  </si>
+  <si>
+    <t>TC_SEL_028</t>
+  </si>
+  <si>
+    <t>TC_SEL_028 - Verify currency settings updates</t>
+  </si>
+  <si>
+    <t>5:33:55 PM</t>
+  </si>
+  <si>
+    <t>5:33:59 PM</t>
+  </si>
+  <si>
+    <t>2.87s</t>
+  </si>
+  <si>
+    <t>TC_SEL_029</t>
+  </si>
+  <si>
+    <t>TC_SEL_029 - Verify session persistence on page refresh</t>
+  </si>
+  <si>
+    <t>5:34:05 PM</t>
+  </si>
+  <si>
+    <t>5:34:09 PM</t>
+  </si>
+  <si>
+    <t>2.89s</t>
+  </si>
+  <si>
+    <t>TC_SEL_030</t>
+  </si>
+  <si>
+    <t>TC_SEL_030 - Verify successful user logout and redirection</t>
+  </si>
+  <si>
+    <t>5:34:15 PM</t>
+  </si>
+  <si>
+    <t>5:34:19 PM</t>
   </si>
   <si>
     <t>2.53s</t>
   </si>
   <si>
-    <t>TC_SEL_004</t>
-  </si>
-  <si>
-    <t>TC_SEL_004 - Verify registration invalid password constraints</t>
-  </si>
-  <si>
-    <t>5:22:13 PM</t>
-  </si>
-  <si>
-    <t>5:22:17 PM</t>
-  </si>
-  <si>
-    <t>2.39s</t>
-  </si>
-  <si>
-    <t>TC_SEL_005</t>
-  </si>
-  <si>
-    <t>TC_SEL_005 - Verify login page load</t>
-  </si>
-  <si>
-    <t>5:22:23 PM</t>
-  </si>
-  <si>
-    <t>5:22:27 PM</t>
-  </si>
-  <si>
-    <t>1.86s</t>
-  </si>
-  <si>
-    <t>TC_SEL_006</t>
-  </si>
-  <si>
-    <t>TC_SEL_006 - Verify successful login with valid credentials</t>
-  </si>
-  <si>
-    <t>5:22:33 PM</t>
-  </si>
-  <si>
-    <t>5:22:37 PM</t>
-  </si>
-  <si>
-    <t>2.76s</t>
-  </si>
-  <si>
-    <t>TC_SEL_007</t>
-  </si>
-  <si>
-    <t>TC_SEL_007 - Verify login error warning with invalid credentials</t>
-  </si>
-  <si>
-    <t>5:22:43 PM</t>
-  </si>
-  <si>
-    <t>5:22:47 PM</t>
-  </si>
-  <si>
-    <t>1.61s</t>
-  </si>
-  <si>
-    <t>TC_SEL_008</t>
-  </si>
-  <si>
-    <t>TC_SEL_008 - Verify forgot password page load</t>
-  </si>
-  <si>
-    <t>5:22:53 PM</t>
-  </si>
-  <si>
-    <t>5:22:57 PM</t>
-  </si>
-  <si>
-    <t>2.96s</t>
-  </si>
-  <si>
-    <t>TC_SEL_009</t>
-  </si>
-  <si>
-    <t>TC_SEL_009 - Verify forgot password email submission</t>
-  </si>
-  <si>
-    <t>5:23:03 PM</t>
-  </si>
-  <si>
-    <t>5:23:07 PM</t>
-  </si>
-  <si>
-    <t>2.33s</t>
-  </si>
-  <si>
-    <t>TC_SEL_010</t>
-  </si>
-  <si>
-    <t>Transactions</t>
-  </si>
-  <si>
-    <t>TC_SEL_010 - Verify dashboard load and initial welcome metrics</t>
-  </si>
-  <si>
-    <t>5:23:13 PM</t>
-  </si>
-  <si>
-    <t>5:23:17 PM</t>
-  </si>
-  <si>
-    <t>2.63s</t>
-  </si>
-  <si>
-    <t>TC_SEL_011</t>
-  </si>
-  <si>
-    <t>TC_SEL_011 - Verify add income transaction</t>
-  </si>
-  <si>
-    <t>5:23:23 PM</t>
-  </si>
-  <si>
-    <t>5:23:27 PM</t>
-  </si>
-  <si>
-    <t>2.10s</t>
-  </si>
-  <si>
-    <t>TC_SEL_012</t>
-  </si>
-  <si>
-    <t>TC_SEL_012 - Verify add expense transaction</t>
-  </si>
-  <si>
-    <t>5:23:33 PM</t>
-  </si>
-  <si>
-    <t>5:23:37 PM</t>
-  </si>
-  <si>
-    <t>2.80s</t>
-  </si>
-  <si>
-    <t>TC_SEL_013</t>
-  </si>
-  <si>
-    <t>TC_SEL_013 - Verify transaction field input sanitization</t>
-  </si>
-  <si>
-    <t>5:23:43 PM</t>
-  </si>
-  <si>
-    <t>5:23:47 PM</t>
-  </si>
-  <si>
-    <t>1.37s</t>
-  </si>
-  <si>
-    <t>TC_SEL_014</t>
-  </si>
-  <si>
-    <t>TC_SEL_014 - Verify edit transaction title</t>
-  </si>
-  <si>
-    <t>5:23:53 PM</t>
-  </si>
-  <si>
-    <t>5:23:57 PM</t>
-  </si>
-  <si>
-    <t>TC_SEL_015</t>
-  </si>
-  <si>
-    <t>TC_SEL_015 - Verify edit transaction amount and category updates</t>
-  </si>
-  <si>
-    <t>5:24:03 PM</t>
-  </si>
-  <si>
-    <t>5:24:07 PM</t>
-  </si>
-  <si>
-    <t>2.67s</t>
-  </si>
-  <si>
-    <t>TC_SEL_016</t>
-  </si>
-  <si>
-    <t>TC_SEL_016 - Verify transaction deletion and balance recalculation</t>
-  </si>
-  <si>
-    <t>5:24:13 PM</t>
-  </si>
-  <si>
-    <t>5:24:17 PM</t>
-  </si>
-  <si>
-    <t>2.13s</t>
-  </si>
-  <si>
-    <t>TC_SEL_017</t>
-  </si>
-  <si>
-    <t>TC_SEL_017 - Verify search transaction by keyword</t>
-  </si>
-  <si>
-    <t>5:24:23 PM</t>
-  </si>
-  <si>
-    <t>5:24:27 PM</t>
-  </si>
-  <si>
-    <t>2.24s</t>
-  </si>
-  <si>
-    <t>TC_SEL_018</t>
-  </si>
-  <si>
-    <t>TC_SEL_018 - Verify filter transactions by category</t>
-  </si>
-  <si>
-    <t>5:24:33 PM</t>
-  </si>
-  <si>
-    <t>5:24:37 PM</t>
-  </si>
-  <si>
-    <t>1.34s</t>
-  </si>
-  <si>
-    <t>TC_SEL_019</t>
-  </si>
-  <si>
-    <t>TC_SEL_019 - Verify filter transactions by date ranges</t>
-  </si>
-  <si>
-    <t>5:24:43 PM</t>
-  </si>
-  <si>
-    <t>5:24:47 PM</t>
+    <t>TC_SEL_031</t>
+  </si>
+  <si>
+    <t>TC_SEL_031 - Verify currency settings updates in layout</t>
+  </si>
+  <si>
+    <t>5:34:25 PM</t>
+  </si>
+  <si>
+    <t>5:34:29 PM</t>
+  </si>
+  <si>
+    <t>1.02s</t>
+  </si>
+  <si>
+    <t>TC_SEL_032</t>
+  </si>
+  <si>
+    <t>TC_SEL_032 - Verify monthly budget limit notifications triggers</t>
+  </si>
+  <si>
+    <t>5:34:35 PM</t>
+  </si>
+  <si>
+    <t>5:34:39 PM</t>
+  </si>
+  <si>
+    <t>TC_SEL_033</t>
+  </si>
+  <si>
+    <t>TC_SEL_033 - Verify monthly PDF report download functionality</t>
+  </si>
+  <si>
+    <t>5:34:45 PM</t>
+  </si>
+  <si>
+    <t>5:34:49 PM</t>
+  </si>
+  <si>
+    <t>5.12s</t>
+  </si>
+  <si>
+    <t>TC_SEC_001</t>
+  </si>
+  <si>
+    <t>Auth Injection</t>
+  </si>
+  <si>
+    <t>TC_SEC_001 - Verify SQL injection prevention in Login email field</t>
+  </si>
+  <si>
+    <t>5:30:58 PM</t>
+  </si>
+  <si>
+    <t>1.59s</t>
+  </si>
+  <si>
+    <t>TC_SEC_002</t>
+  </si>
+  <si>
+    <t>TC_SEC_002 - Verify SQL injection prevention in Login password field</t>
+  </si>
+  <si>
+    <t>5:31:03 PM</t>
+  </si>
+  <si>
+    <t>5:31:06 PM</t>
+  </si>
+  <si>
+    <t>0.94s</t>
+  </si>
+  <si>
+    <t>TC_SEC_003</t>
+  </si>
+  <si>
+    <t>TC_SEC_003 - Verify SQL injection prevention in register input fields</t>
+  </si>
+  <si>
+    <t>5:31:11 PM</t>
+  </si>
+  <si>
+    <t>5:31:14 PM</t>
+  </si>
+  <si>
+    <t>1.31s</t>
+  </si>
+  <si>
+    <t>TC_SEC_004</t>
+  </si>
+  <si>
+    <t>CSRF Prevention</t>
+  </si>
+  <si>
+    <t>TC_SEC_004 - Verify HTML / Script tag sanitization in transaction title input</t>
+  </si>
+  <si>
+    <t>5:31:22 PM</t>
+  </si>
+  <si>
+    <t>1.67s</t>
+  </si>
+  <si>
+    <t>TC_SEC_005</t>
+  </si>
+  <si>
+    <t>TC_SEC_005 - Verify sanitization of script tags in transaction category input</t>
+  </si>
+  <si>
+    <t>5:31:27 PM</t>
+  </si>
+  <si>
+    <t>5:31:30 PM</t>
+  </si>
+  <si>
+    <t>1.97s</t>
+  </si>
+  <si>
+    <t>TC_SEC_006</t>
+  </si>
+  <si>
+    <t>TC_SEC_006 - Verify anti-CSRF token verification on POST transactions endpoint</t>
+  </si>
+  <si>
+    <t>5:31:38 PM</t>
+  </si>
+  <si>
+    <t>TC_SEC_007</t>
+  </si>
+  <si>
+    <t>TC_SEC_007 - Verify anti-CSRF token verification on DELETE budget endpoint</t>
+  </si>
+  <si>
+    <t>5:31:43 PM</t>
+  </si>
+  <si>
+    <t>5:31:46 PM</t>
+  </si>
+  <si>
+    <t>1.01s</t>
+  </si>
+  <si>
+    <t>TC_SEC_008</t>
+  </si>
+  <si>
+    <t>JWT Validation</t>
+  </si>
+  <si>
+    <t>TC_SEC_008 - Verify JWT token validation with incorrect signatures</t>
+  </si>
+  <si>
+    <t>5:31:51 PM</t>
+  </si>
+  <si>
+    <t>5:31:54 PM</t>
+  </si>
+  <si>
+    <t>0.87s</t>
+  </si>
+  <si>
+    <t>TC_SEC_009</t>
+  </si>
+  <si>
+    <t>TC_SEC_009 - Verify JWT token expiration enforcement</t>
+  </si>
+  <si>
+    <t>5:32:02 PM</t>
+  </si>
+  <si>
+    <t>1.19s</t>
+  </si>
+  <si>
+    <t>TC_SEC_010</t>
+  </si>
+  <si>
+    <t>TC_SEC_010 - Verify session timeout redirection after inactivity</t>
+  </si>
+  <si>
+    <t>5:32:07 PM</t>
+  </si>
+  <si>
+    <t>5:32:10 PM</t>
+  </si>
+  <si>
+    <t>1.41s</t>
+  </si>
+  <si>
+    <t>TC_SEC_011</t>
+  </si>
+  <si>
+    <t>Access Control</t>
+  </si>
+  <si>
+    <t>TC_SEC_011 - Verify input length validations on transaction title</t>
+  </si>
+  <si>
+    <t>5:32:18 PM</t>
+  </si>
+  <si>
+    <t>1.73s</t>
+  </si>
+  <si>
+    <t>TC_SEC_012</t>
+  </si>
+  <si>
+    <t>TC_SEC_012 - Verify negative amount validation on transaction entries</t>
+  </si>
+  <si>
+    <t>5:32:23 PM</t>
+  </si>
+  <si>
+    <t>5:32:26 PM</t>
+  </si>
+  <si>
+    <t>1.53s</t>
+  </si>
+  <si>
+    <t>TC_SEC_013</t>
+  </si>
+  <si>
+    <t>TC_SEC_013 - Verify non-numeric input rejection on budget amounts</t>
+  </si>
+  <si>
+    <t>5:32:31 PM</t>
+  </si>
+  <si>
+    <t>5:32:34 PM</t>
+  </si>
+  <si>
+    <t>0.82s</t>
+  </si>
+  <si>
+    <t>TC_SEC_014</t>
+  </si>
+  <si>
+    <t>TC_SEC_014 - Verify authorization checks for transaction deletion</t>
+  </si>
+  <si>
+    <t>5:32:42 PM</t>
+  </si>
+  <si>
+    <t>1.29s</t>
+  </si>
+  <si>
+    <t>TC_SEC_015</t>
+  </si>
+  <si>
+    <t>TC_SEC_015 - Verify access control: guest user cannot access dashboard API</t>
+  </si>
+  <si>
+    <t>5:32:47 PM</t>
+  </si>
+  <si>
+    <t>5:32:50 PM</t>
+  </si>
+  <si>
+    <t>1.99s</t>
+  </si>
+  <si>
+    <t>TC_SEC_016</t>
+  </si>
+  <si>
+    <t>TC_SEC_016 - Verify access control: user cannot view other users transactions</t>
+  </si>
+  <si>
+    <t>5:32:58 PM</t>
   </si>
   <si>
     <t>1.79s</t>
   </si>
   <si>
-    <t>TC_SEL_020</t>
-  </si>
-  <si>
-    <t>TC_SEL_020 - Verify sort transactions by date ascending/descending</t>
-  </si>
-  <si>
-    <t>5:24:53 PM</t>
-  </si>
-  <si>
-    <t>5:24:57 PM</t>
-  </si>
-  <si>
-    <t>1.03s</t>
-  </si>
-  <si>
-    <t>TC_SEL_021</t>
-  </si>
-  <si>
-    <t>TC_SEL_021 - Verify sort transactions by amount ascending/descending</t>
-  </si>
-  <si>
-    <t>5:25:03 PM</t>
-  </si>
-  <si>
-    <t>5:25:07 PM</t>
-  </si>
-  <si>
-    <t>1.94s</t>
-  </si>
-  <si>
-    <t>TC_SEL_022</t>
-  </si>
-  <si>
-    <t>Budget</t>
-  </si>
-  <si>
-    <t>TC_SEL_022 - Verify monthly budget creation and save button</t>
-  </si>
-  <si>
-    <t>5:25:13 PM</t>
-  </si>
-  <si>
-    <t>5:25:17 PM</t>
-  </si>
-  <si>
-    <t>TC_SEL_023</t>
-  </si>
-  <si>
-    <t>TC_SEL_023 - Verify budget progress bar updates on transactions</t>
-  </si>
-  <si>
-    <t>5:25:23 PM</t>
-  </si>
-  <si>
-    <t>5:25:27 PM</t>
-  </si>
-  <si>
-    <t>2.79s</t>
-  </si>
-  <si>
-    <t>TC_SEL_024</t>
-  </si>
-  <si>
-    <t>Reports</t>
-  </si>
-  <si>
-    <t>TC_SEL_024 - Verify monthly PDF report generation</t>
-  </si>
-  <si>
-    <t>5:25:33 PM</t>
-  </si>
-  <si>
-    <t>5:25:37 PM</t>
-  </si>
-  <si>
-    <t>1.58s</t>
-  </si>
-  <si>
-    <t>TC_SEL_025</t>
-  </si>
-  <si>
-    <t>TC_SEL_025 - Verify charts render correctly in reports view</t>
-  </si>
-  <si>
-    <t>5:25:43 PM</t>
-  </si>
-  <si>
-    <t>5:25:47 PM</t>
-  </si>
-  <si>
-    <t>2.48s</t>
-  </si>
-  <si>
-    <t>TC_SEL_026</t>
-  </si>
-  <si>
-    <t>Profile</t>
-  </si>
-  <si>
-    <t>TC_SEL_026 - Verify profile details update</t>
-  </si>
-  <si>
-    <t>5:25:53 PM</t>
-  </si>
-  <si>
-    <t>5:25:57 PM</t>
-  </si>
-  <si>
-    <t>TC_SEL_027</t>
-  </si>
-  <si>
-    <t>TC_SEL_027 - Verify password update functionality</t>
-  </si>
-  <si>
-    <t>5:26:03 PM</t>
-  </si>
-  <si>
-    <t>5:26:07 PM</t>
-  </si>
-  <si>
-    <t>1.88s</t>
-  </si>
-  <si>
-    <t>TC_SEL_028</t>
-  </si>
-  <si>
-    <t>TC_SEL_028 - Verify currency settings updates</t>
-  </si>
-  <si>
-    <t>5:26:13 PM</t>
-  </si>
-  <si>
-    <t>5:26:17 PM</t>
-  </si>
-  <si>
-    <t>2.85s</t>
-  </si>
-  <si>
-    <t>TC_SEL_029</t>
-  </si>
-  <si>
-    <t>TC_SEL_029 - Verify session persistence on page refresh</t>
-  </si>
-  <si>
-    <t>5:26:23 PM</t>
-  </si>
-  <si>
-    <t>5:26:27 PM</t>
-  </si>
-  <si>
-    <t>TC_SEL_030</t>
-  </si>
-  <si>
-    <t>TC_SEL_030 - Verify successful user logout and redirection</t>
-  </si>
-  <si>
-    <t>5:26:33 PM</t>
-  </si>
-  <si>
-    <t>5:26:37 PM</t>
-  </si>
-  <si>
-    <t>2.92s</t>
-  </si>
-  <si>
-    <t>TC_SEL_031</t>
-  </si>
-  <si>
-    <t>TC_SEL_031 - Verify currency settings updates in layout</t>
-  </si>
-  <si>
-    <t>5:26:43 PM</t>
-  </si>
-  <si>
-    <t>5:26:47 PM</t>
-  </si>
-  <si>
-    <t>2.38s</t>
-  </si>
-  <si>
-    <t>TC_SEL_032</t>
-  </si>
-  <si>
-    <t>TC_SEL_032 - Verify monthly budget limit notifications triggers</t>
-  </si>
-  <si>
-    <t>5:26:53 PM</t>
-  </si>
-  <si>
-    <t>5:26:57 PM</t>
-  </si>
-  <si>
-    <t>2.78s</t>
-  </si>
-  <si>
-    <t>TC_SEL_033</t>
-  </si>
-  <si>
-    <t>TC_SEL_033 - Verify monthly PDF report download functionality</t>
-  </si>
-  <si>
-    <t>5:27:03 PM</t>
-  </si>
-  <si>
-    <t>5:27:07 PM</t>
-  </si>
-  <si>
-    <t>5.12s</t>
-  </si>
-  <si>
-    <t>TC_SEC_001</t>
-  </si>
-  <si>
-    <t>Auth Injection</t>
-  </si>
-  <si>
-    <t>TC_SEC_001 - Verify SQL injection prevention in Login email field</t>
-  </si>
-  <si>
-    <t>5:23:16 PM</t>
-  </si>
-  <si>
-    <t>0.84s</t>
-  </si>
-  <si>
-    <t>TC_SEC_002</t>
-  </si>
-  <si>
-    <t>TC_SEC_002 - Verify SQL injection prevention in Login password field</t>
-  </si>
-  <si>
-    <t>5:23:21 PM</t>
-  </si>
-  <si>
-    <t>5:23:24 PM</t>
-  </si>
-  <si>
-    <t>0.61s</t>
-  </si>
-  <si>
-    <t>TC_SEC_003</t>
-  </si>
-  <si>
-    <t>TC_SEC_003 - Verify SQL injection prevention in register input fields</t>
-  </si>
-  <si>
-    <t>5:23:29 PM</t>
-  </si>
-  <si>
-    <t>5:23:32 PM</t>
+    <t>TC_SEC_017</t>
+  </si>
+  <si>
+    <t>TC_SEC_017 - Verify password hash complexity strength check</t>
+  </si>
+  <si>
+    <t>5:33:03 PM</t>
+  </si>
+  <si>
+    <t>5:33:06 PM</t>
+  </si>
+  <si>
+    <t>1.72s</t>
+  </si>
+  <si>
+    <t>TC_SEC_018</t>
+  </si>
+  <si>
+    <t>TC_SEC_018 - Verify file upload size validations</t>
+  </si>
+  <si>
+    <t>5:33:11 PM</t>
+  </si>
+  <si>
+    <t>5:33:14 PM</t>
+  </si>
+  <si>
+    <t>0.74s</t>
+  </si>
+  <si>
+    <t>TC_SEC_019</t>
+  </si>
+  <si>
+    <t>TC_SEC_019 - Verify file upload extension whitelist block (.sh, .exe, .js)</t>
+  </si>
+  <si>
+    <t>5:33:22 PM</t>
+  </si>
+  <si>
+    <t>0.55s</t>
+  </si>
+  <si>
+    <t>TC_SEC_020</t>
+  </si>
+  <si>
+    <t>TC_SEC_020 - Verify API authorization on budgets edit endpoint</t>
+  </si>
+  <si>
+    <t>5:33:27 PM</t>
+  </si>
+  <si>
+    <t>5:33:30 PM</t>
+  </si>
+  <si>
+    <t>0.59s</t>
+  </si>
+  <si>
+    <t>TC_SEC_021</t>
+  </si>
+  <si>
+    <t>HTTP Headers</t>
+  </si>
+  <si>
+    <t>TC_SEC_021 - Verify CORS policy matches trusted domains only</t>
+  </si>
+  <si>
+    <t>5:33:38 PM</t>
+  </si>
+  <si>
+    <t>1.74s</t>
+  </si>
+  <si>
+    <t>TC_SEC_022</t>
+  </si>
+  <si>
+    <t>TC_SEC_022 - Verify X-Frame-Options: SAMEORIGIN header presence</t>
+  </si>
+  <si>
+    <t>5:33:43 PM</t>
+  </si>
+  <si>
+    <t>5:33:46 PM</t>
+  </si>
+  <si>
+    <t>0.73s</t>
+  </si>
+  <si>
+    <t>TC_SEC_023</t>
+  </si>
+  <si>
+    <t>TC_SEC_023 - Verify X-Content-Type-Options: nosniff header presence</t>
+  </si>
+  <si>
+    <t>5:33:51 PM</t>
+  </si>
+  <si>
+    <t>5:33:54 PM</t>
+  </si>
+  <si>
+    <t>TC_SEC_024</t>
+  </si>
+  <si>
+    <t>TC_SEC_024 - Verify Strict-Transport-Security header presence</t>
+  </si>
+  <si>
+    <t>5:34:02 PM</t>
+  </si>
+  <si>
+    <t>TC_SEC_025</t>
+  </si>
+  <si>
+    <t>TC_SEC_025 - Verify Content-Security-Policy header presence</t>
+  </si>
+  <si>
+    <t>5:34:07 PM</t>
+  </si>
+  <si>
+    <t>5:34:10 PM</t>
+  </si>
+  <si>
+    <t>1.52s</t>
+  </si>
+  <si>
+    <t>TC_SEC_026</t>
+  </si>
+  <si>
+    <t>TC_SEC_026 - Verify secure cookie attributes (HttpOnly, Secure)</t>
+  </si>
+  <si>
+    <t>5:34:18 PM</t>
+  </si>
+  <si>
+    <t>0.69s</t>
+  </si>
+  <si>
+    <t>TC_SEC_027</t>
+  </si>
+  <si>
+    <t>TC_SEC_027 - Verify rate limiting protection on authentication endpoints</t>
+  </si>
+  <si>
+    <t>5:34:23 PM</t>
+  </si>
+  <si>
+    <t>5:34:26 PM</t>
   </si>
   <si>
     <t>1.50s</t>
   </si>
   <si>
-    <t>TC_SEC_004</t>
-  </si>
-  <si>
-    <t>CSRF Prevention</t>
-  </si>
-  <si>
-    <t>TC_SEC_004 - Verify HTML / Script tag sanitization in transaction title input</t>
-  </si>
-  <si>
-    <t>5:23:40 PM</t>
-  </si>
-  <si>
-    <t>1.60s</t>
-  </si>
-  <si>
-    <t>TC_SEC_005</t>
-  </si>
-  <si>
-    <t>TC_SEC_005 - Verify sanitization of script tags in transaction category input</t>
-  </si>
-  <si>
-    <t>5:23:45 PM</t>
-  </si>
-  <si>
-    <t>5:23:48 PM</t>
-  </si>
-  <si>
-    <t>1.93s</t>
-  </si>
-  <si>
-    <t>TC_SEC_006</t>
-  </si>
-  <si>
-    <t>TC_SEC_006 - Verify anti-CSRF token verification on POST transactions endpoint</t>
-  </si>
-  <si>
-    <t>5:23:56 PM</t>
-  </si>
-  <si>
-    <t>1.97s</t>
-  </si>
-  <si>
-    <t>TC_SEC_007</t>
-  </si>
-  <si>
-    <t>TC_SEC_007 - Verify anti-CSRF token verification on DELETE budget endpoint</t>
-  </si>
-  <si>
-    <t>5:24:01 PM</t>
-  </si>
-  <si>
-    <t>5:24:04 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_008</t>
-  </si>
-  <si>
-    <t>JWT Validation</t>
-  </si>
-  <si>
-    <t>TC_SEC_008 - Verify JWT token validation with incorrect signatures</t>
-  </si>
-  <si>
-    <t>5:24:09 PM</t>
-  </si>
-  <si>
-    <t>5:24:12 PM</t>
-  </si>
-  <si>
-    <t>1.63s</t>
-  </si>
-  <si>
-    <t>TC_SEC_009</t>
-  </si>
-  <si>
-    <t>TC_SEC_009 - Verify JWT token expiration enforcement</t>
-  </si>
-  <si>
-    <t>5:24:20 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_010</t>
-  </si>
-  <si>
-    <t>TC_SEC_010 - Verify session timeout redirection after inactivity</t>
-  </si>
-  <si>
-    <t>5:24:25 PM</t>
-  </si>
-  <si>
-    <t>5:24:28 PM</t>
-  </si>
-  <si>
-    <t>1.26s</t>
-  </si>
-  <si>
-    <t>TC_SEC_011</t>
-  </si>
-  <si>
-    <t>Access Control</t>
-  </si>
-  <si>
-    <t>TC_SEC_011 - Verify input length validations on transaction title</t>
-  </si>
-  <si>
-    <t>5:24:36 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_012</t>
-  </si>
-  <si>
-    <t>TC_SEC_012 - Verify negative amount validation on transaction entries</t>
-  </si>
-  <si>
-    <t>5:24:41 PM</t>
-  </si>
-  <si>
-    <t>5:24:44 PM</t>
-  </si>
-  <si>
-    <t>1.41s</t>
-  </si>
-  <si>
-    <t>TC_SEC_013</t>
-  </si>
-  <si>
-    <t>TC_SEC_013 - Verify non-numeric input rejection on budget amounts</t>
-  </si>
-  <si>
-    <t>5:24:49 PM</t>
-  </si>
-  <si>
-    <t>5:24:52 PM</t>
-  </si>
-  <si>
-    <t>0.91s</t>
-  </si>
-  <si>
-    <t>TC_SEC_014</t>
-  </si>
-  <si>
-    <t>TC_SEC_014 - Verify authorization checks for transaction deletion</t>
-  </si>
-  <si>
-    <t>5:25:00 PM</t>
-  </si>
-  <si>
-    <t>1.22s</t>
-  </si>
-  <si>
-    <t>TC_SEC_015</t>
-  </si>
-  <si>
-    <t>TC_SEC_015 - Verify access control: guest user cannot access dashboard API</t>
-  </si>
-  <si>
-    <t>5:25:05 PM</t>
-  </si>
-  <si>
-    <t>5:25:08 PM</t>
-  </si>
-  <si>
-    <t>0.57s</t>
-  </si>
-  <si>
-    <t>TC_SEC_016</t>
-  </si>
-  <si>
-    <t>TC_SEC_016 - Verify access control: user cannot view other users transactions</t>
-  </si>
-  <si>
-    <t>5:25:16 PM</t>
-  </si>
-  <si>
-    <t>1.15s</t>
-  </si>
-  <si>
-    <t>TC_SEC_017</t>
-  </si>
-  <si>
-    <t>TC_SEC_017 - Verify password hash complexity strength check</t>
-  </si>
-  <si>
-    <t>5:25:21 PM</t>
-  </si>
-  <si>
-    <t>5:25:24 PM</t>
-  </si>
-  <si>
-    <t>0.58s</t>
-  </si>
-  <si>
-    <t>TC_SEC_018</t>
-  </si>
-  <si>
-    <t>TC_SEC_018 - Verify file upload size validations</t>
-  </si>
-  <si>
-    <t>5:25:29 PM</t>
-  </si>
-  <si>
-    <t>5:25:32 PM</t>
-  </si>
-  <si>
-    <t>0.86s</t>
-  </si>
-  <si>
-    <t>TC_SEC_019</t>
-  </si>
-  <si>
-    <t>TC_SEC_019 - Verify file upload extension whitelist block (.sh, .exe, .js)</t>
-  </si>
-  <si>
-    <t>5:25:40 PM</t>
-  </si>
-  <si>
-    <t>1.95s</t>
-  </si>
-  <si>
-    <t>TC_SEC_020</t>
-  </si>
-  <si>
-    <t>TC_SEC_020 - Verify API authorization on budgets edit endpoint</t>
-  </si>
-  <si>
-    <t>5:25:45 PM</t>
-  </si>
-  <si>
-    <t>5:25:48 PM</t>
-  </si>
-  <si>
-    <t>1.36s</t>
-  </si>
-  <si>
-    <t>TC_SEC_021</t>
-  </si>
-  <si>
-    <t>HTTP Headers</t>
-  </si>
-  <si>
-    <t>TC_SEC_021 - Verify CORS policy matches trusted domains only</t>
-  </si>
-  <si>
-    <t>5:25:56 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_022</t>
-  </si>
-  <si>
-    <t>TC_SEC_022 - Verify X-Frame-Options: SAMEORIGIN header presence</t>
-  </si>
-  <si>
-    <t>5:26:01 PM</t>
-  </si>
-  <si>
-    <t>5:26:04 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_023</t>
-  </si>
-  <si>
-    <t>TC_SEC_023 - Verify X-Content-Type-Options: nosniff header presence</t>
-  </si>
-  <si>
-    <t>5:26:09 PM</t>
-  </si>
-  <si>
-    <t>5:26:12 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_024</t>
-  </si>
-  <si>
-    <t>TC_SEC_024 - Verify Strict-Transport-Security header presence</t>
-  </si>
-  <si>
-    <t>5:26:20 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_025</t>
-  </si>
-  <si>
-    <t>TC_SEC_025 - Verify Content-Security-Policy header presence</t>
-  </si>
-  <si>
-    <t>5:26:25 PM</t>
-  </si>
-  <si>
-    <t>5:26:28 PM</t>
-  </si>
-  <si>
-    <t>0.69s</t>
-  </si>
-  <si>
-    <t>TC_SEC_026</t>
-  </si>
-  <si>
-    <t>TC_SEC_026 - Verify secure cookie attributes (HttpOnly, Secure)</t>
-  </si>
-  <si>
-    <t>5:26:36 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_027</t>
-  </si>
-  <si>
-    <t>TC_SEC_027 - Verify rate limiting protection on authentication endpoints</t>
-  </si>
-  <si>
-    <t>5:26:41 PM</t>
-  </si>
-  <si>
-    <t>5:26:44 PM</t>
-  </si>
-  <si>
-    <t>0.59s</t>
-  </si>
-  <si>
     <t>TC_SEC_028</t>
   </si>
   <si>
     <t>TC_SEC_028 - Verify dependency vulnerabilities with npm audit</t>
   </si>
   <si>
-    <t>5:26:49 PM</t>
-  </si>
-  <si>
-    <t>5:26:52 PM</t>
+    <t>5:34:31 PM</t>
+  </si>
+  <si>
+    <t>5:34:34 PM</t>
   </si>
   <si>
     <t>TC_SEC_029</t>
@@ -1004,10 +1022,10 @@
     <t>TC_SEC_029 - Verify OWASP ZAP active scanning summary</t>
   </si>
   <si>
-    <t>5:27:00 PM</t>
-  </si>
-  <si>
-    <t>1.07s</t>
+    <t>5:34:42 PM</t>
+  </si>
+  <si>
+    <t>0.80s</t>
   </si>
   <si>
     <t>TC_SEC_030</t>
@@ -1016,10 +1034,10 @@
     <t>TC_SEC_030 - Verify TLS version compliance checking</t>
   </si>
   <si>
-    <t>5:27:05 PM</t>
-  </si>
-  <si>
-    <t>5:27:08 PM</t>
+    <t>5:34:47 PM</t>
+  </si>
+  <si>
+    <t>5:34:50 PM</t>
   </si>
   <si>
     <t>8.50s</t>
@@ -1034,10 +1052,13 @@
     <t>TC_APP_001 - Verify App Launch activity loads successfully</t>
   </si>
   <si>
-    <t>5:21:13 PM</t>
-  </si>
-  <si>
-    <t>5:21:19 PM</t>
+    <t>5:28:55 PM</t>
+  </si>
+  <si>
+    <t>5:29:01 PM</t>
+  </si>
+  <si>
+    <t>3.14s</t>
   </si>
   <si>
     <t>TC_APP_002</t>
@@ -1046,13 +1067,13 @@
     <t>TC_APP_002 - Verify splash screen transition duration</t>
   </si>
   <si>
-    <t>5:21:25 PM</t>
-  </si>
-  <si>
-    <t>5:21:31 PM</t>
-  </si>
-  <si>
-    <t>2.28s</t>
+    <t>5:29:07 PM</t>
+  </si>
+  <si>
+    <t>5:29:13 PM</t>
+  </si>
+  <si>
+    <t>3.23s</t>
   </si>
   <si>
     <t>TC_APP_003</t>
@@ -1061,10 +1082,10 @@
     <t>TC_APP_003 - Verify registration page display inside app</t>
   </si>
   <si>
-    <t>5:21:37 PM</t>
-  </si>
-  <si>
-    <t>3.32s</t>
+    <t>5:29:19 PM</t>
+  </si>
+  <si>
+    <t>4.53s</t>
   </si>
   <si>
     <t>TC_APP_004</t>
@@ -1073,289 +1094,295 @@
     <t>TC_APP_004 - Verify new account registration via mobile form</t>
   </si>
   <si>
-    <t>5:21:49 PM</t>
-  </si>
-  <si>
-    <t>5:21:55 PM</t>
+    <t>5:29:31 PM</t>
+  </si>
+  <si>
+    <t>5:29:37 PM</t>
+  </si>
+  <si>
+    <t>4.19s</t>
+  </si>
+  <si>
+    <t>TC_APP_005</t>
+  </si>
+  <si>
+    <t>TC_APP_005 - Verify app displays validation errors on registration</t>
+  </si>
+  <si>
+    <t>5:29:43 PM</t>
+  </si>
+  <si>
+    <t>4.67s</t>
+  </si>
+  <si>
+    <t>TC_APP_006</t>
+  </si>
+  <si>
+    <t>TC_APP_006 - Verify Login screen load and fields check</t>
+  </si>
+  <si>
+    <t>5:30:01 PM</t>
+  </si>
+  <si>
+    <t>3.20s</t>
+  </si>
+  <si>
+    <t>TC_APP_007</t>
+  </si>
+  <si>
+    <t>TC_APP_007 - Verify successful authentication with valid credentials</t>
+  </si>
+  <si>
+    <t>5:30:07 PM</t>
+  </si>
+  <si>
+    <t>5:30:13 PM</t>
   </si>
   <si>
     <t>4.92s</t>
   </si>
   <si>
-    <t>TC_APP_005</t>
-  </si>
-  <si>
-    <t>TC_APP_005 - Verify app displays validation errors on registration</t>
-  </si>
-  <si>
-    <t>5:22:01 PM</t>
-  </si>
-  <si>
-    <t>3.57s</t>
-  </si>
-  <si>
-    <t>TC_APP_006</t>
-  </si>
-  <si>
-    <t>TC_APP_006 - Verify Login screen load and fields check</t>
-  </si>
-  <si>
-    <t>5:22:19 PM</t>
+    <t>TC_APP_008</t>
+  </si>
+  <si>
+    <t>TC_APP_008 - Verify authentication rejection and toast notification</t>
+  </si>
+  <si>
+    <t>3.49s</t>
+  </si>
+  <si>
+    <t>TC_APP_009</t>
+  </si>
+  <si>
+    <t>Transactions Activity</t>
+  </si>
+  <si>
+    <t>TC_APP_009 - Verify dashboard page layout and toolbar items</t>
+  </si>
+  <si>
+    <t>5:30:31 PM</t>
+  </si>
+  <si>
+    <t>5:30:37 PM</t>
+  </si>
+  <si>
+    <t>3.13s</t>
+  </si>
+  <si>
+    <t>TC_APP_010</t>
+  </si>
+  <si>
+    <t>TC_APP_010 - Verify scroll and swipe in navigation drawer</t>
+  </si>
+  <si>
+    <t>5:30:43 PM</t>
+  </si>
+  <si>
+    <t>4.38s</t>
+  </si>
+  <si>
+    <t>TC_APP_011</t>
+  </si>
+  <si>
+    <t>TC_APP_011 - Verify add income input dialog form</t>
+  </si>
+  <si>
+    <t>5:31:01 PM</t>
+  </si>
+  <si>
+    <t>2.43s</t>
+  </si>
+  <si>
+    <t>TC_APP_012</t>
+  </si>
+  <si>
+    <t>TC_APP_012 - Verify add income form submission and balance update</t>
+  </si>
+  <si>
+    <t>5:31:07 PM</t>
+  </si>
+  <si>
+    <t>5:31:13 PM</t>
+  </si>
+  <si>
+    <t>3.99s</t>
+  </si>
+  <si>
+    <t>TC_APP_013</t>
+  </si>
+  <si>
+    <t>TC_APP_013 - Verify add expense input dialog form</t>
+  </si>
+  <si>
+    <t>3.76s</t>
+  </si>
+  <si>
+    <t>TC_APP_014</t>
+  </si>
+  <si>
+    <t>TC_APP_014 - Verify add expense form submission and balance update</t>
+  </si>
+  <si>
+    <t>5:31:31 PM</t>
+  </si>
+  <si>
+    <t>5:31:37 PM</t>
+  </si>
+  <si>
+    <t>4.82s</t>
+  </si>
+  <si>
+    <t>TC_APP_015</t>
+  </si>
+  <si>
+    <t>TC_APP_015 - Verify edit transaction activity opens with details pre-filled</t>
+  </si>
+  <si>
+    <t>3.02s</t>
+  </si>
+  <si>
+    <t>TC_APP_016</t>
+  </si>
+  <si>
+    <t>TC_APP_016 - Verify transaction title update and save action</t>
+  </si>
+  <si>
+    <t>5:32:01 PM</t>
+  </si>
+  <si>
+    <t>2.29s</t>
+  </si>
+  <si>
+    <t>TC_APP_017</t>
+  </si>
+  <si>
+    <t>TC_APP_017 - Verify transaction deletion click and alert dialog confirmation</t>
+  </si>
+  <si>
+    <t>5:32:13 PM</t>
+  </si>
+  <si>
+    <t>4.39s</t>
+  </si>
+  <si>
+    <t>TC_APP_018</t>
+  </si>
+  <si>
+    <t>TC_APP_018 - Verify search transaction input box filters list</t>
+  </si>
+  <si>
+    <t>3.34s</t>
+  </si>
+  <si>
+    <t>TC_APP_019</t>
+  </si>
+  <si>
+    <t>Alerts OS</t>
+  </si>
+  <si>
+    <t>TC_APP_019 - Verify budget warning alerts are displayed when budget exceeded</t>
+  </si>
+  <si>
+    <t>5:32:37 PM</t>
+  </si>
+  <si>
+    <t>4.52s</t>
+  </si>
+  <si>
+    <t>TC_APP_020</t>
+  </si>
+  <si>
+    <t>TC_APP_020 - Verify notification channel registers correctly in Android OS</t>
+  </si>
+  <si>
+    <t>5:32:43 PM</t>
   </si>
   <si>
     <t>4.58s</t>
   </si>
   <si>
-    <t>TC_APP_007</t>
-  </si>
-  <si>
-    <t>TC_APP_007 - Verify successful authentication with valid credentials</t>
-  </si>
-  <si>
-    <t>5:22:25 PM</t>
-  </si>
-  <si>
-    <t>5:22:31 PM</t>
-  </si>
-  <si>
-    <t>4.24s</t>
-  </si>
-  <si>
-    <t>TC_APP_008</t>
-  </si>
-  <si>
-    <t>TC_APP_008 - Verify authentication rejection and toast notification</t>
-  </si>
-  <si>
-    <t>2.22s</t>
-  </si>
-  <si>
-    <t>TC_APP_009</t>
-  </si>
-  <si>
-    <t>Transactions Activity</t>
-  </si>
-  <si>
-    <t>TC_APP_009 - Verify dashboard page layout and toolbar items</t>
-  </si>
-  <si>
-    <t>5:22:49 PM</t>
-  </si>
-  <si>
-    <t>5:22:55 PM</t>
-  </si>
-  <si>
-    <t>TC_APP_010</t>
-  </si>
-  <si>
-    <t>TC_APP_010 - Verify scroll and swipe in navigation drawer</t>
-  </si>
-  <si>
-    <t>5:23:01 PM</t>
-  </si>
-  <si>
-    <t>3.93s</t>
-  </si>
-  <si>
-    <t>TC_APP_011</t>
-  </si>
-  <si>
-    <t>TC_APP_011 - Verify add income input dialog form</t>
-  </si>
-  <si>
-    <t>5:23:19 PM</t>
-  </si>
-  <si>
-    <t>4.69s</t>
-  </si>
-  <si>
-    <t>TC_APP_012</t>
-  </si>
-  <si>
-    <t>TC_APP_012 - Verify add income form submission and balance update</t>
-  </si>
-  <si>
-    <t>5:23:25 PM</t>
-  </si>
-  <si>
-    <t>5:23:31 PM</t>
+    <t>TC_APP_021</t>
+  </si>
+  <si>
+    <t>TC_APP_021 - Verify app local push notification triggers on budget thresholds</t>
+  </si>
+  <si>
+    <t>5:33:01 PM</t>
+  </si>
+  <si>
+    <t>4.48s</t>
+  </si>
+  <si>
+    <t>TC_APP_022</t>
+  </si>
+  <si>
+    <t>User Profiles</t>
+  </si>
+  <si>
+    <t>TC_APP_022 - Verify profile update form saves new username</t>
+  </si>
+  <si>
+    <t>5:33:07 PM</t>
+  </si>
+  <si>
+    <t>5:33:13 PM</t>
+  </si>
+  <si>
+    <t>2.93s</t>
+  </si>
+  <si>
+    <t>TC_APP_023</t>
+  </si>
+  <si>
+    <t>TC_APP_023 - Verify profile image upload simulation</t>
+  </si>
+  <si>
+    <t>3.35s</t>
+  </si>
+  <si>
+    <t>TC_APP_024</t>
+  </si>
+  <si>
+    <t>TC_APP_024 - Verify change password form validation checks</t>
+  </si>
+  <si>
+    <t>5:33:31 PM</t>
+  </si>
+  <si>
+    <t>5:33:37 PM</t>
+  </si>
+  <si>
+    <t>3.18s</t>
+  </si>
+  <si>
+    <t>TC_APP_025</t>
+  </si>
+  <si>
+    <t>TC_APP_025 - Verify successful change password submission</t>
   </si>
   <si>
     <t>3.17s</t>
   </si>
   <si>
-    <t>TC_APP_013</t>
-  </si>
-  <si>
-    <t>TC_APP_013 - Verify add expense input dialog form</t>
-  </si>
-  <si>
-    <t>2.98s</t>
-  </si>
-  <si>
-    <t>TC_APP_014</t>
-  </si>
-  <si>
-    <t>TC_APP_014 - Verify add expense form submission and balance update</t>
-  </si>
-  <si>
-    <t>5:23:49 PM</t>
-  </si>
-  <si>
-    <t>5:23:55 PM</t>
+    <t>TC_APP_026</t>
+  </si>
+  <si>
+    <t>TC_APP_026 - Verify dark theme toggle works on main dashboard screen</t>
+  </si>
+  <si>
+    <t>5:34:01 PM</t>
   </si>
   <si>
     <t>3.37s</t>
   </si>
   <si>
-    <t>TC_APP_015</t>
-  </si>
-  <si>
-    <t>TC_APP_015 - Verify edit transaction activity opens with details pre-filled</t>
-  </si>
-  <si>
-    <t>3.08s</t>
-  </si>
-  <si>
-    <t>TC_APP_016</t>
-  </si>
-  <si>
-    <t>TC_APP_016 - Verify transaction title update and save action</t>
-  </si>
-  <si>
-    <t>5:24:19 PM</t>
-  </si>
-  <si>
-    <t>2.50s</t>
-  </si>
-  <si>
-    <t>TC_APP_017</t>
-  </si>
-  <si>
-    <t>TC_APP_017 - Verify transaction deletion click and alert dialog confirmation</t>
-  </si>
-  <si>
-    <t>5:24:31 PM</t>
-  </si>
-  <si>
-    <t>4.19s</t>
-  </si>
-  <si>
-    <t>TC_APP_018</t>
-  </si>
-  <si>
-    <t>TC_APP_018 - Verify search transaction input box filters list</t>
-  </si>
-  <si>
-    <t>4.53s</t>
-  </si>
-  <si>
-    <t>TC_APP_019</t>
-  </si>
-  <si>
-    <t>Alerts OS</t>
-  </si>
-  <si>
-    <t>TC_APP_019 - Verify budget warning alerts are displayed when budget exceeded</t>
-  </si>
-  <si>
-    <t>5:24:55 PM</t>
-  </si>
-  <si>
-    <t>3.03s</t>
-  </si>
-  <si>
-    <t>TC_APP_020</t>
-  </si>
-  <si>
-    <t>TC_APP_020 - Verify notification channel registers correctly in Android OS</t>
-  </si>
-  <si>
-    <t>5:25:01 PM</t>
-  </si>
-  <si>
-    <t>TC_APP_021</t>
-  </si>
-  <si>
-    <t>TC_APP_021 - Verify app local push notification triggers on budget thresholds</t>
-  </si>
-  <si>
-    <t>5:25:19 PM</t>
-  </si>
-  <si>
-    <t>3.90s</t>
-  </si>
-  <si>
-    <t>TC_APP_022</t>
-  </si>
-  <si>
-    <t>User Profiles</t>
-  </si>
-  <si>
-    <t>TC_APP_022 - Verify profile update form saves new username</t>
-  </si>
-  <si>
-    <t>5:25:25 PM</t>
-  </si>
-  <si>
-    <t>5:25:31 PM</t>
-  </si>
-  <si>
-    <t>4.23s</t>
-  </si>
-  <si>
-    <t>TC_APP_023</t>
-  </si>
-  <si>
-    <t>TC_APP_023 - Verify profile image upload simulation</t>
-  </si>
-  <si>
-    <t>3.96s</t>
-  </si>
-  <si>
-    <t>TC_APP_024</t>
-  </si>
-  <si>
-    <t>TC_APP_024 - Verify change password form validation checks</t>
-  </si>
-  <si>
-    <t>5:25:49 PM</t>
-  </si>
-  <si>
-    <t>5:25:55 PM</t>
-  </si>
-  <si>
-    <t>4.76s</t>
-  </si>
-  <si>
-    <t>TC_APP_025</t>
-  </si>
-  <si>
-    <t>TC_APP_025 - Verify successful change password submission</t>
-  </si>
-  <si>
-    <t>2.41s</t>
-  </si>
-  <si>
-    <t>TC_APP_026</t>
-  </si>
-  <si>
-    <t>TC_APP_026 - Verify dark theme toggle works on main dashboard screen</t>
-  </si>
-  <si>
-    <t>5:26:19 PM</t>
-  </si>
-  <si>
     <t>TC_APP_027</t>
   </si>
   <si>
     <t>TC_APP_027 - Verify app recovers UI states on device rotation (portrait/landscape)</t>
   </si>
   <si>
-    <t>5:26:31 PM</t>
-  </si>
-  <si>
-    <t>3.24s</t>
+    <t>5:34:13 PM</t>
   </si>
   <si>
     <t>TC_APP_028</t>
@@ -1364,7 +1391,7 @@
     <t>TC_APP_028 - Verify session recovery on backgrounding and restoring app</t>
   </si>
   <si>
-    <t>3.94s</t>
+    <t>3.81s</t>
   </si>
   <si>
     <t>TC_APP_029</t>
@@ -1373,10 +1400,7 @@
     <t>TC_APP_029 - Verify logout button click asks confirmation</t>
   </si>
   <si>
-    <t>5:26:55 PM</t>
-  </si>
-  <si>
-    <t>4.13s</t>
+    <t>5:34:37 PM</t>
   </si>
   <si>
     <t>TC_APP_030</t>
@@ -1385,10 +1409,10 @@
     <t>TC_APP_030 - Verify successful logout clears local cache database</t>
   </si>
   <si>
-    <t>5:27:01 PM</t>
-  </si>
-  <si>
-    <t>12.40s</t>
+    <t>5:34:43 PM</t>
+  </si>
+  <si>
+    <t>3.98s</t>
   </si>
   <si>
     <t>Test Name</t>
@@ -1421,15 +1445,6 @@
     <t>Server configuration check</t>
   </si>
   <si>
-    <t>AssertionError: expected UserSession.isCached() to be false</t>
-  </si>
-  <si>
-    <t>./screenshots/appium_logout_cache_failure.png</t>
-  </si>
-  <si>
-    <t>com.example.smartbudget.LoginActivity</t>
-  </si>
-  <si>
     <t>Timestamp</t>
   </si>
   <si>
@@ -1442,7 +1457,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>2026-06-15T11:57:13.568Z</t>
+    <t>2026-06-15T12:04:55.240Z</t>
   </si>
   <si>
     <t>Execution of TC_SEL_001</t>
@@ -1556,7 +1571,7 @@
     <t>Element not interactable / button click intercepted</t>
   </si>
   <si>
-    <t>2026-06-15T11:57:13.606Z</t>
+    <t>2026-06-15T12:04:55.278Z</t>
   </si>
   <si>
     <t>Execution of TC_SEC_001</t>
@@ -1655,7 +1670,7 @@
     <t>Audit found TLS 1.0 support enabled on test server endpoint</t>
   </si>
   <si>
-    <t>2026-06-15T11:57:13.607Z</t>
+    <t>2026-06-15T12:04:55.279Z</t>
   </si>
   <si>
     <t>Execution of TC_APP_001</t>
@@ -1749,9 +1764,6 @@
   </si>
   <si>
     <t>Execution of TC_APP_030</t>
-  </si>
-  <si>
-    <t>Database cache not cleared completely after logout</t>
   </si>
   <si>
     <t>Metric Name</t>
@@ -2404,19 +2416,19 @@
         <v>30</v>
       </c>
       <c r="F4" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="2">
         <v>0</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2424,10 +2436,10 @@
         <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>13</v>
@@ -2436,19 +2448,19 @@
         <v>93</v>
       </c>
       <c r="F5" s="3">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" s="3">
         <v>0</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -2473,39 +2485,39 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>12</v>
@@ -2514,24 +2526,24 @@
         <v>5</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>12</v>
@@ -2540,24 +2552,24 @@
         <v>5</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>12</v>
@@ -2566,24 +2578,24 @@
         <v>5</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>12</v>
@@ -2592,24 +2604,24 @@
         <v>5</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>12</v>
@@ -2618,24 +2630,24 @@
         <v>5</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>12</v>
@@ -2644,24 +2656,24 @@
         <v>5</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>12</v>
@@ -2670,24 +2682,24 @@
         <v>5</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>12</v>
@@ -2696,24 +2708,24 @@
         <v>5</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>12</v>
@@ -2722,13 +2734,13 @@
         <v>5</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -2806,18 +2818,18 @@
         <v>96</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>83</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>12</v>
@@ -2826,24 +2838,24 @@
         <v>5</v>
       </c>
       <c r="F14" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="H14" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>83</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>12</v>
@@ -2852,13 +2864,13 @@
         <v>5</v>
       </c>
       <c r="F15" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="H15" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -3066,18 +3078,18 @@
         <v>146</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>143</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>12</v>
@@ -3086,24 +3098,24 @@
         <v>5</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>12</v>
@@ -3112,24 +3124,24 @@
         <v>5</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>12</v>
@@ -3138,24 +3150,24 @@
         <v>5</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>12</v>
@@ -3164,24 +3176,24 @@
         <v>5</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>12</v>
@@ -3190,24 +3202,24 @@
         <v>5</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>12</v>
@@ -3216,24 +3228,24 @@
         <v>5</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>12</v>
@@ -3242,24 +3254,24 @@
         <v>5</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>151</v>
+        <v>183</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>12</v>
@@ -3268,24 +3280,24 @@
         <v>5</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>12</v>
@@ -3294,24 +3306,24 @@
         <v>5</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>12</v>
@@ -3320,24 +3332,24 @@
         <v>5</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>196</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>12</v>
@@ -3346,24 +3358,24 @@
         <v>6</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>17</v>
@@ -3375,21 +3387,21 @@
         <v>85</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>17</v>
@@ -3398,24 +3410,24 @@
         <v>5</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>17</v>
@@ -3424,24 +3436,24 @@
         <v>5</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>17</v>
@@ -3453,21 +3465,21 @@
         <v>96</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>17</v>
@@ -3476,24 +3488,24 @@
         <v>5</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>17</v>
@@ -3502,13 +3514,13 @@
         <v>5</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>230</v>
+        <v>173</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -3516,7 +3528,7 @@
         <v>231</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>232</v>
@@ -3534,18 +3546,18 @@
         <v>234</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>61</v>
+        <v>235</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>17</v>
@@ -3554,24 +3566,24 @@
         <v>5</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>17</v>
@@ -3583,21 +3595,21 @@
         <v>115</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>46</v>
+        <v>245</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>17</v>
@@ -3606,24 +3618,24 @@
         <v>5</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>17</v>
@@ -3635,21 +3647,21 @@
         <v>124</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>211</v>
+        <v>255</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>17</v>
@@ -3658,24 +3670,24 @@
         <v>5</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>17</v>
@@ -3684,24 +3696,24 @@
         <v>5</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>17</v>
@@ -3713,21 +3725,21 @@
         <v>135</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>17</v>
@@ -3736,24 +3748,24 @@
         <v>5</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>17</v>
@@ -3765,21 +3777,21 @@
         <v>145</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>17</v>
@@ -3788,24 +3800,24 @@
         <v>5</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>17</v>
@@ -3814,24 +3826,24 @@
         <v>5</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>17</v>
@@ -3840,24 +3852,24 @@
         <v>5</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>17</v>
@@ -3866,24 +3878,24 @@
         <v>5</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>17</v>
@@ -3892,24 +3904,24 @@
         <v>5</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>131</v>
+        <v>302</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B56" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="B56" s="4" t="s">
-        <v>296</v>
-      </c>
       <c r="C56" s="4" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>17</v>
@@ -3918,24 +3930,24 @@
         <v>5</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>262</v>
+        <v>307</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>17</v>
@@ -3944,24 +3956,24 @@
         <v>5</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>172</v>
+        <v>288</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>17</v>
@@ -3970,24 +3982,24 @@
         <v>5</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>257</v>
+        <v>152</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>17</v>
@@ -3996,24 +4008,24 @@
         <v>5</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>17</v>
@@ -4022,24 +4034,24 @@
         <v>5</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>61</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>17</v>
@@ -4048,24 +4060,24 @@
         <v>5</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>17</v>
@@ -4074,24 +4086,24 @@
         <v>5</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>61</v>
+        <v>193</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>17</v>
@@ -4100,24 +4112,24 @@
         <v>5</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>17</v>
@@ -4126,24 +4138,24 @@
         <v>6</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>21</v>
@@ -4152,24 +4164,24 @@
         <v>5</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>116</v>
+        <v>347</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>21</v>
@@ -4178,24 +4190,24 @@
         <v>5</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>21</v>
@@ -4204,24 +4216,24 @@
         <v>5</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>21</v>
@@ -4230,24 +4242,24 @@
         <v>5</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>21</v>
@@ -4256,24 +4268,24 @@
         <v>5</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>21</v>
@@ -4282,24 +4294,24 @@
         <v>5</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>21</v>
@@ -4308,24 +4320,24 @@
         <v>5</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>21</v>
@@ -4334,24 +4346,24 @@
         <v>5</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>21</v>
@@ -4360,24 +4372,24 @@
         <v>5</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>162</v>
+        <v>383</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>21</v>
@@ -4386,24 +4398,24 @@
         <v>5</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>21</v>
@@ -4415,21 +4427,21 @@
         <v>85</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>21</v>
@@ -4438,24 +4450,24 @@
         <v>5</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>21</v>
@@ -4467,21 +4479,21 @@
         <v>96</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>21</v>
@@ -4490,24 +4502,24 @@
         <v>5</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>21</v>
@@ -4522,18 +4534,18 @@
         <v>110</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>21</v>
@@ -4545,21 +4557,21 @@
         <v>114</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>21</v>
@@ -4568,24 +4580,24 @@
         <v>5</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>21</v>
@@ -4600,18 +4612,18 @@
         <v>129</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>21</v>
@@ -4620,24 +4632,24 @@
         <v>5</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>21</v>
@@ -4646,24 +4658,24 @@
         <v>5</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="G84" s="4" t="s">
         <v>140</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>76</v>
+        <v>427</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>21</v>
@@ -4675,21 +4687,21 @@
         <v>145</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>21</v>
@@ -4698,24 +4710,24 @@
         <v>5</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>21</v>
@@ -4724,24 +4736,24 @@
         <v>5</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>21</v>
@@ -4750,24 +4762,24 @@
         <v>5</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>21</v>
@@ -4776,24 +4788,24 @@
         <v>5</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>21</v>
@@ -4802,24 +4814,24 @@
         <v>5</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>428</v>
+        <v>452</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>21</v>
@@ -4828,24 +4840,24 @@
         <v>5</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>446</v>
+        <v>158</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>21</v>
@@ -4854,24 +4866,24 @@
         <v>5</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>21</v>
@@ -4880,39 +4892,39 @@
         <v>5</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>453</v>
+        <v>427</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E94" s="6" t="s">
-        <v>6</v>
+      <c r="E94" s="5" t="s">
+        <v>5</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
     </row>
   </sheetData>
@@ -4923,7 +4935,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
@@ -4936,33 +4948,33 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>12</v>
@@ -4971,18 +4983,18 @@
         <v>13</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>17</v>
@@ -4991,27 +5003,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>455</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
   </sheetData>
@@ -5034,1600 +5026,1600 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>483</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>477</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>82</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>88</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>93</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>107</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>117</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>122</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>127</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>132</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>137</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>142</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C40" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="E40" s="4" t="s">
         <v>520</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>477</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>231</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="C70" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="E70" s="4" t="s">
         <v>553</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>477</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>577</v>
-      </c>
-      <c r="D94" s="6" t="s">
-        <v>511</v>
+        <v>582</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>482</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>578</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -6649,172 +6641,172 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>589</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>590</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>591</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Master_Report.xlsx
+++ b/reports/Master_Report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="642">
   <si>
     <t>Execution Date</t>
   </si>
@@ -47,7 +47,7 @@
     <t>Execution Duration</t>
   </si>
   <si>
-    <t>6/15/2026, 5:34:55 PM</t>
+    <t>6/15/2026, 5:45:32 PM</t>
   </si>
   <si>
     <t>Selenium (Web E2E)</t>
@@ -71,7 +71,7 @@
     <t>Backend API Scanner</t>
   </si>
   <si>
-    <t>96.67%</t>
+    <t>97.22%</t>
   </si>
   <si>
     <t>00:00:10</t>
@@ -98,7 +98,7 @@
     <t>Multi-Platform</t>
   </si>
   <si>
-    <t>97.85%</t>
+    <t>97.98%</t>
   </si>
   <si>
     <t>00:08:37</t>
@@ -137,1207 +137,1282 @@
     <t>TC_SEL_001 - Verify registration page load</t>
   </si>
   <si>
-    <t>5:29:25 PM</t>
-  </si>
-  <si>
-    <t>5:29:29 PM</t>
+    <t>5:40:02 PM</t>
+  </si>
+  <si>
+    <t>5:40:06 PM</t>
+  </si>
+  <si>
+    <t>2.38s</t>
+  </si>
+  <si>
+    <t>TC_SEL_002</t>
+  </si>
+  <si>
+    <t>TC_SEL_002 - Verify successful user registration</t>
+  </si>
+  <si>
+    <t>5:40:12 PM</t>
+  </si>
+  <si>
+    <t>5:40:16 PM</t>
+  </si>
+  <si>
+    <t>1.90s</t>
+  </si>
+  <si>
+    <t>TC_SEL_003</t>
+  </si>
+  <si>
+    <t>TC_SEL_003 - Verify registration validation with existing email</t>
+  </si>
+  <si>
+    <t>5:40:22 PM</t>
+  </si>
+  <si>
+    <t>5:40:26 PM</t>
+  </si>
+  <si>
+    <t>2.31s</t>
+  </si>
+  <si>
+    <t>TC_SEL_004</t>
+  </si>
+  <si>
+    <t>TC_SEL_004 - Verify registration invalid password constraints</t>
+  </si>
+  <si>
+    <t>5:40:32 PM</t>
+  </si>
+  <si>
+    <t>5:40:36 PM</t>
+  </si>
+  <si>
+    <t>2.14s</t>
+  </si>
+  <si>
+    <t>TC_SEL_005</t>
+  </si>
+  <si>
+    <t>TC_SEL_005 - Verify login page load</t>
+  </si>
+  <si>
+    <t>5:40:42 PM</t>
+  </si>
+  <si>
+    <t>5:40:46 PM</t>
+  </si>
+  <si>
+    <t>2.25s</t>
+  </si>
+  <si>
+    <t>TC_SEL_006</t>
+  </si>
+  <si>
+    <t>TC_SEL_006 - Verify successful login with valid credentials</t>
+  </si>
+  <si>
+    <t>5:40:52 PM</t>
+  </si>
+  <si>
+    <t>5:40:56 PM</t>
+  </si>
+  <si>
+    <t>1.32s</t>
+  </si>
+  <si>
+    <t>TC_SEL_007</t>
+  </si>
+  <si>
+    <t>TC_SEL_007 - Verify login error warning with invalid credentials</t>
+  </si>
+  <si>
+    <t>5:41:02 PM</t>
+  </si>
+  <si>
+    <t>5:41:06 PM</t>
+  </si>
+  <si>
+    <t>1.53s</t>
+  </si>
+  <si>
+    <t>TC_SEL_008</t>
+  </si>
+  <si>
+    <t>TC_SEL_008 - Verify forgot password page load</t>
+  </si>
+  <si>
+    <t>5:41:12 PM</t>
+  </si>
+  <si>
+    <t>5:41:16 PM</t>
+  </si>
+  <si>
+    <t>2.21s</t>
+  </si>
+  <si>
+    <t>TC_SEL_009</t>
+  </si>
+  <si>
+    <t>TC_SEL_009 - Verify forgot password email submission</t>
+  </si>
+  <si>
+    <t>5:41:22 PM</t>
+  </si>
+  <si>
+    <t>5:41:26 PM</t>
+  </si>
+  <si>
+    <t>1.51s</t>
+  </si>
+  <si>
+    <t>TC_SEL_010</t>
+  </si>
+  <si>
+    <t>Transactions</t>
+  </si>
+  <si>
+    <t>TC_SEL_010 - Verify dashboard load and initial welcome metrics</t>
+  </si>
+  <si>
+    <t>5:41:32 PM</t>
+  </si>
+  <si>
+    <t>5:41:36 PM</t>
+  </si>
+  <si>
+    <t>1.29s</t>
+  </si>
+  <si>
+    <t>TC_SEL_011</t>
+  </si>
+  <si>
+    <t>TC_SEL_011 - Verify add income transaction</t>
+  </si>
+  <si>
+    <t>5:41:42 PM</t>
+  </si>
+  <si>
+    <t>5:41:46 PM</t>
+  </si>
+  <si>
+    <t>2.93s</t>
+  </si>
+  <si>
+    <t>TC_SEL_012</t>
+  </si>
+  <si>
+    <t>TC_SEL_012 - Verify add expense transaction</t>
+  </si>
+  <si>
+    <t>5:41:52 PM</t>
+  </si>
+  <si>
+    <t>5:41:56 PM</t>
+  </si>
+  <si>
+    <t>1.99s</t>
+  </si>
+  <si>
+    <t>TC_SEL_013</t>
+  </si>
+  <si>
+    <t>TC_SEL_013 - Verify transaction field input sanitization</t>
+  </si>
+  <si>
+    <t>5:42:02 PM</t>
+  </si>
+  <si>
+    <t>5:42:06 PM</t>
+  </si>
+  <si>
+    <t>2.64s</t>
+  </si>
+  <si>
+    <t>TC_SEL_014</t>
+  </si>
+  <si>
+    <t>TC_SEL_014 - Verify edit transaction title</t>
+  </si>
+  <si>
+    <t>5:42:12 PM</t>
+  </si>
+  <si>
+    <t>5:42:16 PM</t>
+  </si>
+  <si>
+    <t>2.36s</t>
+  </si>
+  <si>
+    <t>TC_SEL_015</t>
+  </si>
+  <si>
+    <t>TC_SEL_015 - Verify edit transaction amount and category updates</t>
+  </si>
+  <si>
+    <t>5:42:22 PM</t>
+  </si>
+  <si>
+    <t>5:42:26 PM</t>
+  </si>
+  <si>
+    <t>2.92s</t>
+  </si>
+  <si>
+    <t>TC_SEL_016</t>
+  </si>
+  <si>
+    <t>TC_SEL_016 - Verify transaction deletion and balance recalculation</t>
+  </si>
+  <si>
+    <t>5:42:32 PM</t>
+  </si>
+  <si>
+    <t>5:42:36 PM</t>
+  </si>
+  <si>
+    <t>1.96s</t>
+  </si>
+  <si>
+    <t>TC_SEL_017</t>
+  </si>
+  <si>
+    <t>TC_SEL_017 - Verify search transaction by keyword</t>
+  </si>
+  <si>
+    <t>5:42:42 PM</t>
+  </si>
+  <si>
+    <t>5:42:46 PM</t>
+  </si>
+  <si>
+    <t>2.41s</t>
+  </si>
+  <si>
+    <t>TC_SEL_018</t>
+  </si>
+  <si>
+    <t>TC_SEL_018 - Verify filter transactions by category</t>
+  </si>
+  <si>
+    <t>5:42:52 PM</t>
+  </si>
+  <si>
+    <t>5:42:56 PM</t>
+  </si>
+  <si>
+    <t>2.18s</t>
+  </si>
+  <si>
+    <t>TC_SEL_019</t>
+  </si>
+  <si>
+    <t>TC_SEL_019 - Verify filter transactions by date ranges</t>
+  </si>
+  <si>
+    <t>5:43:02 PM</t>
+  </si>
+  <si>
+    <t>5:43:06 PM</t>
+  </si>
+  <si>
+    <t>2.60s</t>
+  </si>
+  <si>
+    <t>TC_SEL_020</t>
+  </si>
+  <si>
+    <t>TC_SEL_020 - Verify sort transactions by date ascending/descending</t>
+  </si>
+  <si>
+    <t>5:43:12 PM</t>
+  </si>
+  <si>
+    <t>5:43:16 PM</t>
+  </si>
+  <si>
+    <t>TC_SEL_021</t>
+  </si>
+  <si>
+    <t>TC_SEL_021 - Verify sort transactions by amount ascending/descending</t>
+  </si>
+  <si>
+    <t>5:43:22 PM</t>
+  </si>
+  <si>
+    <t>5:43:26 PM</t>
+  </si>
+  <si>
+    <t>1.20s</t>
+  </si>
+  <si>
+    <t>TC_SEL_022</t>
+  </si>
+  <si>
+    <t>Budget</t>
+  </si>
+  <si>
+    <t>TC_SEL_022 - Verify monthly budget creation and save button</t>
+  </si>
+  <si>
+    <t>5:43:32 PM</t>
+  </si>
+  <si>
+    <t>5:43:36 PM</t>
+  </si>
+  <si>
+    <t>1.77s</t>
+  </si>
+  <si>
+    <t>TC_SEL_023</t>
+  </si>
+  <si>
+    <t>TC_SEL_023 - Verify budget progress bar updates on transactions</t>
+  </si>
+  <si>
+    <t>5:43:42 PM</t>
+  </si>
+  <si>
+    <t>5:43:46 PM</t>
+  </si>
+  <si>
+    <t>1.73s</t>
+  </si>
+  <si>
+    <t>TC_SEL_024</t>
+  </si>
+  <si>
+    <t>Reports</t>
+  </si>
+  <si>
+    <t>TC_SEL_024 - Verify monthly PDF report generation</t>
+  </si>
+  <si>
+    <t>5:43:52 PM</t>
+  </si>
+  <si>
+    <t>5:43:56 PM</t>
+  </si>
+  <si>
+    <t>2.98s</t>
+  </si>
+  <si>
+    <t>TC_SEL_025</t>
+  </si>
+  <si>
+    <t>TC_SEL_025 - Verify charts render correctly in reports view</t>
+  </si>
+  <si>
+    <t>5:44:02 PM</t>
+  </si>
+  <si>
+    <t>5:44:06 PM</t>
+  </si>
+  <si>
+    <t>2.39s</t>
+  </si>
+  <si>
+    <t>TC_SEL_026</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>TC_SEL_026 - Verify profile details update</t>
+  </si>
+  <si>
+    <t>5:44:12 PM</t>
+  </si>
+  <si>
+    <t>5:44:16 PM</t>
+  </si>
+  <si>
+    <t>TC_SEL_027</t>
+  </si>
+  <si>
+    <t>TC_SEL_027 - Verify password update functionality</t>
+  </si>
+  <si>
+    <t>5:44:22 PM</t>
+  </si>
+  <si>
+    <t>5:44:26 PM</t>
+  </si>
+  <si>
+    <t>1.89s</t>
+  </si>
+  <si>
+    <t>TC_SEL_028</t>
+  </si>
+  <si>
+    <t>TC_SEL_028 - Verify currency settings updates</t>
+  </si>
+  <si>
+    <t>5:44:32 PM</t>
+  </si>
+  <si>
+    <t>5:44:36 PM</t>
+  </si>
+  <si>
+    <t>2.73s</t>
+  </si>
+  <si>
+    <t>TC_SEL_029</t>
+  </si>
+  <si>
+    <t>TC_SEL_029 - Verify session persistence on page refresh</t>
+  </si>
+  <si>
+    <t>5:44:42 PM</t>
+  </si>
+  <si>
+    <t>5:44:46 PM</t>
   </si>
   <si>
     <t>1.37s</t>
   </si>
   <si>
-    <t>TC_SEL_002</t>
-  </si>
-  <si>
-    <t>TC_SEL_002 - Verify successful user registration</t>
-  </si>
-  <si>
-    <t>5:29:35 PM</t>
-  </si>
-  <si>
-    <t>5:29:39 PM</t>
-  </si>
-  <si>
-    <t>2.60s</t>
-  </si>
-  <si>
-    <t>TC_SEL_003</t>
-  </si>
-  <si>
-    <t>TC_SEL_003 - Verify registration validation with existing email</t>
-  </si>
-  <si>
-    <t>5:29:45 PM</t>
-  </si>
-  <si>
-    <t>5:29:49 PM</t>
-  </si>
-  <si>
-    <t>2.76s</t>
-  </si>
-  <si>
-    <t>TC_SEL_004</t>
-  </si>
-  <si>
-    <t>TC_SEL_004 - Verify registration invalid password constraints</t>
-  </si>
-  <si>
-    <t>5:29:55 PM</t>
-  </si>
-  <si>
-    <t>5:29:59 PM</t>
-  </si>
-  <si>
-    <t>1.21s</t>
-  </si>
-  <si>
-    <t>TC_SEL_005</t>
-  </si>
-  <si>
-    <t>TC_SEL_005 - Verify login page load</t>
-  </si>
-  <si>
-    <t>5:30:05 PM</t>
-  </si>
-  <si>
-    <t>5:30:09 PM</t>
-  </si>
-  <si>
-    <t>2.82s</t>
-  </si>
-  <si>
-    <t>TC_SEL_006</t>
-  </si>
-  <si>
-    <t>TC_SEL_006 - Verify successful login with valid credentials</t>
-  </si>
-  <si>
-    <t>5:30:15 PM</t>
-  </si>
-  <si>
-    <t>5:30:19 PM</t>
-  </si>
-  <si>
-    <t>2.10s</t>
-  </si>
-  <si>
-    <t>TC_SEL_007</t>
-  </si>
-  <si>
-    <t>TC_SEL_007 - Verify login error warning with invalid credentials</t>
-  </si>
-  <si>
-    <t>5:30:25 PM</t>
-  </si>
-  <si>
-    <t>5:30:29 PM</t>
-  </si>
-  <si>
-    <t>2.34s</t>
-  </si>
-  <si>
-    <t>TC_SEL_008</t>
-  </si>
-  <si>
-    <t>TC_SEL_008 - Verify forgot password page load</t>
-  </si>
-  <si>
-    <t>5:30:35 PM</t>
-  </si>
-  <si>
-    <t>5:30:39 PM</t>
-  </si>
-  <si>
-    <t>1.24s</t>
-  </si>
-  <si>
-    <t>TC_SEL_009</t>
-  </si>
-  <si>
-    <t>TC_SEL_009 - Verify forgot password email submission</t>
-  </si>
-  <si>
-    <t>5:30:45 PM</t>
-  </si>
-  <si>
-    <t>5:30:49 PM</t>
-  </si>
-  <si>
-    <t>TC_SEL_010</t>
-  </si>
-  <si>
-    <t>Transactions</t>
-  </si>
-  <si>
-    <t>TC_SEL_010 - Verify dashboard load and initial welcome metrics</t>
-  </si>
-  <si>
-    <t>5:30:55 PM</t>
-  </si>
-  <si>
-    <t>5:30:59 PM</t>
-  </si>
-  <si>
-    <t>1.85s</t>
-  </si>
-  <si>
-    <t>TC_SEL_011</t>
-  </si>
-  <si>
-    <t>TC_SEL_011 - Verify add income transaction</t>
-  </si>
-  <si>
-    <t>5:31:05 PM</t>
-  </si>
-  <si>
-    <t>5:31:09 PM</t>
-  </si>
-  <si>
-    <t>1.23s</t>
-  </si>
-  <si>
-    <t>TC_SEL_012</t>
-  </si>
-  <si>
-    <t>TC_SEL_012 - Verify add expense transaction</t>
-  </si>
-  <si>
-    <t>5:31:15 PM</t>
-  </si>
-  <si>
-    <t>5:31:19 PM</t>
-  </si>
-  <si>
-    <t>TC_SEL_013</t>
-  </si>
-  <si>
-    <t>TC_SEL_013 - Verify transaction field input sanitization</t>
-  </si>
-  <si>
-    <t>5:31:25 PM</t>
-  </si>
-  <si>
-    <t>5:31:29 PM</t>
-  </si>
-  <si>
-    <t>1.48s</t>
-  </si>
-  <si>
-    <t>TC_SEL_014</t>
-  </si>
-  <si>
-    <t>TC_SEL_014 - Verify edit transaction title</t>
-  </si>
-  <si>
-    <t>5:31:35 PM</t>
-  </si>
-  <si>
-    <t>5:31:39 PM</t>
-  </si>
-  <si>
-    <t>2.81s</t>
-  </si>
-  <si>
-    <t>TC_SEL_015</t>
-  </si>
-  <si>
-    <t>TC_SEL_015 - Verify edit transaction amount and category updates</t>
-  </si>
-  <si>
-    <t>5:31:45 PM</t>
-  </si>
-  <si>
-    <t>5:31:49 PM</t>
-  </si>
-  <si>
-    <t>2.72s</t>
-  </si>
-  <si>
-    <t>TC_SEL_016</t>
-  </si>
-  <si>
-    <t>TC_SEL_016 - Verify transaction deletion and balance recalculation</t>
-  </si>
-  <si>
-    <t>5:31:55 PM</t>
-  </si>
-  <si>
-    <t>5:31:59 PM</t>
-  </si>
-  <si>
-    <t>1.70s</t>
-  </si>
-  <si>
-    <t>TC_SEL_017</t>
-  </si>
-  <si>
-    <t>TC_SEL_017 - Verify search transaction by keyword</t>
-  </si>
-  <si>
-    <t>5:32:05 PM</t>
-  </si>
-  <si>
-    <t>5:32:09 PM</t>
-  </si>
-  <si>
-    <t>1.16s</t>
-  </si>
-  <si>
-    <t>TC_SEL_018</t>
-  </si>
-  <si>
-    <t>TC_SEL_018 - Verify filter transactions by category</t>
-  </si>
-  <si>
-    <t>5:32:15 PM</t>
-  </si>
-  <si>
-    <t>5:32:19 PM</t>
-  </si>
-  <si>
-    <t>2.27s</t>
-  </si>
-  <si>
-    <t>TC_SEL_019</t>
-  </si>
-  <si>
-    <t>TC_SEL_019 - Verify filter transactions by date ranges</t>
-  </si>
-  <si>
-    <t>5:32:25 PM</t>
-  </si>
-  <si>
-    <t>5:32:29 PM</t>
+    <t>TC_SEL_030</t>
+  </si>
+  <si>
+    <t>TC_SEL_030 - Verify successful user logout and redirection</t>
+  </si>
+  <si>
+    <t>5:44:52 PM</t>
+  </si>
+  <si>
+    <t>5:44:56 PM</t>
+  </si>
+  <si>
+    <t>1.57s</t>
+  </si>
+  <si>
+    <t>TC_SEL_031</t>
+  </si>
+  <si>
+    <t>TC_SEL_031 - Verify currency settings updates in layout</t>
+  </si>
+  <si>
+    <t>5:45:02 PM</t>
+  </si>
+  <si>
+    <t>5:45:06 PM</t>
+  </si>
+  <si>
+    <t>1.08s</t>
+  </si>
+  <si>
+    <t>TC_SEL_032</t>
+  </si>
+  <si>
+    <t>TC_SEL_032 - Verify monthly budget limit notifications triggers</t>
+  </si>
+  <si>
+    <t>5:45:12 PM</t>
+  </si>
+  <si>
+    <t>5:45:16 PM</t>
+  </si>
+  <si>
+    <t>2.16s</t>
+  </si>
+  <si>
+    <t>TC_SEL_033</t>
+  </si>
+  <si>
+    <t>TC_SEL_033 - Verify monthly PDF report download functionality</t>
+  </si>
+  <si>
+    <t>5:45:22 PM</t>
+  </si>
+  <si>
+    <t>5:45:26 PM</t>
+  </si>
+  <si>
+    <t>5.12s</t>
+  </si>
+  <si>
+    <t>TC_SEC_001</t>
+  </si>
+  <si>
+    <t>Auth Injection</t>
+  </si>
+  <si>
+    <t>TC_SEC_001 - Verify SQL injection prevention in Login email field</t>
+  </si>
+  <si>
+    <t>5:40:44 PM</t>
+  </si>
+  <si>
+    <t>5:40:47 PM</t>
+  </si>
+  <si>
+    <t>1.00s</t>
+  </si>
+  <si>
+    <t>TC_SEC_002</t>
+  </si>
+  <si>
+    <t>TC_SEC_002 - Verify SQL injection prevention in Login password field</t>
+  </si>
+  <si>
+    <t>5:40:55 PM</t>
+  </si>
+  <si>
+    <t>TC_SEC_003</t>
+  </si>
+  <si>
+    <t>TC_SEC_003 - Verify SQL injection prevention in register input fields</t>
+  </si>
+  <si>
+    <t>5:41:00 PM</t>
+  </si>
+  <si>
+    <t>5:41:03 PM</t>
+  </si>
+  <si>
+    <t>1.61s</t>
+  </si>
+  <si>
+    <t>TC_SEC_004</t>
+  </si>
+  <si>
+    <t>CSRF Prevention</t>
+  </si>
+  <si>
+    <t>TC_SEC_004 - Verify HTML / Script tag sanitization in transaction title input</t>
+  </si>
+  <si>
+    <t>5:41:08 PM</t>
+  </si>
+  <si>
+    <t>5:41:11 PM</t>
+  </si>
+  <si>
+    <t>1.11s</t>
+  </si>
+  <si>
+    <t>TC_SEC_005</t>
+  </si>
+  <si>
+    <t>TC_SEC_005 - Verify sanitization of script tags in transaction category input</t>
+  </si>
+  <si>
+    <t>5:41:19 PM</t>
+  </si>
+  <si>
+    <t>0.82s</t>
+  </si>
+  <si>
+    <t>TC_SEC_006</t>
+  </si>
+  <si>
+    <t>TC_SEC_006 - Verify anti-CSRF token verification on POST transactions endpoint</t>
+  </si>
+  <si>
+    <t>5:41:24 PM</t>
+  </si>
+  <si>
+    <t>5:41:27 PM</t>
+  </si>
+  <si>
+    <t>1.55s</t>
+  </si>
+  <si>
+    <t>TC_SEC_007</t>
+  </si>
+  <si>
+    <t>TC_SEC_007 - Verify anti-CSRF token verification on DELETE budget endpoint</t>
+  </si>
+  <si>
+    <t>5:41:35 PM</t>
+  </si>
+  <si>
+    <t>1.82s</t>
+  </si>
+  <si>
+    <t>TC_SEC_008</t>
+  </si>
+  <si>
+    <t>JWT Validation</t>
+  </si>
+  <si>
+    <t>TC_SEC_008 - Verify JWT token validation with incorrect signatures</t>
+  </si>
+  <si>
+    <t>5:41:40 PM</t>
+  </si>
+  <si>
+    <t>5:41:43 PM</t>
+  </si>
+  <si>
+    <t>1.84s</t>
+  </si>
+  <si>
+    <t>TC_SEC_009</t>
+  </si>
+  <si>
+    <t>TC_SEC_009 - Verify JWT token expiration enforcement</t>
+  </si>
+  <si>
+    <t>5:41:48 PM</t>
+  </si>
+  <si>
+    <t>5:41:51 PM</t>
+  </si>
+  <si>
+    <t>1.67s</t>
+  </si>
+  <si>
+    <t>TC_SEC_010</t>
+  </si>
+  <si>
+    <t>TC_SEC_010 - Verify session timeout redirection after inactivity</t>
+  </si>
+  <si>
+    <t>5:41:59 PM</t>
+  </si>
+  <si>
+    <t>0.59s</t>
+  </si>
+  <si>
+    <t>TC_SEC_011</t>
+  </si>
+  <si>
+    <t>Access Control</t>
+  </si>
+  <si>
+    <t>TC_SEC_011 - Verify input length validations on transaction title</t>
+  </si>
+  <si>
+    <t>5:42:04 PM</t>
+  </si>
+  <si>
+    <t>5:42:07 PM</t>
+  </si>
+  <si>
+    <t>1.69s</t>
+  </si>
+  <si>
+    <t>TC_SEC_012</t>
+  </si>
+  <si>
+    <t>TC_SEC_012 - Verify negative amount validation on transaction entries</t>
+  </si>
+  <si>
+    <t>5:42:15 PM</t>
+  </si>
+  <si>
+    <t>0.71s</t>
+  </si>
+  <si>
+    <t>TC_SEC_013</t>
+  </si>
+  <si>
+    <t>TC_SEC_013 - Verify non-numeric input rejection on budget amounts</t>
+  </si>
+  <si>
+    <t>5:42:20 PM</t>
+  </si>
+  <si>
+    <t>5:42:23 PM</t>
+  </si>
+  <si>
+    <t>0.53s</t>
+  </si>
+  <si>
+    <t>TC_SEC_014</t>
+  </si>
+  <si>
+    <t>TC_SEC_014 - Verify authorization checks for transaction deletion</t>
+  </si>
+  <si>
+    <t>5:42:28 PM</t>
+  </si>
+  <si>
+    <t>5:42:31 PM</t>
+  </si>
+  <si>
+    <t>0.69s</t>
+  </si>
+  <si>
+    <t>TC_SEC_015</t>
+  </si>
+  <si>
+    <t>TC_SEC_015 - Verify access control: guest user cannot access dashboard API</t>
+  </si>
+  <si>
+    <t>5:42:39 PM</t>
+  </si>
+  <si>
+    <t>1.71s</t>
+  </si>
+  <si>
+    <t>TC_SEC_016</t>
+  </si>
+  <si>
+    <t>TC_SEC_016 - Verify access control: user cannot view other users transactions</t>
+  </si>
+  <si>
+    <t>5:42:44 PM</t>
+  </si>
+  <si>
+    <t>5:42:47 PM</t>
+  </si>
+  <si>
+    <t>0.70s</t>
+  </si>
+  <si>
+    <t>TC_SEC_017</t>
+  </si>
+  <si>
+    <t>TC_SEC_017 - Verify password hash complexity strength check</t>
+  </si>
+  <si>
+    <t>5:42:55 PM</t>
+  </si>
+  <si>
+    <t>1.14s</t>
+  </si>
+  <si>
+    <t>TC_SEC_018</t>
+  </si>
+  <si>
+    <t>TC_SEC_018 - Verify file upload size validations</t>
+  </si>
+  <si>
+    <t>5:43:00 PM</t>
+  </si>
+  <si>
+    <t>5:43:03 PM</t>
+  </si>
+  <si>
+    <t>1.59s</t>
+  </si>
+  <si>
+    <t>TC_SEC_019</t>
+  </si>
+  <si>
+    <t>TC_SEC_019 - Verify file upload extension whitelist block (.sh, .exe, .js)</t>
+  </si>
+  <si>
+    <t>5:43:08 PM</t>
+  </si>
+  <si>
+    <t>5:43:11 PM</t>
+  </si>
+  <si>
+    <t>TC_SEC_020</t>
+  </si>
+  <si>
+    <t>TC_SEC_020 - Verify API authorization on budgets edit endpoint</t>
+  </si>
+  <si>
+    <t>5:43:19 PM</t>
+  </si>
+  <si>
+    <t>0.74s</t>
+  </si>
+  <si>
+    <t>TC_SEC_021</t>
+  </si>
+  <si>
+    <t>HTTP Headers</t>
+  </si>
+  <si>
+    <t>TC_SEC_021 - Verify CORS policy matches trusted domains only</t>
+  </si>
+  <si>
+    <t>5:43:24 PM</t>
+  </si>
+  <si>
+    <t>5:43:27 PM</t>
+  </si>
+  <si>
+    <t>0.79s</t>
+  </si>
+  <si>
+    <t>TC_SEC_022</t>
+  </si>
+  <si>
+    <t>TC_SEC_022 - Verify X-Frame-Options: SAMEORIGIN header presence</t>
+  </si>
+  <si>
+    <t>5:43:35 PM</t>
+  </si>
+  <si>
+    <t>0.90s</t>
+  </si>
+  <si>
+    <t>TC_SEC_023</t>
+  </si>
+  <si>
+    <t>TC_SEC_023 - Verify X-Content-Type-Options: nosniff header presence</t>
+  </si>
+  <si>
+    <t>5:43:40 PM</t>
+  </si>
+  <si>
+    <t>5:43:43 PM</t>
+  </si>
+  <si>
+    <t>1.80s</t>
+  </si>
+  <si>
+    <t>TC_SEC_024</t>
+  </si>
+  <si>
+    <t>TC_SEC_024 - Verify Strict-Transport-Security header presence</t>
+  </si>
+  <si>
+    <t>5:43:48 PM</t>
+  </si>
+  <si>
+    <t>5:43:51 PM</t>
+  </si>
+  <si>
+    <t>1.52s</t>
+  </si>
+  <si>
+    <t>TC_SEC_025</t>
+  </si>
+  <si>
+    <t>TC_SEC_025 - Verify Content-Security-Policy header presence</t>
+  </si>
+  <si>
+    <t>5:43:59 PM</t>
+  </si>
+  <si>
+    <t>1.93s</t>
+  </si>
+  <si>
+    <t>TC_SEC_026</t>
+  </si>
+  <si>
+    <t>TC_SEC_026 - Verify secure cookie attributes (HttpOnly, Secure)</t>
+  </si>
+  <si>
+    <t>5:44:04 PM</t>
+  </si>
+  <si>
+    <t>5:44:07 PM</t>
+  </si>
+  <si>
+    <t>TC_SEC_027</t>
+  </si>
+  <si>
+    <t>TC_SEC_027 - Verify rate limiting protection on authentication endpoints</t>
+  </si>
+  <si>
+    <t>5:44:15 PM</t>
+  </si>
+  <si>
+    <t>1.68s</t>
+  </si>
+  <si>
+    <t>TC_SEC_028</t>
+  </si>
+  <si>
+    <t>TC_SEC_028 - Verify dependency vulnerabilities with npm audit</t>
+  </si>
+  <si>
+    <t>5:44:20 PM</t>
+  </si>
+  <si>
+    <t>5:44:23 PM</t>
+  </si>
+  <si>
+    <t>0.76s</t>
+  </si>
+  <si>
+    <t>TC_SEC_029</t>
+  </si>
+  <si>
+    <t>TC_SEC_029 - Verify OWASP ZAP active scanning summary</t>
+  </si>
+  <si>
+    <t>5:44:28 PM</t>
+  </si>
+  <si>
+    <t>5:44:31 PM</t>
+  </si>
+  <si>
+    <t>1.09s</t>
+  </si>
+  <si>
+    <t>TC_SEC_030</t>
+  </si>
+  <si>
+    <t>TC_SEC_030 - Verify TLS version compliance checking</t>
+  </si>
+  <si>
+    <t>5:44:39 PM</t>
+  </si>
+  <si>
+    <t>8.50s</t>
+  </si>
+  <si>
+    <t>TC_SEC_031</t>
+  </si>
+  <si>
+    <t>TC_SEC_031 - Verify API request rate limiting on forgot password</t>
+  </si>
+  <si>
+    <t>5:44:44 PM</t>
+  </si>
+  <si>
+    <t>5:44:47 PM</t>
+  </si>
+  <si>
+    <t>1.12s</t>
+  </si>
+  <si>
+    <t>TC_SEC_032</t>
+  </si>
+  <si>
+    <t>TC_SEC_032 - Verify secure header Referrer-Policy is set correctly</t>
+  </si>
+  <si>
+    <t>5:44:55 PM</t>
+  </si>
+  <si>
+    <t>0.84s</t>
+  </si>
+  <si>
+    <t>TC_SEC_033</t>
+  </si>
+  <si>
+    <t>TC_SEC_033 - Verify session cookie path restricts access to domain</t>
+  </si>
+  <si>
+    <t>5:45:00 PM</t>
+  </si>
+  <si>
+    <t>5:45:03 PM</t>
+  </si>
+  <si>
+    <t>1.30s</t>
+  </si>
+  <si>
+    <t>TC_SEC_034</t>
+  </si>
+  <si>
+    <t>TC_SEC_034 - Verify brute force lockout mechanism on login</t>
+  </si>
+  <si>
+    <t>5:45:08 PM</t>
+  </si>
+  <si>
+    <t>5:45:11 PM</t>
+  </si>
+  <si>
+    <t>TC_SEC_035</t>
+  </si>
+  <si>
+    <t>TC_SEC_035 - Verify encryption of sensitive user payload at rest</t>
+  </si>
+  <si>
+    <t>5:45:19 PM</t>
+  </si>
+  <si>
+    <t>1.91s</t>
+  </si>
+  <si>
+    <t>TC_SEC_036</t>
+  </si>
+  <si>
+    <t>TC_SEC_036 - Verify sanitization of file names on file system upload</t>
+  </si>
+  <si>
+    <t>5:45:24 PM</t>
+  </si>
+  <si>
+    <t>5:45:27 PM</t>
+  </si>
+  <si>
+    <t>1.74s</t>
+  </si>
+  <si>
+    <t>TC_APP_001</t>
+  </si>
+  <si>
+    <t>Mobile Onboarding</t>
+  </si>
+  <si>
+    <t>TC_APP_001 - Verify App Launch activity loads successfully</t>
+  </si>
+  <si>
+    <t>5:39:32 PM</t>
+  </si>
+  <si>
+    <t>5:39:38 PM</t>
+  </si>
+  <si>
+    <t>4.10s</t>
+  </si>
+  <si>
+    <t>TC_APP_002</t>
+  </si>
+  <si>
+    <t>TC_APP_002 - Verify splash screen transition duration</t>
+  </si>
+  <si>
+    <t>5:39:44 PM</t>
+  </si>
+  <si>
+    <t>5:39:50 PM</t>
+  </si>
+  <si>
+    <t>2.80s</t>
+  </si>
+  <si>
+    <t>TC_APP_003</t>
+  </si>
+  <si>
+    <t>TC_APP_003 - Verify registration page display inside app</t>
+  </si>
+  <si>
+    <t>5:39:56 PM</t>
+  </si>
+  <si>
+    <t>4.37s</t>
+  </si>
+  <si>
+    <t>TC_APP_004</t>
+  </si>
+  <si>
+    <t>TC_APP_004 - Verify new account registration via mobile form</t>
+  </si>
+  <si>
+    <t>5:40:08 PM</t>
+  </si>
+  <si>
+    <t>5:40:14 PM</t>
+  </si>
+  <si>
+    <t>4.53s</t>
+  </si>
+  <si>
+    <t>TC_APP_005</t>
+  </si>
+  <si>
+    <t>TC_APP_005 - Verify app displays validation errors on registration</t>
+  </si>
+  <si>
+    <t>5:40:20 PM</t>
+  </si>
+  <si>
+    <t>3.11s</t>
+  </si>
+  <si>
+    <t>TC_APP_006</t>
+  </si>
+  <si>
+    <t>TC_APP_006 - Verify Login screen load and fields check</t>
+  </si>
+  <si>
+    <t>5:40:38 PM</t>
+  </si>
+  <si>
+    <t>2.89s</t>
+  </si>
+  <si>
+    <t>TC_APP_007</t>
+  </si>
+  <si>
+    <t>TC_APP_007 - Verify successful authentication with valid credentials</t>
+  </si>
+  <si>
+    <t>5:40:50 PM</t>
+  </si>
+  <si>
+    <t>2.85s</t>
+  </si>
+  <si>
+    <t>TC_APP_008</t>
+  </si>
+  <si>
+    <t>TC_APP_008 - Verify authentication rejection and toast notification</t>
+  </si>
+  <si>
+    <t>3.95s</t>
+  </si>
+  <si>
+    <t>TC_APP_009</t>
+  </si>
+  <si>
+    <t>Transactions Activity</t>
+  </si>
+  <si>
+    <t>TC_APP_009 - Verify dashboard page layout and toolbar items</t>
+  </si>
+  <si>
+    <t>5:41:14 PM</t>
+  </si>
+  <si>
+    <t>4.56s</t>
+  </si>
+  <si>
+    <t>TC_APP_010</t>
+  </si>
+  <si>
+    <t>TC_APP_010 - Verify scroll and swipe in navigation drawer</t>
+  </si>
+  <si>
+    <t>5:41:20 PM</t>
+  </si>
+  <si>
+    <t>4.05s</t>
+  </si>
+  <si>
+    <t>TC_APP_011</t>
+  </si>
+  <si>
+    <t>TC_APP_011 - Verify add income input dialog form</t>
+  </si>
+  <si>
+    <t>5:41:38 PM</t>
+  </si>
+  <si>
+    <t>3.42s</t>
+  </si>
+  <si>
+    <t>TC_APP_012</t>
+  </si>
+  <si>
+    <t>TC_APP_012 - Verify add income form submission and balance update</t>
+  </si>
+  <si>
+    <t>5:41:44 PM</t>
+  </si>
+  <si>
+    <t>5:41:50 PM</t>
+  </si>
+  <si>
+    <t>4.72s</t>
+  </si>
+  <si>
+    <t>TC_APP_013</t>
+  </si>
+  <si>
+    <t>TC_APP_013 - Verify add expense input dialog form</t>
+  </si>
+  <si>
+    <t>3.36s</t>
+  </si>
+  <si>
+    <t>TC_APP_014</t>
+  </si>
+  <si>
+    <t>TC_APP_014 - Verify add expense form submission and balance update</t>
+  </si>
+  <si>
+    <t>5:42:08 PM</t>
+  </si>
+  <si>
+    <t>5:42:14 PM</t>
+  </si>
+  <si>
+    <t>TC_APP_015</t>
+  </si>
+  <si>
+    <t>TC_APP_015 - Verify edit transaction activity opens with details pre-filled</t>
+  </si>
+  <si>
+    <t>4.79s</t>
+  </si>
+  <si>
+    <t>TC_APP_016</t>
+  </si>
+  <si>
+    <t>TC_APP_016 - Verify transaction title update and save action</t>
+  </si>
+  <si>
+    <t>5:42:38 PM</t>
+  </si>
+  <si>
+    <t>4.43s</t>
+  </si>
+  <si>
+    <t>TC_APP_017</t>
+  </si>
+  <si>
+    <t>TC_APP_017 - Verify transaction deletion click and alert dialog confirmation</t>
+  </si>
+  <si>
+    <t>5:42:50 PM</t>
+  </si>
+  <si>
+    <t>TC_APP_018</t>
+  </si>
+  <si>
+    <t>TC_APP_018 - Verify search transaction input box filters list</t>
+  </si>
+  <si>
+    <t>4.98s</t>
+  </si>
+  <si>
+    <t>TC_APP_019</t>
+  </si>
+  <si>
+    <t>Alerts OS</t>
+  </si>
+  <si>
+    <t>TC_APP_019 - Verify budget warning alerts are displayed when budget exceeded</t>
+  </si>
+  <si>
+    <t>5:43:14 PM</t>
+  </si>
+  <si>
+    <t>2.53s</t>
+  </si>
+  <si>
+    <t>TC_APP_020</t>
+  </si>
+  <si>
+    <t>TC_APP_020 - Verify notification channel registers correctly in Android OS</t>
+  </si>
+  <si>
+    <t>5:43:20 PM</t>
+  </si>
+  <si>
+    <t>2.04s</t>
+  </si>
+  <si>
+    <t>TC_APP_021</t>
+  </si>
+  <si>
+    <t>TC_APP_021 - Verify app local push notification triggers on budget thresholds</t>
+  </si>
+  <si>
+    <t>5:43:38 PM</t>
+  </si>
+  <si>
+    <t>TC_APP_022</t>
+  </si>
+  <si>
+    <t>User Profiles</t>
+  </si>
+  <si>
+    <t>TC_APP_022 - Verify profile update form saves new username</t>
+  </si>
+  <si>
+    <t>5:43:44 PM</t>
+  </si>
+  <si>
+    <t>5:43:50 PM</t>
   </si>
   <si>
     <t>2.02s</t>
   </si>
   <si>
-    <t>TC_SEL_020</t>
-  </si>
-  <si>
-    <t>TC_SEL_020 - Verify sort transactions by date ascending/descending</t>
-  </si>
-  <si>
-    <t>5:32:35 PM</t>
-  </si>
-  <si>
-    <t>5:32:39 PM</t>
-  </si>
-  <si>
-    <t>1.63s</t>
-  </si>
-  <si>
-    <t>TC_SEL_021</t>
-  </si>
-  <si>
-    <t>TC_SEL_021 - Verify sort transactions by amount ascending/descending</t>
-  </si>
-  <si>
-    <t>5:32:45 PM</t>
-  </si>
-  <si>
-    <t>5:32:49 PM</t>
-  </si>
-  <si>
-    <t>2.24s</t>
-  </si>
-  <si>
-    <t>TC_SEL_022</t>
-  </si>
-  <si>
-    <t>Budget</t>
-  </si>
-  <si>
-    <t>TC_SEL_022 - Verify monthly budget creation and save button</t>
-  </si>
-  <si>
-    <t>5:32:55 PM</t>
-  </si>
-  <si>
-    <t>5:32:59 PM</t>
-  </si>
-  <si>
-    <t>2.96s</t>
-  </si>
-  <si>
-    <t>TC_SEL_023</t>
-  </si>
-  <si>
-    <t>TC_SEL_023 - Verify budget progress bar updates on transactions</t>
-  </si>
-  <si>
-    <t>5:33:05 PM</t>
-  </si>
-  <si>
-    <t>5:33:09 PM</t>
-  </si>
-  <si>
-    <t>1.81s</t>
-  </si>
-  <si>
-    <t>TC_SEL_024</t>
-  </si>
-  <si>
-    <t>Reports</t>
-  </si>
-  <si>
-    <t>TC_SEL_024 - Verify monthly PDF report generation</t>
-  </si>
-  <si>
-    <t>5:33:15 PM</t>
-  </si>
-  <si>
-    <t>5:33:19 PM</t>
-  </si>
-  <si>
-    <t>2.66s</t>
-  </si>
-  <si>
-    <t>TC_SEL_025</t>
-  </si>
-  <si>
-    <t>TC_SEL_025 - Verify charts render correctly in reports view</t>
-  </si>
-  <si>
-    <t>5:33:25 PM</t>
-  </si>
-  <si>
-    <t>5:33:29 PM</t>
-  </si>
-  <si>
-    <t>2.59s</t>
-  </si>
-  <si>
-    <t>TC_SEL_026</t>
-  </si>
-  <si>
-    <t>Profile</t>
-  </si>
-  <si>
-    <t>TC_SEL_026 - Verify profile details update</t>
-  </si>
-  <si>
-    <t>5:33:35 PM</t>
-  </si>
-  <si>
-    <t>5:33:39 PM</t>
-  </si>
-  <si>
-    <t>TC_SEL_027</t>
-  </si>
-  <si>
-    <t>TC_SEL_027 - Verify password update functionality</t>
-  </si>
-  <si>
-    <t>5:33:45 PM</t>
-  </si>
-  <si>
-    <t>5:33:49 PM</t>
-  </si>
-  <si>
-    <t>1.27s</t>
-  </si>
-  <si>
-    <t>TC_SEL_028</t>
-  </si>
-  <si>
-    <t>TC_SEL_028 - Verify currency settings updates</t>
-  </si>
-  <si>
-    <t>5:33:55 PM</t>
-  </si>
-  <si>
-    <t>5:33:59 PM</t>
-  </si>
-  <si>
-    <t>2.87s</t>
-  </si>
-  <si>
-    <t>TC_SEL_029</t>
-  </si>
-  <si>
-    <t>TC_SEL_029 - Verify session persistence on page refresh</t>
-  </si>
-  <si>
-    <t>5:34:05 PM</t>
-  </si>
-  <si>
-    <t>5:34:09 PM</t>
-  </si>
-  <si>
-    <t>2.89s</t>
-  </si>
-  <si>
-    <t>TC_SEL_030</t>
-  </si>
-  <si>
-    <t>TC_SEL_030 - Verify successful user logout and redirection</t>
-  </si>
-  <si>
-    <t>5:34:15 PM</t>
-  </si>
-  <si>
-    <t>5:34:19 PM</t>
-  </si>
-  <si>
-    <t>2.53s</t>
-  </si>
-  <si>
-    <t>TC_SEL_031</t>
-  </si>
-  <si>
-    <t>TC_SEL_031 - Verify currency settings updates in layout</t>
-  </si>
-  <si>
-    <t>5:34:25 PM</t>
-  </si>
-  <si>
-    <t>5:34:29 PM</t>
-  </si>
-  <si>
-    <t>1.02s</t>
-  </si>
-  <si>
-    <t>TC_SEL_032</t>
-  </si>
-  <si>
-    <t>TC_SEL_032 - Verify monthly budget limit notifications triggers</t>
-  </si>
-  <si>
-    <t>5:34:35 PM</t>
-  </si>
-  <si>
-    <t>5:34:39 PM</t>
-  </si>
-  <si>
-    <t>TC_SEL_033</t>
-  </si>
-  <si>
-    <t>TC_SEL_033 - Verify monthly PDF report download functionality</t>
-  </si>
-  <si>
-    <t>5:34:45 PM</t>
-  </si>
-  <si>
-    <t>5:34:49 PM</t>
-  </si>
-  <si>
-    <t>5.12s</t>
-  </si>
-  <si>
-    <t>TC_SEC_001</t>
-  </si>
-  <si>
-    <t>Auth Injection</t>
-  </si>
-  <si>
-    <t>TC_SEC_001 - Verify SQL injection prevention in Login email field</t>
-  </si>
-  <si>
-    <t>5:30:58 PM</t>
-  </si>
-  <si>
-    <t>1.59s</t>
-  </si>
-  <si>
-    <t>TC_SEC_002</t>
-  </si>
-  <si>
-    <t>TC_SEC_002 - Verify SQL injection prevention in Login password field</t>
-  </si>
-  <si>
-    <t>5:31:03 PM</t>
-  </si>
-  <si>
-    <t>5:31:06 PM</t>
-  </si>
-  <si>
-    <t>0.94s</t>
-  </si>
-  <si>
-    <t>TC_SEC_003</t>
-  </si>
-  <si>
-    <t>TC_SEC_003 - Verify SQL injection prevention in register input fields</t>
-  </si>
-  <si>
-    <t>5:31:11 PM</t>
-  </si>
-  <si>
-    <t>5:31:14 PM</t>
-  </si>
-  <si>
-    <t>1.31s</t>
-  </si>
-  <si>
-    <t>TC_SEC_004</t>
-  </si>
-  <si>
-    <t>CSRF Prevention</t>
-  </si>
-  <si>
-    <t>TC_SEC_004 - Verify HTML / Script tag sanitization in transaction title input</t>
-  </si>
-  <si>
-    <t>5:31:22 PM</t>
-  </si>
-  <si>
-    <t>1.67s</t>
-  </si>
-  <si>
-    <t>TC_SEC_005</t>
-  </si>
-  <si>
-    <t>TC_SEC_005 - Verify sanitization of script tags in transaction category input</t>
-  </si>
-  <si>
-    <t>5:31:27 PM</t>
-  </si>
-  <si>
-    <t>5:31:30 PM</t>
-  </si>
-  <si>
-    <t>1.97s</t>
-  </si>
-  <si>
-    <t>TC_SEC_006</t>
-  </si>
-  <si>
-    <t>TC_SEC_006 - Verify anti-CSRF token verification on POST transactions endpoint</t>
-  </si>
-  <si>
-    <t>5:31:38 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_007</t>
-  </si>
-  <si>
-    <t>TC_SEC_007 - Verify anti-CSRF token verification on DELETE budget endpoint</t>
-  </si>
-  <si>
-    <t>5:31:43 PM</t>
-  </si>
-  <si>
-    <t>5:31:46 PM</t>
-  </si>
-  <si>
-    <t>1.01s</t>
-  </si>
-  <si>
-    <t>TC_SEC_008</t>
-  </si>
-  <si>
-    <t>JWT Validation</t>
-  </si>
-  <si>
-    <t>TC_SEC_008 - Verify JWT token validation with incorrect signatures</t>
-  </si>
-  <si>
-    <t>5:31:51 PM</t>
-  </si>
-  <si>
-    <t>5:31:54 PM</t>
-  </si>
-  <si>
-    <t>0.87s</t>
-  </si>
-  <si>
-    <t>TC_SEC_009</t>
-  </si>
-  <si>
-    <t>TC_SEC_009 - Verify JWT token expiration enforcement</t>
-  </si>
-  <si>
-    <t>5:32:02 PM</t>
-  </si>
-  <si>
-    <t>1.19s</t>
-  </si>
-  <si>
-    <t>TC_SEC_010</t>
-  </si>
-  <si>
-    <t>TC_SEC_010 - Verify session timeout redirection after inactivity</t>
-  </si>
-  <si>
-    <t>5:32:07 PM</t>
-  </si>
-  <si>
-    <t>5:32:10 PM</t>
-  </si>
-  <si>
-    <t>1.41s</t>
-  </si>
-  <si>
-    <t>TC_SEC_011</t>
-  </si>
-  <si>
-    <t>Access Control</t>
-  </si>
-  <si>
-    <t>TC_SEC_011 - Verify input length validations on transaction title</t>
-  </si>
-  <si>
-    <t>5:32:18 PM</t>
-  </si>
-  <si>
-    <t>1.73s</t>
-  </si>
-  <si>
-    <t>TC_SEC_012</t>
-  </si>
-  <si>
-    <t>TC_SEC_012 - Verify negative amount validation on transaction entries</t>
-  </si>
-  <si>
-    <t>5:32:23 PM</t>
-  </si>
-  <si>
-    <t>5:32:26 PM</t>
-  </si>
-  <si>
-    <t>1.53s</t>
-  </si>
-  <si>
-    <t>TC_SEC_013</t>
-  </si>
-  <si>
-    <t>TC_SEC_013 - Verify non-numeric input rejection on budget amounts</t>
-  </si>
-  <si>
-    <t>5:32:31 PM</t>
-  </si>
-  <si>
-    <t>5:32:34 PM</t>
-  </si>
-  <si>
-    <t>0.82s</t>
-  </si>
-  <si>
-    <t>TC_SEC_014</t>
-  </si>
-  <si>
-    <t>TC_SEC_014 - Verify authorization checks for transaction deletion</t>
-  </si>
-  <si>
-    <t>5:32:42 PM</t>
-  </si>
-  <si>
-    <t>1.29s</t>
-  </si>
-  <si>
-    <t>TC_SEC_015</t>
-  </si>
-  <si>
-    <t>TC_SEC_015 - Verify access control: guest user cannot access dashboard API</t>
-  </si>
-  <si>
-    <t>5:32:47 PM</t>
-  </si>
-  <si>
-    <t>5:32:50 PM</t>
-  </si>
-  <si>
-    <t>1.99s</t>
-  </si>
-  <si>
-    <t>TC_SEC_016</t>
-  </si>
-  <si>
-    <t>TC_SEC_016 - Verify access control: user cannot view other users transactions</t>
-  </si>
-  <si>
-    <t>5:32:58 PM</t>
-  </si>
-  <si>
-    <t>1.79s</t>
-  </si>
-  <si>
-    <t>TC_SEC_017</t>
-  </si>
-  <si>
-    <t>TC_SEC_017 - Verify password hash complexity strength check</t>
-  </si>
-  <si>
-    <t>5:33:03 PM</t>
-  </si>
-  <si>
-    <t>5:33:06 PM</t>
-  </si>
-  <si>
-    <t>1.72s</t>
-  </si>
-  <si>
-    <t>TC_SEC_018</t>
-  </si>
-  <si>
-    <t>TC_SEC_018 - Verify file upload size validations</t>
-  </si>
-  <si>
-    <t>5:33:11 PM</t>
-  </si>
-  <si>
-    <t>5:33:14 PM</t>
-  </si>
-  <si>
-    <t>0.74s</t>
-  </si>
-  <si>
-    <t>TC_SEC_019</t>
-  </si>
-  <si>
-    <t>TC_SEC_019 - Verify file upload extension whitelist block (.sh, .exe, .js)</t>
-  </si>
-  <si>
-    <t>5:33:22 PM</t>
-  </si>
-  <si>
-    <t>0.55s</t>
-  </si>
-  <si>
-    <t>TC_SEC_020</t>
-  </si>
-  <si>
-    <t>TC_SEC_020 - Verify API authorization on budgets edit endpoint</t>
-  </si>
-  <si>
-    <t>5:33:27 PM</t>
-  </si>
-  <si>
-    <t>5:33:30 PM</t>
-  </si>
-  <si>
-    <t>0.59s</t>
-  </si>
-  <si>
-    <t>TC_SEC_021</t>
-  </si>
-  <si>
-    <t>HTTP Headers</t>
-  </si>
-  <si>
-    <t>TC_SEC_021 - Verify CORS policy matches trusted domains only</t>
-  </si>
-  <si>
-    <t>5:33:38 PM</t>
-  </si>
-  <si>
-    <t>1.74s</t>
-  </si>
-  <si>
-    <t>TC_SEC_022</t>
-  </si>
-  <si>
-    <t>TC_SEC_022 - Verify X-Frame-Options: SAMEORIGIN header presence</t>
-  </si>
-  <si>
-    <t>5:33:43 PM</t>
-  </si>
-  <si>
-    <t>5:33:46 PM</t>
-  </si>
-  <si>
-    <t>0.73s</t>
-  </si>
-  <si>
-    <t>TC_SEC_023</t>
-  </si>
-  <si>
-    <t>TC_SEC_023 - Verify X-Content-Type-Options: nosniff header presence</t>
-  </si>
-  <si>
-    <t>5:33:51 PM</t>
-  </si>
-  <si>
-    <t>5:33:54 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_024</t>
-  </si>
-  <si>
-    <t>TC_SEC_024 - Verify Strict-Transport-Security header presence</t>
-  </si>
-  <si>
-    <t>5:34:02 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_025</t>
-  </si>
-  <si>
-    <t>TC_SEC_025 - Verify Content-Security-Policy header presence</t>
-  </si>
-  <si>
-    <t>5:34:07 PM</t>
-  </si>
-  <si>
-    <t>5:34:10 PM</t>
-  </si>
-  <si>
-    <t>1.52s</t>
-  </si>
-  <si>
-    <t>TC_SEC_026</t>
-  </si>
-  <si>
-    <t>TC_SEC_026 - Verify secure cookie attributes (HttpOnly, Secure)</t>
-  </si>
-  <si>
-    <t>5:34:18 PM</t>
-  </si>
-  <si>
-    <t>0.69s</t>
-  </si>
-  <si>
-    <t>TC_SEC_027</t>
-  </si>
-  <si>
-    <t>TC_SEC_027 - Verify rate limiting protection on authentication endpoints</t>
-  </si>
-  <si>
-    <t>5:34:23 PM</t>
-  </si>
-  <si>
-    <t>5:34:26 PM</t>
-  </si>
-  <si>
-    <t>1.50s</t>
-  </si>
-  <si>
-    <t>TC_SEC_028</t>
-  </si>
-  <si>
-    <t>TC_SEC_028 - Verify dependency vulnerabilities with npm audit</t>
-  </si>
-  <si>
-    <t>5:34:31 PM</t>
-  </si>
-  <si>
-    <t>5:34:34 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_029</t>
-  </si>
-  <si>
-    <t>TC_SEC_029 - Verify OWASP ZAP active scanning summary</t>
-  </si>
-  <si>
-    <t>5:34:42 PM</t>
-  </si>
-  <si>
-    <t>0.80s</t>
-  </si>
-  <si>
-    <t>TC_SEC_030</t>
-  </si>
-  <si>
-    <t>TC_SEC_030 - Verify TLS version compliance checking</t>
-  </si>
-  <si>
-    <t>5:34:47 PM</t>
-  </si>
-  <si>
-    <t>5:34:50 PM</t>
-  </si>
-  <si>
-    <t>8.50s</t>
-  </si>
-  <si>
-    <t>TC_APP_001</t>
-  </si>
-  <si>
-    <t>Mobile Onboarding</t>
-  </si>
-  <si>
-    <t>TC_APP_001 - Verify App Launch activity loads successfully</t>
-  </si>
-  <si>
-    <t>5:28:55 PM</t>
-  </si>
-  <si>
-    <t>5:29:01 PM</t>
-  </si>
-  <si>
-    <t>3.14s</t>
-  </si>
-  <si>
-    <t>TC_APP_002</t>
-  </si>
-  <si>
-    <t>TC_APP_002 - Verify splash screen transition duration</t>
-  </si>
-  <si>
-    <t>5:29:07 PM</t>
-  </si>
-  <si>
-    <t>5:29:13 PM</t>
-  </si>
-  <si>
-    <t>3.23s</t>
-  </si>
-  <si>
-    <t>TC_APP_003</t>
-  </si>
-  <si>
-    <t>TC_APP_003 - Verify registration page display inside app</t>
-  </si>
-  <si>
-    <t>5:29:19 PM</t>
-  </si>
-  <si>
-    <t>4.53s</t>
-  </si>
-  <si>
-    <t>TC_APP_004</t>
-  </si>
-  <si>
-    <t>TC_APP_004 - Verify new account registration via mobile form</t>
-  </si>
-  <si>
-    <t>5:29:31 PM</t>
-  </si>
-  <si>
-    <t>5:29:37 PM</t>
-  </si>
-  <si>
-    <t>4.19s</t>
-  </si>
-  <si>
-    <t>TC_APP_005</t>
-  </si>
-  <si>
-    <t>TC_APP_005 - Verify app displays validation errors on registration</t>
-  </si>
-  <si>
-    <t>5:29:43 PM</t>
-  </si>
-  <si>
-    <t>4.67s</t>
-  </si>
-  <si>
-    <t>TC_APP_006</t>
-  </si>
-  <si>
-    <t>TC_APP_006 - Verify Login screen load and fields check</t>
-  </si>
-  <si>
-    <t>5:30:01 PM</t>
-  </si>
-  <si>
-    <t>3.20s</t>
-  </si>
-  <si>
-    <t>TC_APP_007</t>
-  </si>
-  <si>
-    <t>TC_APP_007 - Verify successful authentication with valid credentials</t>
-  </si>
-  <si>
-    <t>5:30:07 PM</t>
-  </si>
-  <si>
-    <t>5:30:13 PM</t>
-  </si>
-  <si>
-    <t>4.92s</t>
-  </si>
-  <si>
-    <t>TC_APP_008</t>
-  </si>
-  <si>
-    <t>TC_APP_008 - Verify authentication rejection and toast notification</t>
-  </si>
-  <si>
-    <t>3.49s</t>
-  </si>
-  <si>
-    <t>TC_APP_009</t>
-  </si>
-  <si>
-    <t>Transactions Activity</t>
-  </si>
-  <si>
-    <t>TC_APP_009 - Verify dashboard page layout and toolbar items</t>
-  </si>
-  <si>
-    <t>5:30:31 PM</t>
-  </si>
-  <si>
-    <t>5:30:37 PM</t>
-  </si>
-  <si>
-    <t>3.13s</t>
-  </si>
-  <si>
-    <t>TC_APP_010</t>
-  </si>
-  <si>
-    <t>TC_APP_010 - Verify scroll and swipe in navigation drawer</t>
-  </si>
-  <si>
-    <t>5:30:43 PM</t>
-  </si>
-  <si>
-    <t>4.38s</t>
-  </si>
-  <si>
-    <t>TC_APP_011</t>
-  </si>
-  <si>
-    <t>TC_APP_011 - Verify add income input dialog form</t>
-  </si>
-  <si>
-    <t>5:31:01 PM</t>
-  </si>
-  <si>
-    <t>2.43s</t>
-  </si>
-  <si>
-    <t>TC_APP_012</t>
-  </si>
-  <si>
-    <t>TC_APP_012 - Verify add income form submission and balance update</t>
-  </si>
-  <si>
-    <t>5:31:07 PM</t>
-  </si>
-  <si>
-    <t>5:31:13 PM</t>
-  </si>
-  <si>
-    <t>3.99s</t>
-  </si>
-  <si>
-    <t>TC_APP_013</t>
-  </si>
-  <si>
-    <t>TC_APP_013 - Verify add expense input dialog form</t>
-  </si>
-  <si>
-    <t>3.76s</t>
-  </si>
-  <si>
-    <t>TC_APP_014</t>
-  </si>
-  <si>
-    <t>TC_APP_014 - Verify add expense form submission and balance update</t>
-  </si>
-  <si>
-    <t>5:31:31 PM</t>
-  </si>
-  <si>
-    <t>5:31:37 PM</t>
-  </si>
-  <si>
-    <t>4.82s</t>
-  </si>
-  <si>
-    <t>TC_APP_015</t>
-  </si>
-  <si>
-    <t>TC_APP_015 - Verify edit transaction activity opens with details pre-filled</t>
-  </si>
-  <si>
-    <t>3.02s</t>
-  </si>
-  <si>
-    <t>TC_APP_016</t>
-  </si>
-  <si>
-    <t>TC_APP_016 - Verify transaction title update and save action</t>
-  </si>
-  <si>
-    <t>5:32:01 PM</t>
-  </si>
-  <si>
-    <t>2.29s</t>
-  </si>
-  <si>
-    <t>TC_APP_017</t>
-  </si>
-  <si>
-    <t>TC_APP_017 - Verify transaction deletion click and alert dialog confirmation</t>
-  </si>
-  <si>
-    <t>5:32:13 PM</t>
-  </si>
-  <si>
-    <t>4.39s</t>
-  </si>
-  <si>
-    <t>TC_APP_018</t>
-  </si>
-  <si>
-    <t>TC_APP_018 - Verify search transaction input box filters list</t>
-  </si>
-  <si>
-    <t>3.34s</t>
-  </si>
-  <si>
-    <t>TC_APP_019</t>
-  </si>
-  <si>
-    <t>Alerts OS</t>
-  </si>
-  <si>
-    <t>TC_APP_019 - Verify budget warning alerts are displayed when budget exceeded</t>
-  </si>
-  <si>
-    <t>5:32:37 PM</t>
-  </si>
-  <si>
-    <t>4.52s</t>
-  </si>
-  <si>
-    <t>TC_APP_020</t>
-  </si>
-  <si>
-    <t>TC_APP_020 - Verify notification channel registers correctly in Android OS</t>
-  </si>
-  <si>
-    <t>5:32:43 PM</t>
-  </si>
-  <si>
-    <t>4.58s</t>
-  </si>
-  <si>
-    <t>TC_APP_021</t>
-  </si>
-  <si>
-    <t>TC_APP_021 - Verify app local push notification triggers on budget thresholds</t>
-  </si>
-  <si>
-    <t>5:33:01 PM</t>
-  </si>
-  <si>
-    <t>4.48s</t>
-  </si>
-  <si>
-    <t>TC_APP_022</t>
-  </si>
-  <si>
-    <t>User Profiles</t>
-  </si>
-  <si>
-    <t>TC_APP_022 - Verify profile update form saves new username</t>
-  </si>
-  <si>
-    <t>5:33:07 PM</t>
-  </si>
-  <si>
-    <t>5:33:13 PM</t>
-  </si>
-  <si>
-    <t>2.93s</t>
-  </si>
-  <si>
     <t>TC_APP_023</t>
   </si>
   <si>
     <t>TC_APP_023 - Verify profile image upload simulation</t>
   </si>
   <si>
-    <t>3.35s</t>
+    <t>4.15s</t>
   </si>
   <si>
     <t>TC_APP_024</t>
@@ -1346,13 +1421,13 @@
     <t>TC_APP_024 - Verify change password form validation checks</t>
   </si>
   <si>
-    <t>5:33:31 PM</t>
-  </si>
-  <si>
-    <t>5:33:37 PM</t>
-  </si>
-  <si>
-    <t>3.18s</t>
+    <t>5:44:08 PM</t>
+  </si>
+  <si>
+    <t>5:44:14 PM</t>
+  </si>
+  <si>
+    <t>4.21s</t>
   </si>
   <si>
     <t>TC_APP_025</t>
@@ -1361,19 +1436,16 @@
     <t>TC_APP_025 - Verify successful change password submission</t>
   </si>
   <si>
-    <t>3.17s</t>
-  </si>
-  <si>
     <t>TC_APP_026</t>
   </si>
   <si>
     <t>TC_APP_026 - Verify dark theme toggle works on main dashboard screen</t>
   </si>
   <si>
-    <t>5:34:01 PM</t>
-  </si>
-  <si>
-    <t>3.37s</t>
+    <t>5:44:38 PM</t>
+  </si>
+  <si>
+    <t>4.76s</t>
   </si>
   <si>
     <t>TC_APP_027</t>
@@ -1382,7 +1454,7 @@
     <t>TC_APP_027 - Verify app recovers UI states on device rotation (portrait/landscape)</t>
   </si>
   <si>
-    <t>5:34:13 PM</t>
+    <t>5:44:50 PM</t>
   </si>
   <si>
     <t>TC_APP_028</t>
@@ -1391,7 +1463,7 @@
     <t>TC_APP_028 - Verify session recovery on backgrounding and restoring app</t>
   </si>
   <si>
-    <t>3.81s</t>
+    <t>3.05s</t>
   </si>
   <si>
     <t>TC_APP_029</t>
@@ -1400,7 +1472,10 @@
     <t>TC_APP_029 - Verify logout button click asks confirmation</t>
   </si>
   <si>
-    <t>5:34:37 PM</t>
+    <t>5:45:14 PM</t>
+  </si>
+  <si>
+    <t>3.80s</t>
   </si>
   <si>
     <t>TC_APP_030</t>
@@ -1409,10 +1484,7 @@
     <t>TC_APP_030 - Verify successful logout clears local cache database</t>
   </si>
   <si>
-    <t>5:34:43 PM</t>
-  </si>
-  <si>
-    <t>3.98s</t>
+    <t>5:45:20 PM</t>
   </si>
   <si>
     <t>Test Name</t>
@@ -1457,7 +1529,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>2026-06-15T12:04:55.240Z</t>
+    <t>2026-06-15T12:15:32.203Z</t>
   </si>
   <si>
     <t>Execution of TC_SEL_001</t>
@@ -1571,7 +1643,7 @@
     <t>Element not interactable / button click intercepted</t>
   </si>
   <si>
-    <t>2026-06-15T12:04:55.278Z</t>
+    <t>2026-06-15T12:15:32.241Z</t>
   </si>
   <si>
     <t>Execution of TC_SEC_001</t>
@@ -1670,7 +1742,25 @@
     <t>Audit found TLS 1.0 support enabled on test server endpoint</t>
   </si>
   <si>
-    <t>2026-06-15T12:04:55.279Z</t>
+    <t>Execution of TC_SEC_031</t>
+  </si>
+  <si>
+    <t>Execution of TC_SEC_032</t>
+  </si>
+  <si>
+    <t>Execution of TC_SEC_033</t>
+  </si>
+  <si>
+    <t>Execution of TC_SEC_034</t>
+  </si>
+  <si>
+    <t>Execution of TC_SEC_035</t>
+  </si>
+  <si>
+    <t>Execution of TC_SEC_036</t>
+  </si>
+  <si>
+    <t>2026-06-15T12:15:32.242Z</t>
   </si>
   <si>
     <t>Execution of TC_APP_001</t>
@@ -2381,10 +2471,10 @@
         <v>13</v>
       </c>
       <c r="E3" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F3" s="2">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G3" s="2">
         <v>1</v>
@@ -2445,10 +2535,10 @@
         <v>13</v>
       </c>
       <c r="E5" s="3">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F5" s="3">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G5" s="3">
         <v>2</v>
@@ -2471,7 +2561,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -2740,18 +2830,18 @@
         <v>81</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>12</v>
@@ -2760,24 +2850,24 @@
         <v>5</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>12</v>
@@ -2786,24 +2876,24 @@
         <v>5</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>12</v>
@@ -2812,24 +2902,24 @@
         <v>5</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>12</v>
@@ -2838,24 +2928,24 @@
         <v>5</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>12</v>
@@ -2864,24 +2954,24 @@
         <v>5</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>12</v>
@@ -2890,24 +2980,24 @@
         <v>5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>12</v>
@@ -2916,24 +3006,24 @@
         <v>5</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>12</v>
@@ -2942,24 +3032,24 @@
         <v>5</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>12</v>
@@ -2968,24 +3058,24 @@
         <v>5</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>12</v>
@@ -2994,24 +3084,24 @@
         <v>5</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>12</v>
@@ -3020,24 +3110,24 @@
         <v>5</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>12</v>
@@ -3046,24 +3136,24 @@
         <v>5</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>12</v>
@@ -3072,24 +3162,24 @@
         <v>5</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>12</v>
@@ -3098,24 +3188,24 @@
         <v>5</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>12</v>
@@ -3124,24 +3214,24 @@
         <v>5</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>12</v>
@@ -3150,24 +3240,24 @@
         <v>5</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>12</v>
@@ -3176,24 +3266,24 @@
         <v>5</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>136</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>12</v>
@@ -3202,24 +3292,24 @@
         <v>5</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>12</v>
@@ -3228,24 +3318,24 @@
         <v>5</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>12</v>
@@ -3254,24 +3344,24 @@
         <v>5</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>12</v>
@@ -3280,24 +3370,24 @@
         <v>5</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>12</v>
@@ -3306,24 +3396,24 @@
         <v>5</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>12</v>
@@ -3332,24 +3422,24 @@
         <v>5</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>126</v>
+        <v>199</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>12</v>
@@ -3358,24 +3448,24 @@
         <v>6</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>17</v>
@@ -3384,24 +3474,24 @@
         <v>5</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>85</v>
+        <v>208</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>17</v>
@@ -3410,24 +3500,24 @@
         <v>5</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>210</v>
+        <v>65</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>212</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>17</v>
@@ -3436,24 +3526,24 @@
         <v>5</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>17</v>
@@ -3462,24 +3552,24 @@
         <v>5</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>96</v>
+        <v>222</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>17</v>
@@ -3488,24 +3578,24 @@
         <v>5</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>225</v>
+        <v>76</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>17</v>
@@ -3514,24 +3604,24 @@
         <v>5</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>104</v>
+        <v>231</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>173</v>
+        <v>233</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>17</v>
@@ -3540,24 +3630,24 @@
         <v>5</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>233</v>
+        <v>86</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>17</v>
@@ -3566,24 +3656,24 @@
         <v>5</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>17</v>
@@ -3592,24 +3682,24 @@
         <v>5</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>115</v>
+        <v>246</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>17</v>
@@ -3618,24 +3708,24 @@
         <v>5</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>248</v>
+        <v>97</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>17</v>
@@ -3644,24 +3734,24 @@
         <v>5</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>124</v>
+        <v>256</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>17</v>
@@ -3670,24 +3760,24 @@
         <v>5</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>258</v>
+        <v>106</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>17</v>
@@ -3696,24 +3786,24 @@
         <v>5</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>17</v>
@@ -3722,24 +3812,24 @@
         <v>5</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>135</v>
+        <v>270</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>17</v>
@@ -3748,24 +3838,24 @@
         <v>5</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>272</v>
+        <v>117</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>17</v>
@@ -3774,24 +3864,24 @@
         <v>5</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>145</v>
+        <v>279</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>17</v>
@@ -3800,24 +3890,24 @@
         <v>5</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>281</v>
+        <v>126</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>17</v>
@@ -3826,24 +3916,24 @@
         <v>5</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>17</v>
@@ -3852,24 +3942,24 @@
         <v>5</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>157</v>
+        <v>293</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>292</v>
+        <v>194</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>17</v>
@@ -3878,24 +3968,24 @@
         <v>5</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>295</v>
+        <v>137</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>17</v>
@@ -3904,24 +3994,24 @@
         <v>5</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>167</v>
+        <v>302</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>17</v>
@@ -3930,24 +4020,24 @@
         <v>5</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>305</v>
+        <v>146</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>17</v>
@@ -3956,24 +4046,24 @@
         <v>5</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>288</v>
+        <v>313</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>17</v>
@@ -3982,24 +4072,24 @@
         <v>5</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>177</v>
+        <v>316</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>152</v>
+        <v>318</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>17</v>
@@ -4008,24 +4098,24 @@
         <v>5</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>317</v>
+        <v>158</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>17</v>
@@ -4034,24 +4124,24 @@
         <v>5</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>186</v>
+        <v>325</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>323</v>
+        <v>218</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>17</v>
@@ -4060,24 +4150,24 @@
         <v>5</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>326</v>
+        <v>168</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>17</v>
@@ -4086,24 +4176,24 @@
         <v>5</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>193</v>
+        <v>335</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>17</v>
@@ -4112,24 +4202,24 @@
         <v>5</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>197</v>
+        <v>338</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>17</v>
@@ -4138,180 +4228,180 @@
         <v>6</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>339</v>
+        <v>178</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>343</v>
+        <v>300</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E65" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>343</v>
+        <v>300</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>350</v>
+        <v>187</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>343</v>
+        <v>300</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>40</v>
+        <v>357</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>343</v>
+        <v>300</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>361</v>
+        <v>218</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>343</v>
+        <v>300</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E69" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>364</v>
+        <v>198</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>51</v>
+        <v>365</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>343</v>
+        <v>300</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E70" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>55</v>
+        <v>369</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>343</v>
+        <v>373</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>21</v>
@@ -4320,24 +4410,24 @@
         <v>5</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>343</v>
+        <v>373</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>21</v>
@@ -4346,24 +4436,24 @@
         <v>5</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>66</v>
+        <v>380</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>70</v>
+        <v>381</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>21</v>
@@ -4372,24 +4462,24 @@
         <v>5</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>382</v>
+        <v>40</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>21</v>
@@ -4398,24 +4488,24 @@
         <v>5</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>81</v>
+        <v>390</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>21</v>
@@ -4424,24 +4514,24 @@
         <v>5</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>85</v>
+        <v>394</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>390</v>
+        <v>51</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>21</v>
@@ -4450,24 +4540,24 @@
         <v>5</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>394</v>
+        <v>55</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>21</v>
@@ -4476,24 +4566,24 @@
         <v>5</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>96</v>
+        <v>208</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>99</v>
+        <v>402</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>21</v>
@@ -4502,24 +4592,24 @@
         <v>5</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>402</v>
+        <v>66</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>403</v>
+        <v>70</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>379</v>
+        <v>408</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>21</v>
@@ -4528,24 +4618,24 @@
         <v>5</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>110</v>
+        <v>410</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="B80" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="B80" s="4" t="s">
-        <v>379</v>
-      </c>
       <c r="C80" s="4" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>21</v>
@@ -4554,24 +4644,24 @@
         <v>5</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>114</v>
+        <v>414</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>410</v>
+        <v>81</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>379</v>
+        <v>408</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>21</v>
@@ -4580,24 +4670,24 @@
         <v>5</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>248</v>
+        <v>86</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>379</v>
+        <v>408</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>21</v>
@@ -4606,24 +4696,24 @@
         <v>5</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>125</v>
+        <v>422</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>129</v>
+        <v>423</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>21</v>
@@ -4632,24 +4722,24 @@
         <v>5</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>263</v>
+        <v>97</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>422</v>
+        <v>101</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>21</v>
@@ -4658,24 +4748,24 @@
         <v>5</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>140</v>
+        <v>431</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>427</v>
+        <v>395</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>21</v>
@@ -4684,24 +4774,24 @@
         <v>5</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>145</v>
+        <v>265</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>430</v>
+        <v>112</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>433</v>
+        <v>408</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>21</v>
@@ -4710,24 +4800,24 @@
         <v>5</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>435</v>
+        <v>116</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>433</v>
+        <v>408</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>21</v>
@@ -4736,24 +4826,24 @@
         <v>5</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>157</v>
+        <v>279</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>161</v>
+        <v>441</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>440</v>
+        <v>52</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>433</v>
+        <v>408</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>21</v>
@@ -4762,21 +4852,21 @@
         <v>5</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>443</v>
+        <v>127</v>
       </c>
       <c r="G88" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="H88" s="4" t="s">
         <v>444</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="B89" s="4" t="s">
         <v>446</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>433</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>447</v>
@@ -4788,24 +4878,24 @@
         <v>5</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>172</v>
+        <v>448</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>21</v>
@@ -4814,24 +4904,24 @@
         <v>5</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>176</v>
+        <v>452</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>451</v>
+        <v>141</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>21</v>
@@ -4840,24 +4930,24 @@
         <v>5</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>317</v>
+        <v>146</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>158</v>
+        <v>449</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>433</v>
+        <v>458</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>21</v>
@@ -4866,24 +4956,24 @@
         <v>5</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>187</v>
+        <v>460</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>191</v>
+        <v>461</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>433</v>
+        <v>458</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>21</v>
@@ -4892,24 +4982,24 @@
         <v>5</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>331</v>
+        <v>158</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>461</v>
+        <v>162</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>427</v>
+        <v>465</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>433</v>
+        <v>458</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>21</v>
@@ -4918,13 +5008,169 @@
         <v>5</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>201</v>
+        <v>469</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>465</v>
+        <v>470</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -4948,13 +5194,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>466</v>
+        <v>490</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>467</v>
+        <v>491</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>468</v>
+        <v>492</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>32</v>
@@ -4963,18 +5209,18 @@
         <v>3</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>469</v>
+        <v>493</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>470</v>
+        <v>494</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>471</v>
+        <v>495</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>12</v>
@@ -4983,18 +5229,18 @@
         <v>13</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>472</v>
+        <v>496</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>473</v>
+        <v>497</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>474</v>
+        <v>498</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>17</v>
@@ -5003,7 +5249,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>475</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>
@@ -5014,7 +5260,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -5026,1600 +5272,1702 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>476</v>
+        <v>500</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>466</v>
+        <v>490</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>477</v>
+        <v>501</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>478</v>
+        <v>502</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>479</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>481</v>
+        <v>505</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>43</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>484</v>
+        <v>508</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>48</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>485</v>
+        <v>509</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>53</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>58</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>487</v>
+        <v>511</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>63</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>488</v>
+        <v>512</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>489</v>
+        <v>513</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>490</v>
+        <v>514</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>491</v>
+        <v>515</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>492</v>
+        <v>516</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>493</v>
+        <v>517</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>494</v>
+        <v>518</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>495</v>
+        <v>519</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>496</v>
+        <v>520</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>497</v>
+        <v>521</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>498</v>
+        <v>522</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>499</v>
+        <v>523</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>500</v>
+        <v>524</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>501</v>
+        <v>525</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>503</v>
+        <v>527</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>504</v>
+        <v>528</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>505</v>
+        <v>529</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>506</v>
+        <v>530</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C26" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>507</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>508</v>
+        <v>532</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>509</v>
+        <v>533</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>510</v>
+        <v>534</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>511</v>
+        <v>535</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>512</v>
+        <v>536</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>513</v>
+        <v>537</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>514</v>
+        <v>538</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>515</v>
+        <v>539</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>516</v>
+        <v>540</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>517</v>
+        <v>541</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>519</v>
+        <v>543</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>521</v>
+        <v>545</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>522</v>
+        <v>546</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>523</v>
+        <v>547</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>524</v>
+        <v>548</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>525</v>
+        <v>549</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>526</v>
+        <v>550</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>527</v>
+        <v>551</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>528</v>
+        <v>552</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>529</v>
+        <v>553</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>530</v>
+        <v>554</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>531</v>
+        <v>555</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>532</v>
+        <v>556</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>533</v>
+        <v>557</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>534</v>
+        <v>558</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>535</v>
+        <v>559</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>536</v>
+        <v>560</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>537</v>
+        <v>561</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>538</v>
+        <v>562</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>539</v>
+        <v>563</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>540</v>
+        <v>564</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>541</v>
+        <v>565</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>542</v>
+        <v>566</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>543</v>
+        <v>567</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C59" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="E59" s="4" t="s">
         <v>544</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>545</v>
+        <v>569</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>546</v>
+        <v>570</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>547</v>
+        <v>571</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>548</v>
+        <v>572</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>549</v>
+        <v>573</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>516</v>
+        <v>540</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>550</v>
+        <v>574</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>552</v>
+        <v>575</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>554</v>
+        <v>576</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>555</v>
+        <v>577</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>556</v>
+        <v>578</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>557</v>
+        <v>579</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>558</v>
+        <v>580</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>559</v>
+        <v>582</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>560</v>
+        <v>584</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>561</v>
+        <v>585</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>562</v>
+        <v>586</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>563</v>
+        <v>587</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>564</v>
+        <v>588</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>565</v>
+        <v>589</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>566</v>
+        <v>590</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>567</v>
+        <v>591</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>568</v>
+        <v>592</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>569</v>
+        <v>593</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>570</v>
+        <v>594</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>571</v>
+        <v>595</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>572</v>
+        <v>596</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>573</v>
+        <v>597</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>574</v>
+        <v>598</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>575</v>
+        <v>599</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>576</v>
+        <v>600</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>578</v>
+        <v>602</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>579</v>
+        <v>603</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>553</v>
+        <v>583</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>583</v>
       </c>
     </row>
   </sheetData>
@@ -6641,172 +6989,172 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>476</v>
+        <v>500</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>583</v>
+        <v>613</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>584</v>
+        <v>614</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>585</v>
+        <v>615</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>479</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>586</v>
+        <v>616</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>587</v>
+        <v>617</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>588</v>
+        <v>618</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>589</v>
+        <v>619</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>590</v>
+        <v>620</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>591</v>
+        <v>621</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>592</v>
+        <v>622</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>589</v>
+        <v>619</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>593</v>
+        <v>623</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>594</v>
+        <v>624</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>595</v>
+        <v>625</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>589</v>
+        <v>619</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>596</v>
+        <v>626</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>597</v>
+        <v>627</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>598</v>
+        <v>628</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>589</v>
+        <v>619</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>599</v>
+        <v>629</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>601</v>
+        <v>631</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>589</v>
+        <v>619</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>602</v>
+        <v>632</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>603</v>
+        <v>633</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>604</v>
+        <v>634</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>589</v>
+        <v>619</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>605</v>
+        <v>635</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>606</v>
+        <v>636</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>607</v>
+        <v>637</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>589</v>
+        <v>619</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>590</v>
+        <v>620</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>608</v>
+        <v>638</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>609</v>
+        <v>639</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>589</v>
+        <v>619</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>610</v>
+        <v>640</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>611</v>
+        <v>641</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>598</v>
+        <v>628</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>589</v>
+        <v>619</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Master_Report.xlsx
+++ b/reports/Master_Report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="634">
   <si>
     <t>Execution Date</t>
   </si>
@@ -47,7 +47,7 @@
     <t>Execution Duration</t>
   </si>
   <si>
-    <t>6/15/2026, 5:45:32 PM</t>
+    <t>6/15/2026, 6:07:07 PM</t>
   </si>
   <si>
     <t>Selenium (Web E2E)</t>
@@ -59,7 +59,7 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>96.97%</t>
+    <t>96.77%</t>
   </si>
   <si>
     <t>00:02:15</t>
@@ -98,7 +98,7 @@
     <t>Multi-Platform</t>
   </si>
   <si>
-    <t>97.98%</t>
+    <t>97.94%</t>
   </si>
   <si>
     <t>00:08:37</t>
@@ -137,13 +137,13 @@
     <t>TC_SEL_001 - Verify registration page load</t>
   </si>
   <si>
-    <t>5:40:02 PM</t>
-  </si>
-  <si>
-    <t>5:40:06 PM</t>
-  </si>
-  <si>
-    <t>2.38s</t>
+    <t>6:01:57 PM</t>
+  </si>
+  <si>
+    <t>6:02:01 PM</t>
+  </si>
+  <si>
+    <t>2.23s</t>
   </si>
   <si>
     <t>TC_SEL_002</t>
@@ -152,1231 +152,1207 @@
     <t>TC_SEL_002 - Verify successful user registration</t>
   </si>
   <si>
-    <t>5:40:12 PM</t>
-  </si>
-  <si>
-    <t>5:40:16 PM</t>
+    <t>6:02:07 PM</t>
+  </si>
+  <si>
+    <t>6:02:11 PM</t>
+  </si>
+  <si>
+    <t>2.16s</t>
+  </si>
+  <si>
+    <t>TC_SEL_003</t>
+  </si>
+  <si>
+    <t>TC_SEL_003 - Verify registration validation with existing email</t>
+  </si>
+  <si>
+    <t>6:02:17 PM</t>
+  </si>
+  <si>
+    <t>6:02:21 PM</t>
+  </si>
+  <si>
+    <t>2.28s</t>
+  </si>
+  <si>
+    <t>TC_SEL_004</t>
+  </si>
+  <si>
+    <t>TC_SEL_004 - Verify registration invalid password constraints</t>
+  </si>
+  <si>
+    <t>6:02:27 PM</t>
+  </si>
+  <si>
+    <t>6:02:31 PM</t>
+  </si>
+  <si>
+    <t>1.68s</t>
+  </si>
+  <si>
+    <t>TC_SEL_005</t>
+  </si>
+  <si>
+    <t>TC_SEL_005 - Verify login page load</t>
+  </si>
+  <si>
+    <t>6:02:37 PM</t>
+  </si>
+  <si>
+    <t>6:02:41 PM</t>
+  </si>
+  <si>
+    <t>1.52s</t>
+  </si>
+  <si>
+    <t>TC_SEL_006</t>
+  </si>
+  <si>
+    <t>TC_SEL_006 - Verify successful login with valid credentials</t>
+  </si>
+  <si>
+    <t>6:02:47 PM</t>
+  </si>
+  <si>
+    <t>6:02:51 PM</t>
+  </si>
+  <si>
+    <t>1.18s</t>
+  </si>
+  <si>
+    <t>TC_SEL_007</t>
+  </si>
+  <si>
+    <t>TC_SEL_007 - Verify login error warning with invalid credentials</t>
+  </si>
+  <si>
+    <t>6:02:57 PM</t>
+  </si>
+  <si>
+    <t>6:03:01 PM</t>
+  </si>
+  <si>
+    <t>1.62s</t>
+  </si>
+  <si>
+    <t>TC_SEL_008</t>
+  </si>
+  <si>
+    <t>TC_SEL_008 - Verify forgot password page load</t>
+  </si>
+  <si>
+    <t>6:03:07 PM</t>
+  </si>
+  <si>
+    <t>6:03:11 PM</t>
+  </si>
+  <si>
+    <t>1.37s</t>
+  </si>
+  <si>
+    <t>TC_SEL_009</t>
+  </si>
+  <si>
+    <t>TC_SEL_009 - Verify forgot password email submission</t>
+  </si>
+  <si>
+    <t>6:03:17 PM</t>
+  </si>
+  <si>
+    <t>6:03:21 PM</t>
+  </si>
+  <si>
+    <t>2.89s</t>
+  </si>
+  <si>
+    <t>TC_SEL_010</t>
+  </si>
+  <si>
+    <t>Transactions</t>
+  </si>
+  <si>
+    <t>TC_SEL_010 - Verify dashboard load and initial welcome metrics</t>
+  </si>
+  <si>
+    <t>6:03:27 PM</t>
+  </si>
+  <si>
+    <t>6:03:31 PM</t>
+  </si>
+  <si>
+    <t>2.02s</t>
+  </si>
+  <si>
+    <t>TC_SEL_011</t>
+  </si>
+  <si>
+    <t>TC_SEL_011 - Verify add income transaction</t>
+  </si>
+  <si>
+    <t>6:03:37 PM</t>
+  </si>
+  <si>
+    <t>6:03:41 PM</t>
+  </si>
+  <si>
+    <t>1.59s</t>
+  </si>
+  <si>
+    <t>TC_SEL_012</t>
+  </si>
+  <si>
+    <t>TC_SEL_012 - Verify add expense transaction</t>
+  </si>
+  <si>
+    <t>6:03:47 PM</t>
+  </si>
+  <si>
+    <t>6:03:51 PM</t>
+  </si>
+  <si>
+    <t>1.85s</t>
+  </si>
+  <si>
+    <t>TC_SEL_013</t>
+  </si>
+  <si>
+    <t>TC_SEL_013 - Verify transaction field input sanitization</t>
+  </si>
+  <si>
+    <t>6:03:57 PM</t>
+  </si>
+  <si>
+    <t>6:04:01 PM</t>
+  </si>
+  <si>
+    <t>1.22s</t>
+  </si>
+  <si>
+    <t>TC_SEL_014</t>
+  </si>
+  <si>
+    <t>TC_SEL_014 - Verify edit transaction title</t>
+  </si>
+  <si>
+    <t>6:04:07 PM</t>
+  </si>
+  <si>
+    <t>6:04:11 PM</t>
+  </si>
+  <si>
+    <t>1.63s</t>
+  </si>
+  <si>
+    <t>TC_SEL_015</t>
+  </si>
+  <si>
+    <t>TC_SEL_015 - Verify edit transaction amount and category updates</t>
+  </si>
+  <si>
+    <t>6:04:17 PM</t>
+  </si>
+  <si>
+    <t>6:04:21 PM</t>
+  </si>
+  <si>
+    <t>1.26s</t>
+  </si>
+  <si>
+    <t>TC_SEL_016</t>
+  </si>
+  <si>
+    <t>TC_SEL_016 - Verify transaction deletion and balance recalculation</t>
+  </si>
+  <si>
+    <t>6:04:27 PM</t>
+  </si>
+  <si>
+    <t>6:04:31 PM</t>
+  </si>
+  <si>
+    <t>2.20s</t>
+  </si>
+  <si>
+    <t>TC_SEL_017</t>
+  </si>
+  <si>
+    <t>TC_SEL_017 - Verify search transaction by keyword</t>
+  </si>
+  <si>
+    <t>6:04:37 PM</t>
+  </si>
+  <si>
+    <t>6:04:41 PM</t>
+  </si>
+  <si>
+    <t>1.32s</t>
+  </si>
+  <si>
+    <t>TC_SEL_018</t>
+  </si>
+  <si>
+    <t>TC_SEL_018 - Verify filter transactions by category</t>
+  </si>
+  <si>
+    <t>6:04:47 PM</t>
+  </si>
+  <si>
+    <t>6:04:51 PM</t>
+  </si>
+  <si>
+    <t>2.80s</t>
+  </si>
+  <si>
+    <t>TC_SEL_019</t>
+  </si>
+  <si>
+    <t>TC_SEL_019 - Verify filter transactions by date ranges</t>
+  </si>
+  <si>
+    <t>6:04:57 PM</t>
+  </si>
+  <si>
+    <t>6:05:01 PM</t>
+  </si>
+  <si>
+    <t>1.12s</t>
+  </si>
+  <si>
+    <t>TC_SEL_020</t>
+  </si>
+  <si>
+    <t>TC_SEL_020 - Verify sort transactions by date ascending/descending</t>
+  </si>
+  <si>
+    <t>6:05:07 PM</t>
+  </si>
+  <si>
+    <t>6:05:11 PM</t>
+  </si>
+  <si>
+    <t>2.29s</t>
+  </si>
+  <si>
+    <t>TC_SEL_021</t>
+  </si>
+  <si>
+    <t>TC_SEL_021 - Verify sort transactions by amount ascending/descending</t>
+  </si>
+  <si>
+    <t>6:05:17 PM</t>
+  </si>
+  <si>
+    <t>6:05:21 PM</t>
+  </si>
+  <si>
+    <t>2.81s</t>
+  </si>
+  <si>
+    <t>TC_SEL_022</t>
+  </si>
+  <si>
+    <t>Budget</t>
+  </si>
+  <si>
+    <t>TC_SEL_022 - Verify monthly budget creation and save button</t>
+  </si>
+  <si>
+    <t>6:05:27 PM</t>
+  </si>
+  <si>
+    <t>6:05:31 PM</t>
+  </si>
+  <si>
+    <t>1.66s</t>
+  </si>
+  <si>
+    <t>TC_SEL_023</t>
+  </si>
+  <si>
+    <t>TC_SEL_023 - Verify budget progress bar updates on transactions</t>
+  </si>
+  <si>
+    <t>6:05:37 PM</t>
+  </si>
+  <si>
+    <t>6:05:41 PM</t>
+  </si>
+  <si>
+    <t>1.84s</t>
+  </si>
+  <si>
+    <t>TC_SEL_024</t>
+  </si>
+  <si>
+    <t>Reports</t>
+  </si>
+  <si>
+    <t>TC_SEL_024 - Verify monthly PDF report generation</t>
+  </si>
+  <si>
+    <t>6:05:47 PM</t>
+  </si>
+  <si>
+    <t>6:05:51 PM</t>
+  </si>
+  <si>
+    <t>1.50s</t>
+  </si>
+  <si>
+    <t>TC_SEL_025</t>
+  </si>
+  <si>
+    <t>TC_SEL_025 - Verify charts render correctly in reports view</t>
+  </si>
+  <si>
+    <t>6:05:57 PM</t>
+  </si>
+  <si>
+    <t>6:06:01 PM</t>
+  </si>
+  <si>
+    <t>2.65s</t>
+  </si>
+  <si>
+    <t>TC_SEL_026</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>TC_SEL_026 - Verify profile details update</t>
+  </si>
+  <si>
+    <t>6:06:07 PM</t>
+  </si>
+  <si>
+    <t>6:06:11 PM</t>
+  </si>
+  <si>
+    <t>1.55s</t>
+  </si>
+  <si>
+    <t>TC_SEL_027</t>
+  </si>
+  <si>
+    <t>TC_SEL_027 - Verify password update functionality</t>
+  </si>
+  <si>
+    <t>6:06:17 PM</t>
+  </si>
+  <si>
+    <t>6:06:21 PM</t>
+  </si>
+  <si>
+    <t>1.74s</t>
+  </si>
+  <si>
+    <t>TC_SEL_028</t>
+  </si>
+  <si>
+    <t>TC_SEL_028 - Verify currency settings updates</t>
+  </si>
+  <si>
+    <t>6:06:27 PM</t>
+  </si>
+  <si>
+    <t>6:06:31 PM</t>
+  </si>
+  <si>
+    <t>2.47s</t>
+  </si>
+  <si>
+    <t>TC_SEL_029</t>
+  </si>
+  <si>
+    <t>TC_SEL_029 - Verify session persistence on page refresh</t>
+  </si>
+  <si>
+    <t>6:06:37 PM</t>
+  </si>
+  <si>
+    <t>6:06:41 PM</t>
+  </si>
+  <si>
+    <t>TC_SEL_030</t>
+  </si>
+  <si>
+    <t>TC_SEL_030 - Verify successful user logout and redirection</t>
+  </si>
+  <si>
+    <t>6:06:47 PM</t>
+  </si>
+  <si>
+    <t>6:06:51 PM</t>
+  </si>
+  <si>
+    <t>1.64s</t>
+  </si>
+  <si>
+    <t>TC_SEL_031</t>
+  </si>
+  <si>
+    <t>TC_SEL_031 - Verify monthly PDF report download functionality</t>
+  </si>
+  <si>
+    <t>6:06:57 PM</t>
+  </si>
+  <si>
+    <t>6:07:01 PM</t>
+  </si>
+  <si>
+    <t>5.12s</t>
+  </si>
+  <si>
+    <t>TC_SEC_001</t>
+  </si>
+  <si>
+    <t>Auth Injection</t>
+  </si>
+  <si>
+    <t>TC_SEC_001 - Verify SQL injection prevention in Login email field</t>
+  </si>
+  <si>
+    <t>6:02:19 PM</t>
+  </si>
+  <si>
+    <t>6:02:22 PM</t>
+  </si>
+  <si>
+    <t>TC_SEC_002</t>
+  </si>
+  <si>
+    <t>TC_SEC_002 - Verify SQL injection prevention in Login password field</t>
+  </si>
+  <si>
+    <t>6:02:30 PM</t>
+  </si>
+  <si>
+    <t>0.53s</t>
+  </si>
+  <si>
+    <t>TC_SEC_003</t>
+  </si>
+  <si>
+    <t>TC_SEC_003 - Verify SQL injection prevention in register input fields</t>
+  </si>
+  <si>
+    <t>6:02:35 PM</t>
+  </si>
+  <si>
+    <t>6:02:38 PM</t>
+  </si>
+  <si>
+    <t>1.72s</t>
+  </si>
+  <si>
+    <t>TC_SEC_004</t>
+  </si>
+  <si>
+    <t>CSRF Prevention</t>
+  </si>
+  <si>
+    <t>TC_SEC_004 - Verify HTML / Script tag sanitization in transaction title input</t>
+  </si>
+  <si>
+    <t>6:02:43 PM</t>
+  </si>
+  <si>
+    <t>6:02:46 PM</t>
+  </si>
+  <si>
+    <t>TC_SEC_005</t>
+  </si>
+  <si>
+    <t>TC_SEC_005 - Verify sanitization of script tags in transaction category input</t>
+  </si>
+  <si>
+    <t>6:02:54 PM</t>
+  </si>
+  <si>
+    <t>0.67s</t>
+  </si>
+  <si>
+    <t>TC_SEC_006</t>
+  </si>
+  <si>
+    <t>TC_SEC_006 - Verify anti-CSRF token verification on POST transactions endpoint</t>
+  </si>
+  <si>
+    <t>6:02:59 PM</t>
+  </si>
+  <si>
+    <t>6:03:02 PM</t>
+  </si>
+  <si>
+    <t>0.70s</t>
+  </si>
+  <si>
+    <t>TC_SEC_007</t>
+  </si>
+  <si>
+    <t>TC_SEC_007 - Verify anti-CSRF token verification on DELETE budget endpoint</t>
+  </si>
+  <si>
+    <t>6:03:10 PM</t>
+  </si>
+  <si>
+    <t>1.93s</t>
+  </si>
+  <si>
+    <t>TC_SEC_008</t>
+  </si>
+  <si>
+    <t>JWT Validation</t>
+  </si>
+  <si>
+    <t>TC_SEC_008 - Verify JWT token validation with incorrect signatures</t>
+  </si>
+  <si>
+    <t>6:03:15 PM</t>
+  </si>
+  <si>
+    <t>6:03:18 PM</t>
+  </si>
+  <si>
+    <t>0.61s</t>
+  </si>
+  <si>
+    <t>TC_SEC_009</t>
+  </si>
+  <si>
+    <t>TC_SEC_009 - Verify JWT token expiration enforcement</t>
+  </si>
+  <si>
+    <t>6:03:23 PM</t>
+  </si>
+  <si>
+    <t>6:03:26 PM</t>
+  </si>
+  <si>
+    <t>1.29s</t>
+  </si>
+  <si>
+    <t>TC_SEC_010</t>
+  </si>
+  <si>
+    <t>TC_SEC_010 - Verify session timeout redirection after inactivity</t>
+  </si>
+  <si>
+    <t>6:03:34 PM</t>
+  </si>
+  <si>
+    <t>1.54s</t>
+  </si>
+  <si>
+    <t>TC_SEC_011</t>
+  </si>
+  <si>
+    <t>Access Control</t>
+  </si>
+  <si>
+    <t>TC_SEC_011 - Verify input length validations on transaction title</t>
+  </si>
+  <si>
+    <t>6:03:39 PM</t>
+  </si>
+  <si>
+    <t>6:03:42 PM</t>
+  </si>
+  <si>
+    <t>0.74s</t>
+  </si>
+  <si>
+    <t>TC_SEC_012</t>
+  </si>
+  <si>
+    <t>TC_SEC_012 - Verify negative amount validation on transaction entries</t>
+  </si>
+  <si>
+    <t>6:03:50 PM</t>
+  </si>
+  <si>
+    <t>1.35s</t>
+  </si>
+  <si>
+    <t>TC_SEC_013</t>
+  </si>
+  <si>
+    <t>TC_SEC_013 - Verify non-numeric input rejection on budget amounts</t>
+  </si>
+  <si>
+    <t>6:03:55 PM</t>
+  </si>
+  <si>
+    <t>6:03:58 PM</t>
   </si>
   <si>
     <t>1.90s</t>
   </si>
   <si>
-    <t>TC_SEL_003</t>
-  </si>
-  <si>
-    <t>TC_SEL_003 - Verify registration validation with existing email</t>
-  </si>
-  <si>
-    <t>5:40:22 PM</t>
-  </si>
-  <si>
-    <t>5:40:26 PM</t>
-  </si>
-  <si>
-    <t>2.31s</t>
-  </si>
-  <si>
-    <t>TC_SEL_004</t>
-  </si>
-  <si>
-    <t>TC_SEL_004 - Verify registration invalid password constraints</t>
-  </si>
-  <si>
-    <t>5:40:32 PM</t>
-  </si>
-  <si>
-    <t>5:40:36 PM</t>
-  </si>
-  <si>
-    <t>2.14s</t>
-  </si>
-  <si>
-    <t>TC_SEL_005</t>
-  </si>
-  <si>
-    <t>TC_SEL_005 - Verify login page load</t>
-  </si>
-  <si>
-    <t>5:40:42 PM</t>
-  </si>
-  <si>
-    <t>5:40:46 PM</t>
-  </si>
-  <si>
-    <t>2.25s</t>
-  </si>
-  <si>
-    <t>TC_SEL_006</t>
-  </si>
-  <si>
-    <t>TC_SEL_006 - Verify successful login with valid credentials</t>
-  </si>
-  <si>
-    <t>5:40:52 PM</t>
-  </si>
-  <si>
-    <t>5:40:56 PM</t>
-  </si>
-  <si>
-    <t>1.32s</t>
-  </si>
-  <si>
-    <t>TC_SEL_007</t>
-  </si>
-  <si>
-    <t>TC_SEL_007 - Verify login error warning with invalid credentials</t>
-  </si>
-  <si>
-    <t>5:41:02 PM</t>
-  </si>
-  <si>
-    <t>5:41:06 PM</t>
+    <t>TC_SEC_014</t>
+  </si>
+  <si>
+    <t>TC_SEC_014 - Verify authorization checks for transaction deletion</t>
+  </si>
+  <si>
+    <t>6:04:03 PM</t>
+  </si>
+  <si>
+    <t>6:04:06 PM</t>
+  </si>
+  <si>
+    <t>1.69s</t>
+  </si>
+  <si>
+    <t>TC_SEC_015</t>
+  </si>
+  <si>
+    <t>TC_SEC_015 - Verify access control: guest user cannot access dashboard API</t>
+  </si>
+  <si>
+    <t>6:04:14 PM</t>
+  </si>
+  <si>
+    <t>1.99s</t>
+  </si>
+  <si>
+    <t>TC_SEC_016</t>
+  </si>
+  <si>
+    <t>TC_SEC_016 - Verify access control: user cannot view other users transactions</t>
+  </si>
+  <si>
+    <t>6:04:19 PM</t>
+  </si>
+  <si>
+    <t>6:04:22 PM</t>
+  </si>
+  <si>
+    <t>0.60s</t>
+  </si>
+  <si>
+    <t>TC_SEC_017</t>
+  </si>
+  <si>
+    <t>TC_SEC_017 - Verify password hash complexity strength check</t>
+  </si>
+  <si>
+    <t>6:04:30 PM</t>
+  </si>
+  <si>
+    <t>0.84s</t>
+  </si>
+  <si>
+    <t>TC_SEC_018</t>
+  </si>
+  <si>
+    <t>TC_SEC_018 - Verify file upload size validations</t>
+  </si>
+  <si>
+    <t>6:04:35 PM</t>
+  </si>
+  <si>
+    <t>6:04:38 PM</t>
+  </si>
+  <si>
+    <t>0.97s</t>
+  </si>
+  <si>
+    <t>TC_SEC_019</t>
+  </si>
+  <si>
+    <t>TC_SEC_019 - Verify file upload extension whitelist block (.sh, .exe, .js)</t>
+  </si>
+  <si>
+    <t>6:04:43 PM</t>
+  </si>
+  <si>
+    <t>6:04:46 PM</t>
+  </si>
+  <si>
+    <t>1.31s</t>
+  </si>
+  <si>
+    <t>TC_SEC_020</t>
+  </si>
+  <si>
+    <t>TC_SEC_020 - Verify API authorization on budgets edit endpoint</t>
+  </si>
+  <si>
+    <t>6:04:54 PM</t>
+  </si>
+  <si>
+    <t>0.79s</t>
+  </si>
+  <si>
+    <t>TC_SEC_021</t>
+  </si>
+  <si>
+    <t>HTTP Headers</t>
+  </si>
+  <si>
+    <t>TC_SEC_021 - Verify CORS policy matches trusted domains only</t>
+  </si>
+  <si>
+    <t>6:04:59 PM</t>
+  </si>
+  <si>
+    <t>6:05:02 PM</t>
+  </si>
+  <si>
+    <t>1.13s</t>
+  </si>
+  <si>
+    <t>TC_SEC_022</t>
+  </si>
+  <si>
+    <t>TC_SEC_022 - Verify X-Frame-Options: SAMEORIGIN header presence</t>
+  </si>
+  <si>
+    <t>6:05:10 PM</t>
+  </si>
+  <si>
+    <t>1.27s</t>
+  </si>
+  <si>
+    <t>TC_SEC_023</t>
+  </si>
+  <si>
+    <t>TC_SEC_023 - Verify X-Content-Type-Options: nosniff header presence</t>
+  </si>
+  <si>
+    <t>6:05:15 PM</t>
+  </si>
+  <si>
+    <t>6:05:18 PM</t>
+  </si>
+  <si>
+    <t>1.57s</t>
+  </si>
+  <si>
+    <t>TC_SEC_024</t>
+  </si>
+  <si>
+    <t>TC_SEC_024 - Verify Strict-Transport-Security header presence</t>
+  </si>
+  <si>
+    <t>6:05:23 PM</t>
+  </si>
+  <si>
+    <t>6:05:26 PM</t>
+  </si>
+  <si>
+    <t>1.43s</t>
+  </si>
+  <si>
+    <t>TC_SEC_025</t>
+  </si>
+  <si>
+    <t>TC_SEC_025 - Verify Content-Security-Policy header presence</t>
+  </si>
+  <si>
+    <t>6:05:34 PM</t>
+  </si>
+  <si>
+    <t>0.92s</t>
+  </si>
+  <si>
+    <t>TC_SEC_026</t>
+  </si>
+  <si>
+    <t>TC_SEC_026 - Verify secure cookie attributes (HttpOnly, Secure)</t>
+  </si>
+  <si>
+    <t>6:05:39 PM</t>
+  </si>
+  <si>
+    <t>6:05:42 PM</t>
+  </si>
+  <si>
+    <t>TC_SEC_027</t>
+  </si>
+  <si>
+    <t>TC_SEC_027 - Verify rate limiting protection on authentication endpoints</t>
+  </si>
+  <si>
+    <t>6:05:50 PM</t>
+  </si>
+  <si>
+    <t>TC_SEC_028</t>
+  </si>
+  <si>
+    <t>TC_SEC_028 - Verify dependency vulnerabilities with npm audit</t>
+  </si>
+  <si>
+    <t>6:05:55 PM</t>
+  </si>
+  <si>
+    <t>6:05:58 PM</t>
+  </si>
+  <si>
+    <t>1.42s</t>
+  </si>
+  <si>
+    <t>TC_SEC_029</t>
+  </si>
+  <si>
+    <t>TC_SEC_029 - Verify OWASP ZAP active scanning summary</t>
+  </si>
+  <si>
+    <t>6:06:03 PM</t>
+  </si>
+  <si>
+    <t>6:06:06 PM</t>
+  </si>
+  <si>
+    <t>TC_SEC_030</t>
+  </si>
+  <si>
+    <t>TC_SEC_030 - Verify TLS version compliance checking</t>
+  </si>
+  <si>
+    <t>6:06:14 PM</t>
+  </si>
+  <si>
+    <t>8.50s</t>
+  </si>
+  <si>
+    <t>TC_SEC_031</t>
+  </si>
+  <si>
+    <t>TC_SEC_031 - Verify API request rate limiting on forgot password</t>
+  </si>
+  <si>
+    <t>6:06:19 PM</t>
+  </si>
+  <si>
+    <t>6:06:22 PM</t>
+  </si>
+  <si>
+    <t>0.85s</t>
+  </si>
+  <si>
+    <t>TC_SEC_032</t>
+  </si>
+  <si>
+    <t>TC_SEC_032 - Verify secure header Referrer-Policy is set correctly</t>
+  </si>
+  <si>
+    <t>6:06:30 PM</t>
   </si>
   <si>
     <t>1.53s</t>
   </si>
   <si>
-    <t>TC_SEL_008</t>
-  </si>
-  <si>
-    <t>TC_SEL_008 - Verify forgot password page load</t>
-  </si>
-  <si>
-    <t>5:41:12 PM</t>
-  </si>
-  <si>
-    <t>5:41:16 PM</t>
-  </si>
-  <si>
-    <t>2.21s</t>
-  </si>
-  <si>
-    <t>TC_SEL_009</t>
-  </si>
-  <si>
-    <t>TC_SEL_009 - Verify forgot password email submission</t>
-  </si>
-  <si>
-    <t>5:41:22 PM</t>
-  </si>
-  <si>
-    <t>5:41:26 PM</t>
-  </si>
-  <si>
-    <t>1.51s</t>
-  </si>
-  <si>
-    <t>TC_SEL_010</t>
-  </si>
-  <si>
-    <t>Transactions</t>
-  </si>
-  <si>
-    <t>TC_SEL_010 - Verify dashboard load and initial welcome metrics</t>
-  </si>
-  <si>
-    <t>5:41:32 PM</t>
-  </si>
-  <si>
-    <t>5:41:36 PM</t>
-  </si>
-  <si>
-    <t>1.29s</t>
-  </si>
-  <si>
-    <t>TC_SEL_011</t>
-  </si>
-  <si>
-    <t>TC_SEL_011 - Verify add income transaction</t>
-  </si>
-  <si>
-    <t>5:41:42 PM</t>
-  </si>
-  <si>
-    <t>5:41:46 PM</t>
-  </si>
-  <si>
-    <t>2.93s</t>
-  </si>
-  <si>
-    <t>TC_SEL_012</t>
-  </si>
-  <si>
-    <t>TC_SEL_012 - Verify add expense transaction</t>
-  </si>
-  <si>
-    <t>5:41:52 PM</t>
-  </si>
-  <si>
-    <t>5:41:56 PM</t>
-  </si>
-  <si>
-    <t>1.99s</t>
-  </si>
-  <si>
-    <t>TC_SEL_013</t>
-  </si>
-  <si>
-    <t>TC_SEL_013 - Verify transaction field input sanitization</t>
-  </si>
-  <si>
-    <t>5:42:02 PM</t>
-  </si>
-  <si>
-    <t>5:42:06 PM</t>
-  </si>
-  <si>
-    <t>2.64s</t>
-  </si>
-  <si>
-    <t>TC_SEL_014</t>
-  </si>
-  <si>
-    <t>TC_SEL_014 - Verify edit transaction title</t>
-  </si>
-  <si>
-    <t>5:42:12 PM</t>
-  </si>
-  <si>
-    <t>5:42:16 PM</t>
-  </si>
-  <si>
-    <t>2.36s</t>
-  </si>
-  <si>
-    <t>TC_SEL_015</t>
-  </si>
-  <si>
-    <t>TC_SEL_015 - Verify edit transaction amount and category updates</t>
-  </si>
-  <si>
-    <t>5:42:22 PM</t>
-  </si>
-  <si>
-    <t>5:42:26 PM</t>
-  </si>
-  <si>
-    <t>2.92s</t>
-  </si>
-  <si>
-    <t>TC_SEL_016</t>
-  </si>
-  <si>
-    <t>TC_SEL_016 - Verify transaction deletion and balance recalculation</t>
-  </si>
-  <si>
-    <t>5:42:32 PM</t>
-  </si>
-  <si>
-    <t>5:42:36 PM</t>
-  </si>
-  <si>
-    <t>1.96s</t>
-  </si>
-  <si>
-    <t>TC_SEL_017</t>
-  </si>
-  <si>
-    <t>TC_SEL_017 - Verify search transaction by keyword</t>
-  </si>
-  <si>
-    <t>5:42:42 PM</t>
-  </si>
-  <si>
-    <t>5:42:46 PM</t>
+    <t>TC_SEC_033</t>
+  </si>
+  <si>
+    <t>TC_SEC_033 - Verify session cookie path restricts access to domain</t>
+  </si>
+  <si>
+    <t>6:06:35 PM</t>
+  </si>
+  <si>
+    <t>6:06:38 PM</t>
+  </si>
+  <si>
+    <t>1.81s</t>
+  </si>
+  <si>
+    <t>TC_SEC_034</t>
+  </si>
+  <si>
+    <t>TC_SEC_034 - Verify brute force lockout mechanism on login</t>
+  </si>
+  <si>
+    <t>6:06:43 PM</t>
+  </si>
+  <si>
+    <t>6:06:46 PM</t>
+  </si>
+  <si>
+    <t>1.48s</t>
+  </si>
+  <si>
+    <t>TC_SEC_035</t>
+  </si>
+  <si>
+    <t>TC_SEC_035 - Verify encryption of sensitive user payload at rest</t>
+  </si>
+  <si>
+    <t>6:06:54 PM</t>
+  </si>
+  <si>
+    <t>1.82s</t>
+  </si>
+  <si>
+    <t>TC_SEC_036</t>
+  </si>
+  <si>
+    <t>TC_SEC_036 - Verify sanitization of file names on file system upload</t>
+  </si>
+  <si>
+    <t>6:06:59 PM</t>
+  </si>
+  <si>
+    <t>6:07:02 PM</t>
+  </si>
+  <si>
+    <t>0.95s</t>
+  </si>
+  <si>
+    <t>TC_APP_001</t>
+  </si>
+  <si>
+    <t>Mobile Onboarding</t>
+  </si>
+  <si>
+    <t>TC_APP_001 - Verify App Launch activity loads successfully</t>
+  </si>
+  <si>
+    <t>6:01:07 PM</t>
+  </si>
+  <si>
+    <t>6:01:13 PM</t>
+  </si>
+  <si>
+    <t>3.93s</t>
+  </si>
+  <si>
+    <t>TC_APP_002</t>
+  </si>
+  <si>
+    <t>TC_APP_002 - Verify splash screen transition duration</t>
+  </si>
+  <si>
+    <t>6:01:19 PM</t>
+  </si>
+  <si>
+    <t>6:01:25 PM</t>
+  </si>
+  <si>
+    <t>TC_APP_003</t>
+  </si>
+  <si>
+    <t>TC_APP_003 - Verify registration page display inside app</t>
+  </si>
+  <si>
+    <t>6:01:31 PM</t>
+  </si>
+  <si>
+    <t>6:01:37 PM</t>
+  </si>
+  <si>
+    <t>3.05s</t>
+  </si>
+  <si>
+    <t>TC_APP_004</t>
+  </si>
+  <si>
+    <t>TC_APP_004 - Verify new account registration via mobile form</t>
+  </si>
+  <si>
+    <t>6:01:43 PM</t>
+  </si>
+  <si>
+    <t>6:01:49 PM</t>
+  </si>
+  <si>
+    <t>3.91s</t>
+  </si>
+  <si>
+    <t>TC_APP_005</t>
+  </si>
+  <si>
+    <t>TC_APP_005 - Verify app displays validation errors on registration</t>
+  </si>
+  <si>
+    <t>6:01:55 PM</t>
+  </si>
+  <si>
+    <t>2.57s</t>
+  </si>
+  <si>
+    <t>TC_APP_006</t>
+  </si>
+  <si>
+    <t>TC_APP_006 - Verify Login screen load and fields check</t>
+  </si>
+  <si>
+    <t>6:02:13 PM</t>
+  </si>
+  <si>
+    <t>4.97s</t>
+  </si>
+  <si>
+    <t>TC_APP_007</t>
+  </si>
+  <si>
+    <t>TC_APP_007 - Verify successful authentication with valid credentials</t>
+  </si>
+  <si>
+    <t>6:02:25 PM</t>
+  </si>
+  <si>
+    <t>3.60s</t>
+  </si>
+  <si>
+    <t>TC_APP_008</t>
+  </si>
+  <si>
+    <t>TC_APP_008 - Verify authentication rejection and toast notification</t>
+  </si>
+  <si>
+    <t>4.83s</t>
+  </si>
+  <si>
+    <t>TC_APP_009</t>
+  </si>
+  <si>
+    <t>Transactions Activity</t>
+  </si>
+  <si>
+    <t>TC_APP_009 - Verify dashboard page layout and toolbar items</t>
+  </si>
+  <si>
+    <t>6:02:49 PM</t>
+  </si>
+  <si>
+    <t>2.35s</t>
+  </si>
+  <si>
+    <t>TC_APP_010</t>
+  </si>
+  <si>
+    <t>TC_APP_010 - Verify scroll and swipe in navigation drawer</t>
+  </si>
+  <si>
+    <t>6:02:55 PM</t>
+  </si>
+  <si>
+    <t>2.44s</t>
+  </si>
+  <si>
+    <t>TC_APP_011</t>
+  </si>
+  <si>
+    <t>TC_APP_011 - Verify add income input dialog form</t>
+  </si>
+  <si>
+    <t>6:03:13 PM</t>
+  </si>
+  <si>
+    <t>2.19s</t>
+  </si>
+  <si>
+    <t>TC_APP_012</t>
+  </si>
+  <si>
+    <t>TC_APP_012 - Verify add income form submission and balance update</t>
+  </si>
+  <si>
+    <t>6:03:19 PM</t>
+  </si>
+  <si>
+    <t>6:03:25 PM</t>
+  </si>
+  <si>
+    <t>2.42s</t>
+  </si>
+  <si>
+    <t>TC_APP_013</t>
+  </si>
+  <si>
+    <t>TC_APP_013 - Verify add expense input dialog form</t>
+  </si>
+  <si>
+    <t>2.22s</t>
+  </si>
+  <si>
+    <t>TC_APP_014</t>
+  </si>
+  <si>
+    <t>TC_APP_014 - Verify add expense form submission and balance update</t>
+  </si>
+  <si>
+    <t>6:03:43 PM</t>
+  </si>
+  <si>
+    <t>6:03:49 PM</t>
+  </si>
+  <si>
+    <t>4.59s</t>
+  </si>
+  <si>
+    <t>TC_APP_015</t>
+  </si>
+  <si>
+    <t>TC_APP_015 - Verify edit transaction activity opens with details pre-filled</t>
+  </si>
+  <si>
+    <t>4.70s</t>
+  </si>
+  <si>
+    <t>TC_APP_016</t>
+  </si>
+  <si>
+    <t>TC_APP_016 - Verify transaction title update and save action</t>
+  </si>
+  <si>
+    <t>6:04:13 PM</t>
+  </si>
+  <si>
+    <t>2.33s</t>
+  </si>
+  <si>
+    <t>TC_APP_017</t>
+  </si>
+  <si>
+    <t>TC_APP_017 - Verify transaction deletion click and alert dialog confirmation</t>
+  </si>
+  <si>
+    <t>6:04:25 PM</t>
+  </si>
+  <si>
+    <t>4.40s</t>
+  </si>
+  <si>
+    <t>TC_APP_018</t>
+  </si>
+  <si>
+    <t>TC_APP_018 - Verify search transaction input box filters list</t>
   </si>
   <si>
     <t>2.41s</t>
   </si>
   <si>
-    <t>TC_SEL_018</t>
-  </si>
-  <si>
-    <t>TC_SEL_018 - Verify filter transactions by category</t>
-  </si>
-  <si>
-    <t>5:42:52 PM</t>
-  </si>
-  <si>
-    <t>5:42:56 PM</t>
-  </si>
-  <si>
-    <t>2.18s</t>
-  </si>
-  <si>
-    <t>TC_SEL_019</t>
-  </si>
-  <si>
-    <t>TC_SEL_019 - Verify filter transactions by date ranges</t>
-  </si>
-  <si>
-    <t>5:43:02 PM</t>
-  </si>
-  <si>
-    <t>5:43:06 PM</t>
-  </si>
-  <si>
-    <t>2.60s</t>
-  </si>
-  <si>
-    <t>TC_SEL_020</t>
-  </si>
-  <si>
-    <t>TC_SEL_020 - Verify sort transactions by date ascending/descending</t>
-  </si>
-  <si>
-    <t>5:43:12 PM</t>
-  </si>
-  <si>
-    <t>5:43:16 PM</t>
-  </si>
-  <si>
-    <t>TC_SEL_021</t>
-  </si>
-  <si>
-    <t>TC_SEL_021 - Verify sort transactions by amount ascending/descending</t>
-  </si>
-  <si>
-    <t>5:43:22 PM</t>
-  </si>
-  <si>
-    <t>5:43:26 PM</t>
-  </si>
-  <si>
-    <t>1.20s</t>
-  </si>
-  <si>
-    <t>TC_SEL_022</t>
-  </si>
-  <si>
-    <t>Budget</t>
-  </si>
-  <si>
-    <t>TC_SEL_022 - Verify monthly budget creation and save button</t>
-  </si>
-  <si>
-    <t>5:43:32 PM</t>
-  </si>
-  <si>
-    <t>5:43:36 PM</t>
-  </si>
-  <si>
-    <t>1.77s</t>
-  </si>
-  <si>
-    <t>TC_SEL_023</t>
-  </si>
-  <si>
-    <t>TC_SEL_023 - Verify budget progress bar updates on transactions</t>
-  </si>
-  <si>
-    <t>5:43:42 PM</t>
-  </si>
-  <si>
-    <t>5:43:46 PM</t>
-  </si>
-  <si>
-    <t>1.73s</t>
-  </si>
-  <si>
-    <t>TC_SEL_024</t>
-  </si>
-  <si>
-    <t>Reports</t>
-  </si>
-  <si>
-    <t>TC_SEL_024 - Verify monthly PDF report generation</t>
-  </si>
-  <si>
-    <t>5:43:52 PM</t>
-  </si>
-  <si>
-    <t>5:43:56 PM</t>
-  </si>
-  <si>
-    <t>2.98s</t>
-  </si>
-  <si>
-    <t>TC_SEL_025</t>
-  </si>
-  <si>
-    <t>TC_SEL_025 - Verify charts render correctly in reports view</t>
-  </si>
-  <si>
-    <t>5:44:02 PM</t>
-  </si>
-  <si>
-    <t>5:44:06 PM</t>
-  </si>
-  <si>
-    <t>2.39s</t>
-  </si>
-  <si>
-    <t>TC_SEL_026</t>
-  </si>
-  <si>
-    <t>Profile</t>
-  </si>
-  <si>
-    <t>TC_SEL_026 - Verify profile details update</t>
-  </si>
-  <si>
-    <t>5:44:12 PM</t>
-  </si>
-  <si>
-    <t>5:44:16 PM</t>
-  </si>
-  <si>
-    <t>TC_SEL_027</t>
-  </si>
-  <si>
-    <t>TC_SEL_027 - Verify password update functionality</t>
-  </si>
-  <si>
-    <t>5:44:22 PM</t>
-  </si>
-  <si>
-    <t>5:44:26 PM</t>
-  </si>
-  <si>
-    <t>1.89s</t>
-  </si>
-  <si>
-    <t>TC_SEL_028</t>
-  </si>
-  <si>
-    <t>TC_SEL_028 - Verify currency settings updates</t>
-  </si>
-  <si>
-    <t>5:44:32 PM</t>
-  </si>
-  <si>
-    <t>5:44:36 PM</t>
-  </si>
-  <si>
-    <t>2.73s</t>
-  </si>
-  <si>
-    <t>TC_SEL_029</t>
-  </si>
-  <si>
-    <t>TC_SEL_029 - Verify session persistence on page refresh</t>
-  </si>
-  <si>
-    <t>5:44:42 PM</t>
-  </si>
-  <si>
-    <t>5:44:46 PM</t>
-  </si>
-  <si>
-    <t>1.37s</t>
-  </si>
-  <si>
-    <t>TC_SEL_030</t>
-  </si>
-  <si>
-    <t>TC_SEL_030 - Verify successful user logout and redirection</t>
-  </si>
-  <si>
-    <t>5:44:52 PM</t>
-  </si>
-  <si>
-    <t>5:44:56 PM</t>
-  </si>
-  <si>
-    <t>1.57s</t>
-  </si>
-  <si>
-    <t>TC_SEL_031</t>
-  </si>
-  <si>
-    <t>TC_SEL_031 - Verify currency settings updates in layout</t>
-  </si>
-  <si>
-    <t>5:45:02 PM</t>
-  </si>
-  <si>
-    <t>5:45:06 PM</t>
-  </si>
-  <si>
-    <t>1.08s</t>
-  </si>
-  <si>
-    <t>TC_SEL_032</t>
-  </si>
-  <si>
-    <t>TC_SEL_032 - Verify monthly budget limit notifications triggers</t>
-  </si>
-  <si>
-    <t>5:45:12 PM</t>
-  </si>
-  <si>
-    <t>5:45:16 PM</t>
-  </si>
-  <si>
-    <t>2.16s</t>
-  </si>
-  <si>
-    <t>TC_SEL_033</t>
-  </si>
-  <si>
-    <t>TC_SEL_033 - Verify monthly PDF report download functionality</t>
-  </si>
-  <si>
-    <t>5:45:22 PM</t>
-  </si>
-  <si>
-    <t>5:45:26 PM</t>
-  </si>
-  <si>
-    <t>5.12s</t>
-  </si>
-  <si>
-    <t>TC_SEC_001</t>
-  </si>
-  <si>
-    <t>Auth Injection</t>
-  </si>
-  <si>
-    <t>TC_SEC_001 - Verify SQL injection prevention in Login email field</t>
-  </si>
-  <si>
-    <t>5:40:44 PM</t>
-  </si>
-  <si>
-    <t>5:40:47 PM</t>
-  </si>
-  <si>
-    <t>1.00s</t>
-  </si>
-  <si>
-    <t>TC_SEC_002</t>
-  </si>
-  <si>
-    <t>TC_SEC_002 - Verify SQL injection prevention in Login password field</t>
-  </si>
-  <si>
-    <t>5:40:55 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_003</t>
-  </si>
-  <si>
-    <t>TC_SEC_003 - Verify SQL injection prevention in register input fields</t>
-  </si>
-  <si>
-    <t>5:41:00 PM</t>
-  </si>
-  <si>
-    <t>5:41:03 PM</t>
-  </si>
-  <si>
-    <t>1.61s</t>
-  </si>
-  <si>
-    <t>TC_SEC_004</t>
-  </si>
-  <si>
-    <t>CSRF Prevention</t>
-  </si>
-  <si>
-    <t>TC_SEC_004 - Verify HTML / Script tag sanitization in transaction title input</t>
-  </si>
-  <si>
-    <t>5:41:08 PM</t>
-  </si>
-  <si>
-    <t>5:41:11 PM</t>
-  </si>
-  <si>
-    <t>1.11s</t>
-  </si>
-  <si>
-    <t>TC_SEC_005</t>
-  </si>
-  <si>
-    <t>TC_SEC_005 - Verify sanitization of script tags in transaction category input</t>
-  </si>
-  <si>
-    <t>5:41:19 PM</t>
-  </si>
-  <si>
-    <t>0.82s</t>
-  </si>
-  <si>
-    <t>TC_SEC_006</t>
-  </si>
-  <si>
-    <t>TC_SEC_006 - Verify anti-CSRF token verification on POST transactions endpoint</t>
-  </si>
-  <si>
-    <t>5:41:24 PM</t>
-  </si>
-  <si>
-    <t>5:41:27 PM</t>
-  </si>
-  <si>
-    <t>1.55s</t>
-  </si>
-  <si>
-    <t>TC_SEC_007</t>
-  </si>
-  <si>
-    <t>TC_SEC_007 - Verify anti-CSRF token verification on DELETE budget endpoint</t>
-  </si>
-  <si>
-    <t>5:41:35 PM</t>
-  </si>
-  <si>
-    <t>1.82s</t>
-  </si>
-  <si>
-    <t>TC_SEC_008</t>
-  </si>
-  <si>
-    <t>JWT Validation</t>
-  </si>
-  <si>
-    <t>TC_SEC_008 - Verify JWT token validation with incorrect signatures</t>
-  </si>
-  <si>
-    <t>5:41:40 PM</t>
-  </si>
-  <si>
-    <t>5:41:43 PM</t>
-  </si>
-  <si>
-    <t>1.84s</t>
-  </si>
-  <si>
-    <t>TC_SEC_009</t>
-  </si>
-  <si>
-    <t>TC_SEC_009 - Verify JWT token expiration enforcement</t>
-  </si>
-  <si>
-    <t>5:41:48 PM</t>
-  </si>
-  <si>
-    <t>5:41:51 PM</t>
-  </si>
-  <si>
-    <t>1.67s</t>
-  </si>
-  <si>
-    <t>TC_SEC_010</t>
-  </si>
-  <si>
-    <t>TC_SEC_010 - Verify session timeout redirection after inactivity</t>
-  </si>
-  <si>
-    <t>5:41:59 PM</t>
-  </si>
-  <si>
-    <t>0.59s</t>
-  </si>
-  <si>
-    <t>TC_SEC_011</t>
-  </si>
-  <si>
-    <t>Access Control</t>
-  </si>
-  <si>
-    <t>TC_SEC_011 - Verify input length validations on transaction title</t>
-  </si>
-  <si>
-    <t>5:42:04 PM</t>
-  </si>
-  <si>
-    <t>5:42:07 PM</t>
-  </si>
-  <si>
-    <t>1.69s</t>
-  </si>
-  <si>
-    <t>TC_SEC_012</t>
-  </si>
-  <si>
-    <t>TC_SEC_012 - Verify negative amount validation on transaction entries</t>
-  </si>
-  <si>
-    <t>5:42:15 PM</t>
-  </si>
-  <si>
-    <t>0.71s</t>
-  </si>
-  <si>
-    <t>TC_SEC_013</t>
-  </si>
-  <si>
-    <t>TC_SEC_013 - Verify non-numeric input rejection on budget amounts</t>
-  </si>
-  <si>
-    <t>5:42:20 PM</t>
-  </si>
-  <si>
-    <t>5:42:23 PM</t>
-  </si>
-  <si>
-    <t>0.53s</t>
-  </si>
-  <si>
-    <t>TC_SEC_014</t>
-  </si>
-  <si>
-    <t>TC_SEC_014 - Verify authorization checks for transaction deletion</t>
-  </si>
-  <si>
-    <t>5:42:28 PM</t>
-  </si>
-  <si>
-    <t>5:42:31 PM</t>
-  </si>
-  <si>
-    <t>0.69s</t>
-  </si>
-  <si>
-    <t>TC_SEC_015</t>
-  </si>
-  <si>
-    <t>TC_SEC_015 - Verify access control: guest user cannot access dashboard API</t>
-  </si>
-  <si>
-    <t>5:42:39 PM</t>
-  </si>
-  <si>
-    <t>1.71s</t>
-  </si>
-  <si>
-    <t>TC_SEC_016</t>
-  </si>
-  <si>
-    <t>TC_SEC_016 - Verify access control: user cannot view other users transactions</t>
-  </si>
-  <si>
-    <t>5:42:44 PM</t>
-  </si>
-  <si>
-    <t>5:42:47 PM</t>
-  </si>
-  <si>
-    <t>0.70s</t>
-  </si>
-  <si>
-    <t>TC_SEC_017</t>
-  </si>
-  <si>
-    <t>TC_SEC_017 - Verify password hash complexity strength check</t>
-  </si>
-  <si>
-    <t>5:42:55 PM</t>
-  </si>
-  <si>
-    <t>1.14s</t>
-  </si>
-  <si>
-    <t>TC_SEC_018</t>
-  </si>
-  <si>
-    <t>TC_SEC_018 - Verify file upload size validations</t>
-  </si>
-  <si>
-    <t>5:43:00 PM</t>
-  </si>
-  <si>
-    <t>5:43:03 PM</t>
-  </si>
-  <si>
-    <t>1.59s</t>
-  </si>
-  <si>
-    <t>TC_SEC_019</t>
-  </si>
-  <si>
-    <t>TC_SEC_019 - Verify file upload extension whitelist block (.sh, .exe, .js)</t>
-  </si>
-  <si>
-    <t>5:43:08 PM</t>
-  </si>
-  <si>
-    <t>5:43:11 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_020</t>
-  </si>
-  <si>
-    <t>TC_SEC_020 - Verify API authorization on budgets edit endpoint</t>
-  </si>
-  <si>
-    <t>5:43:19 PM</t>
-  </si>
-  <si>
-    <t>0.74s</t>
-  </si>
-  <si>
-    <t>TC_SEC_021</t>
-  </si>
-  <si>
-    <t>HTTP Headers</t>
-  </si>
-  <si>
-    <t>TC_SEC_021 - Verify CORS policy matches trusted domains only</t>
-  </si>
-  <si>
-    <t>5:43:24 PM</t>
-  </si>
-  <si>
-    <t>5:43:27 PM</t>
-  </si>
-  <si>
-    <t>0.79s</t>
-  </si>
-  <si>
-    <t>TC_SEC_022</t>
-  </si>
-  <si>
-    <t>TC_SEC_022 - Verify X-Frame-Options: SAMEORIGIN header presence</t>
-  </si>
-  <si>
-    <t>5:43:35 PM</t>
-  </si>
-  <si>
-    <t>0.90s</t>
-  </si>
-  <si>
-    <t>TC_SEC_023</t>
-  </si>
-  <si>
-    <t>TC_SEC_023 - Verify X-Content-Type-Options: nosniff header presence</t>
-  </si>
-  <si>
-    <t>5:43:40 PM</t>
-  </si>
-  <si>
-    <t>5:43:43 PM</t>
-  </si>
-  <si>
-    <t>1.80s</t>
-  </si>
-  <si>
-    <t>TC_SEC_024</t>
-  </si>
-  <si>
-    <t>TC_SEC_024 - Verify Strict-Transport-Security header presence</t>
-  </si>
-  <si>
-    <t>5:43:48 PM</t>
-  </si>
-  <si>
-    <t>5:43:51 PM</t>
-  </si>
-  <si>
-    <t>1.52s</t>
-  </si>
-  <si>
-    <t>TC_SEC_025</t>
-  </si>
-  <si>
-    <t>TC_SEC_025 - Verify Content-Security-Policy header presence</t>
-  </si>
-  <si>
-    <t>5:43:59 PM</t>
-  </si>
-  <si>
-    <t>1.93s</t>
-  </si>
-  <si>
-    <t>TC_SEC_026</t>
-  </si>
-  <si>
-    <t>TC_SEC_026 - Verify secure cookie attributes (HttpOnly, Secure)</t>
-  </si>
-  <si>
-    <t>5:44:04 PM</t>
-  </si>
-  <si>
-    <t>5:44:07 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_027</t>
-  </si>
-  <si>
-    <t>TC_SEC_027 - Verify rate limiting protection on authentication endpoints</t>
-  </si>
-  <si>
-    <t>5:44:15 PM</t>
-  </si>
-  <si>
-    <t>1.68s</t>
-  </si>
-  <si>
-    <t>TC_SEC_028</t>
-  </si>
-  <si>
-    <t>TC_SEC_028 - Verify dependency vulnerabilities with npm audit</t>
-  </si>
-  <si>
-    <t>5:44:20 PM</t>
-  </si>
-  <si>
-    <t>5:44:23 PM</t>
-  </si>
-  <si>
-    <t>0.76s</t>
-  </si>
-  <si>
-    <t>TC_SEC_029</t>
-  </si>
-  <si>
-    <t>TC_SEC_029 - Verify OWASP ZAP active scanning summary</t>
-  </si>
-  <si>
-    <t>5:44:28 PM</t>
-  </si>
-  <si>
-    <t>5:44:31 PM</t>
-  </si>
-  <si>
-    <t>1.09s</t>
-  </si>
-  <si>
-    <t>TC_SEC_030</t>
-  </si>
-  <si>
-    <t>TC_SEC_030 - Verify TLS version compliance checking</t>
-  </si>
-  <si>
-    <t>5:44:39 PM</t>
-  </si>
-  <si>
-    <t>8.50s</t>
-  </si>
-  <si>
-    <t>TC_SEC_031</t>
-  </si>
-  <si>
-    <t>TC_SEC_031 - Verify API request rate limiting on forgot password</t>
-  </si>
-  <si>
-    <t>5:44:44 PM</t>
-  </si>
-  <si>
-    <t>5:44:47 PM</t>
-  </si>
-  <si>
-    <t>1.12s</t>
-  </si>
-  <si>
-    <t>TC_SEC_032</t>
-  </si>
-  <si>
-    <t>TC_SEC_032 - Verify secure header Referrer-Policy is set correctly</t>
-  </si>
-  <si>
-    <t>5:44:55 PM</t>
-  </si>
-  <si>
-    <t>0.84s</t>
-  </si>
-  <si>
-    <t>TC_SEC_033</t>
-  </si>
-  <si>
-    <t>TC_SEC_033 - Verify session cookie path restricts access to domain</t>
-  </si>
-  <si>
-    <t>5:45:00 PM</t>
-  </si>
-  <si>
-    <t>5:45:03 PM</t>
-  </si>
-  <si>
-    <t>1.30s</t>
-  </si>
-  <si>
-    <t>TC_SEC_034</t>
-  </si>
-  <si>
-    <t>TC_SEC_034 - Verify brute force lockout mechanism on login</t>
-  </si>
-  <si>
-    <t>5:45:08 PM</t>
-  </si>
-  <si>
-    <t>5:45:11 PM</t>
-  </si>
-  <si>
-    <t>TC_SEC_035</t>
-  </si>
-  <si>
-    <t>TC_SEC_035 - Verify encryption of sensitive user payload at rest</t>
-  </si>
-  <si>
-    <t>5:45:19 PM</t>
-  </si>
-  <si>
-    <t>1.91s</t>
-  </si>
-  <si>
-    <t>TC_SEC_036</t>
-  </si>
-  <si>
-    <t>TC_SEC_036 - Verify sanitization of file names on file system upload</t>
-  </si>
-  <si>
-    <t>5:45:24 PM</t>
-  </si>
-  <si>
-    <t>5:45:27 PM</t>
-  </si>
-  <si>
-    <t>1.74s</t>
-  </si>
-  <si>
-    <t>TC_APP_001</t>
-  </si>
-  <si>
-    <t>Mobile Onboarding</t>
-  </si>
-  <si>
-    <t>TC_APP_001 - Verify App Launch activity loads successfully</t>
-  </si>
-  <si>
-    <t>5:39:32 PM</t>
-  </si>
-  <si>
-    <t>5:39:38 PM</t>
-  </si>
-  <si>
-    <t>4.10s</t>
-  </si>
-  <si>
-    <t>TC_APP_002</t>
-  </si>
-  <si>
-    <t>TC_APP_002 - Verify splash screen transition duration</t>
-  </si>
-  <si>
-    <t>5:39:44 PM</t>
-  </si>
-  <si>
-    <t>5:39:50 PM</t>
-  </si>
-  <si>
-    <t>2.80s</t>
-  </si>
-  <si>
-    <t>TC_APP_003</t>
-  </si>
-  <si>
-    <t>TC_APP_003 - Verify registration page display inside app</t>
-  </si>
-  <si>
-    <t>5:39:56 PM</t>
-  </si>
-  <si>
-    <t>4.37s</t>
-  </si>
-  <si>
-    <t>TC_APP_004</t>
-  </si>
-  <si>
-    <t>TC_APP_004 - Verify new account registration via mobile form</t>
-  </si>
-  <si>
-    <t>5:40:08 PM</t>
-  </si>
-  <si>
-    <t>5:40:14 PM</t>
-  </si>
-  <si>
-    <t>4.53s</t>
-  </si>
-  <si>
-    <t>TC_APP_005</t>
-  </si>
-  <si>
-    <t>TC_APP_005 - Verify app displays validation errors on registration</t>
-  </si>
-  <si>
-    <t>5:40:20 PM</t>
-  </si>
-  <si>
-    <t>3.11s</t>
-  </si>
-  <si>
-    <t>TC_APP_006</t>
-  </si>
-  <si>
-    <t>TC_APP_006 - Verify Login screen load and fields check</t>
-  </si>
-  <si>
-    <t>5:40:38 PM</t>
-  </si>
-  <si>
-    <t>2.89s</t>
-  </si>
-  <si>
-    <t>TC_APP_007</t>
-  </si>
-  <si>
-    <t>TC_APP_007 - Verify successful authentication with valid credentials</t>
-  </si>
-  <si>
-    <t>5:40:50 PM</t>
-  </si>
-  <si>
-    <t>2.85s</t>
-  </si>
-  <si>
-    <t>TC_APP_008</t>
-  </si>
-  <si>
-    <t>TC_APP_008 - Verify authentication rejection and toast notification</t>
-  </si>
-  <si>
-    <t>3.95s</t>
-  </si>
-  <si>
-    <t>TC_APP_009</t>
-  </si>
-  <si>
-    <t>Transactions Activity</t>
-  </si>
-  <si>
-    <t>TC_APP_009 - Verify dashboard page layout and toolbar items</t>
-  </si>
-  <si>
-    <t>5:41:14 PM</t>
+    <t>TC_APP_019</t>
+  </si>
+  <si>
+    <t>Alerts OS</t>
+  </si>
+  <si>
+    <t>TC_APP_019 - Verify budget warning alerts are displayed when budget exceeded</t>
+  </si>
+  <si>
+    <t>6:04:49 PM</t>
   </si>
   <si>
     <t>4.56s</t>
   </si>
   <si>
-    <t>TC_APP_010</t>
-  </si>
-  <si>
-    <t>TC_APP_010 - Verify scroll and swipe in navigation drawer</t>
-  </si>
-  <si>
-    <t>5:41:20 PM</t>
-  </si>
-  <si>
-    <t>4.05s</t>
-  </si>
-  <si>
-    <t>TC_APP_011</t>
-  </si>
-  <si>
-    <t>TC_APP_011 - Verify add income input dialog form</t>
-  </si>
-  <si>
-    <t>5:41:38 PM</t>
-  </si>
-  <si>
-    <t>3.42s</t>
-  </si>
-  <si>
-    <t>TC_APP_012</t>
-  </si>
-  <si>
-    <t>TC_APP_012 - Verify add income form submission and balance update</t>
-  </si>
-  <si>
-    <t>5:41:44 PM</t>
-  </si>
-  <si>
-    <t>5:41:50 PM</t>
-  </si>
-  <si>
-    <t>4.72s</t>
-  </si>
-  <si>
-    <t>TC_APP_013</t>
-  </si>
-  <si>
-    <t>TC_APP_013 - Verify add expense input dialog form</t>
-  </si>
-  <si>
-    <t>3.36s</t>
-  </si>
-  <si>
-    <t>TC_APP_014</t>
-  </si>
-  <si>
-    <t>TC_APP_014 - Verify add expense form submission and balance update</t>
-  </si>
-  <si>
-    <t>5:42:08 PM</t>
-  </si>
-  <si>
-    <t>5:42:14 PM</t>
-  </si>
-  <si>
-    <t>TC_APP_015</t>
-  </si>
-  <si>
-    <t>TC_APP_015 - Verify edit transaction activity opens with details pre-filled</t>
-  </si>
-  <si>
-    <t>4.79s</t>
-  </si>
-  <si>
-    <t>TC_APP_016</t>
-  </si>
-  <si>
-    <t>TC_APP_016 - Verify transaction title update and save action</t>
-  </si>
-  <si>
-    <t>5:42:38 PM</t>
-  </si>
-  <si>
-    <t>4.43s</t>
-  </si>
-  <si>
-    <t>TC_APP_017</t>
-  </si>
-  <si>
-    <t>TC_APP_017 - Verify transaction deletion click and alert dialog confirmation</t>
-  </si>
-  <si>
-    <t>5:42:50 PM</t>
-  </si>
-  <si>
-    <t>TC_APP_018</t>
-  </si>
-  <si>
-    <t>TC_APP_018 - Verify search transaction input box filters list</t>
-  </si>
-  <si>
-    <t>4.98s</t>
-  </si>
-  <si>
-    <t>TC_APP_019</t>
-  </si>
-  <si>
-    <t>Alerts OS</t>
-  </si>
-  <si>
-    <t>TC_APP_019 - Verify budget warning alerts are displayed when budget exceeded</t>
-  </si>
-  <si>
-    <t>5:43:14 PM</t>
-  </si>
-  <si>
-    <t>2.53s</t>
-  </si>
-  <si>
     <t>TC_APP_020</t>
   </si>
   <si>
     <t>TC_APP_020 - Verify notification channel registers correctly in Android OS</t>
   </si>
   <si>
-    <t>5:43:20 PM</t>
-  </si>
-  <si>
-    <t>2.04s</t>
+    <t>6:04:55 PM</t>
+  </si>
+  <si>
+    <t>4.12s</t>
   </si>
   <si>
     <t>TC_APP_021</t>
@@ -1385,7 +1361,10 @@
     <t>TC_APP_021 - Verify app local push notification triggers on budget thresholds</t>
   </si>
   <si>
-    <t>5:43:38 PM</t>
+    <t>6:05:13 PM</t>
+  </si>
+  <si>
+    <t>3.04s</t>
   </si>
   <si>
     <t>TC_APP_022</t>
@@ -1397,13 +1376,13 @@
     <t>TC_APP_022 - Verify profile update form saves new username</t>
   </si>
   <si>
-    <t>5:43:44 PM</t>
-  </si>
-  <si>
-    <t>5:43:50 PM</t>
-  </si>
-  <si>
-    <t>2.02s</t>
+    <t>6:05:19 PM</t>
+  </si>
+  <si>
+    <t>6:05:25 PM</t>
+  </si>
+  <si>
+    <t>4.78s</t>
   </si>
   <si>
     <t>TC_APP_023</t>
@@ -1412,7 +1391,7 @@
     <t>TC_APP_023 - Verify profile image upload simulation</t>
   </si>
   <si>
-    <t>4.15s</t>
+    <t>3.86s</t>
   </si>
   <si>
     <t>TC_APP_024</t>
@@ -1421,13 +1400,13 @@
     <t>TC_APP_024 - Verify change password form validation checks</t>
   </si>
   <si>
-    <t>5:44:08 PM</t>
-  </si>
-  <si>
-    <t>5:44:14 PM</t>
-  </si>
-  <si>
-    <t>4.21s</t>
+    <t>6:05:43 PM</t>
+  </si>
+  <si>
+    <t>6:05:49 PM</t>
+  </si>
+  <si>
+    <t>2.27s</t>
   </si>
   <si>
     <t>TC_APP_025</t>
@@ -1436,16 +1415,19 @@
     <t>TC_APP_025 - Verify successful change password submission</t>
   </si>
   <si>
+    <t>2.34s</t>
+  </si>
+  <si>
     <t>TC_APP_026</t>
   </si>
   <si>
     <t>TC_APP_026 - Verify dark theme toggle works on main dashboard screen</t>
   </si>
   <si>
-    <t>5:44:38 PM</t>
-  </si>
-  <si>
-    <t>4.76s</t>
+    <t>6:06:13 PM</t>
+  </si>
+  <si>
+    <t>3.75s</t>
   </si>
   <si>
     <t>TC_APP_027</t>
@@ -1454,7 +1436,10 @@
     <t>TC_APP_027 - Verify app recovers UI states on device rotation (portrait/landscape)</t>
   </si>
   <si>
-    <t>5:44:50 PM</t>
+    <t>6:06:25 PM</t>
+  </si>
+  <si>
+    <t>2.03s</t>
   </si>
   <si>
     <t>TC_APP_028</t>
@@ -1463,7 +1448,7 @@
     <t>TC_APP_028 - Verify session recovery on backgrounding and restoring app</t>
   </si>
   <si>
-    <t>3.05s</t>
+    <t>4.58s</t>
   </si>
   <si>
     <t>TC_APP_029</t>
@@ -1472,10 +1457,7 @@
     <t>TC_APP_029 - Verify logout button click asks confirmation</t>
   </si>
   <si>
-    <t>5:45:14 PM</t>
-  </si>
-  <si>
-    <t>3.80s</t>
+    <t>6:06:49 PM</t>
   </si>
   <si>
     <t>TC_APP_030</t>
@@ -1484,7 +1466,7 @@
     <t>TC_APP_030 - Verify successful logout clears local cache database</t>
   </si>
   <si>
-    <t>5:45:20 PM</t>
+    <t>6:06:55 PM</t>
   </si>
   <si>
     <t>Test Name</t>
@@ -1529,7 +1511,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>2026-06-15T12:15:32.203Z</t>
+    <t>2026-06-15T12:37:07.269Z</t>
   </si>
   <si>
     <t>Execution of TC_SEL_001</t>
@@ -1631,19 +1613,13 @@
     <t>Execution of TC_SEL_031</t>
   </si>
   <si>
-    <t>Execution of TC_SEL_032</t>
-  </si>
-  <si>
-    <t>Execution of TC_SEL_033</t>
-  </si>
-  <si>
     <t>FAILED</t>
   </si>
   <si>
     <t>Element not interactable / button click intercepted</t>
   </si>
   <si>
-    <t>2026-06-15T12:15:32.241Z</t>
+    <t>2026-06-15T12:37:07.309Z</t>
   </si>
   <si>
     <t>Execution of TC_SEC_001</t>
@@ -1760,7 +1736,7 @@
     <t>Execution of TC_SEC_036</t>
   </si>
   <si>
-    <t>2026-06-15T12:15:32.242Z</t>
+    <t>2026-06-15T12:37:07.310Z</t>
   </si>
   <si>
     <t>Execution of TC_APP_001</t>
@@ -2439,10 +2415,10 @@
         <v>13</v>
       </c>
       <c r="E2" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F2" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G2" s="2">
         <v>1</v>
@@ -2535,10 +2511,10 @@
         <v>13</v>
       </c>
       <c r="E5" s="3">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F5" s="3">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G5" s="3">
         <v>2</v>
@@ -2561,7 +2537,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -3116,18 +3092,18 @@
         <v>137</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>12</v>
@@ -3136,24 +3112,24 @@
         <v>5</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>12</v>
@@ -3162,24 +3138,24 @@
         <v>5</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>12</v>
@@ -3188,24 +3164,24 @@
         <v>5</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>12</v>
@@ -3214,24 +3190,24 @@
         <v>5</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>12</v>
@@ -3240,24 +3216,24 @@
         <v>5</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>12</v>
@@ -3266,24 +3242,24 @@
         <v>5</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>12</v>
@@ -3292,24 +3268,24 @@
         <v>5</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>12</v>
@@ -3318,24 +3294,24 @@
         <v>5</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>12</v>
@@ -3344,24 +3320,24 @@
         <v>5</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>12</v>
@@ -3370,85 +3346,85 @@
         <v>5</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>5</v>
+      <c r="E32" s="6" t="s">
+        <v>6</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>199</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>6</v>
+        <v>17</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>5</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>202</v>
+        <v>55</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>203</v>
@@ -3462,10 +3438,10 @@
         <v>205</v>
       </c>
       <c r="B35" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>206</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>207</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>17</v>
@@ -3474,21 +3450,21 @@
         <v>5</v>
       </c>
       <c r="F35" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="H35" s="4" t="s">
         <v>209</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>206</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>212</v>
@@ -3500,24 +3476,24 @@
         <v>5</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>65</v>
+        <v>213</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>118</v>
+        <v>190</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>17</v>
@@ -3526,7 +3502,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>216</v>
+        <v>66</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>217</v>
@@ -3540,10 +3516,10 @@
         <v>219</v>
       </c>
       <c r="B38" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>220</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>221</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>17</v>
@@ -3552,24 +3528,24 @@
         <v>5</v>
       </c>
       <c r="F38" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G38" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="H38" s="4" t="s">
         <v>223</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>225</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>226</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>17</v>
@@ -3578,21 +3554,21 @@
         <v>5</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G39" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="H39" s="4" t="s">
         <v>227</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>229</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>220</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>230</v>
@@ -3618,7 +3594,7 @@
         <v>234</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>235</v>
@@ -3630,21 +3606,21 @@
         <v>5</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>86</v>
+        <v>236</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>240</v>
@@ -3656,21 +3632,21 @@
         <v>5</v>
       </c>
       <c r="F42" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G42" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="H42" s="4" t="s">
         <v>242</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B43" s="4" t="s">
         <v>244</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>239</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>245</v>
@@ -3696,7 +3672,7 @@
         <v>249</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>250</v>
@@ -3708,7 +3684,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>251</v>
@@ -3722,10 +3698,10 @@
         <v>253</v>
       </c>
       <c r="B45" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>254</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>255</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>17</v>
@@ -3734,24 +3710,24 @@
         <v>5</v>
       </c>
       <c r="F45" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="G45" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="H45" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C46" s="4" t="s">
         <v>259</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>260</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>17</v>
@@ -3760,7 +3736,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>106</v>
+        <v>260</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>261</v>
@@ -3774,7 +3750,7 @@
         <v>263</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>264</v>
@@ -3786,24 +3762,24 @@
         <v>5</v>
       </c>
       <c r="F47" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G47" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="H47" s="4" t="s">
         <v>266</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>268</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>269</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>17</v>
@@ -3812,24 +3788,24 @@
         <v>5</v>
       </c>
       <c r="F48" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G48" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="H48" s="4" t="s">
         <v>271</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>273</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>274</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>17</v>
@@ -3838,24 +3814,24 @@
         <v>5</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G49" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="H49" s="4" t="s">
         <v>275</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>277</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>278</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>17</v>
@@ -3864,24 +3840,24 @@
         <v>5</v>
       </c>
       <c r="F50" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="G50" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="G50" s="4" t="s">
+      <c r="H50" s="4" t="s">
         <v>280</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>282</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>283</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>17</v>
@@ -3890,7 +3866,7 @@
         <v>5</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>126</v>
+        <v>283</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>284</v>
@@ -3904,7 +3880,7 @@
         <v>286</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>287</v>
@@ -3916,21 +3892,21 @@
         <v>5</v>
       </c>
       <c r="F52" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G52" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="H52" s="4" t="s">
         <v>289</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B53" s="4" t="s">
         <v>291</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>254</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>292</v>
@@ -3948,18 +3924,18 @@
         <v>294</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>194</v>
+        <v>295</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>254</v>
+        <v>291</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>17</v>
@@ -3968,21 +3944,21 @@
         <v>5</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>301</v>
@@ -4008,7 +3984,7 @@
         <v>305</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>306</v>
@@ -4020,24 +3996,24 @@
         <v>5</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>146</v>
+        <v>307</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>17</v>
@@ -4046,7 +4022,7 @@
         <v>5</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>311</v>
+        <v>148</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>312</v>
@@ -4060,7 +4036,7 @@
         <v>314</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>315</v>
@@ -4078,18 +4054,18 @@
         <v>317</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>318</v>
+        <v>233</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>319</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>320</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>17</v>
@@ -4101,21 +4077,21 @@
         <v>158</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>322</v>
+        <v>275</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>17</v>
@@ -4124,24 +4100,24 @@
         <v>5</v>
       </c>
       <c r="F60" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="H60" s="4" t="s">
         <v>325</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>327</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>328</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>17</v>
@@ -4150,50 +4126,50 @@
         <v>5</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>168</v>
+        <v>328</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>329</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>330</v>
+        <v>233</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>331</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>332</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E62" s="5" t="s">
-        <v>5</v>
+      <c r="E62" s="6" t="s">
+        <v>6</v>
       </c>
       <c r="F62" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="H62" s="4" t="s">
         <v>333</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="H62" s="4" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>17</v>
@@ -4202,50 +4178,50 @@
         <v>5</v>
       </c>
       <c r="F63" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="H63" s="4" t="s">
         <v>338</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E64" s="6" t="s">
-        <v>6</v>
+      <c r="E64" s="5" t="s">
+        <v>5</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>17</v>
@@ -4254,24 +4230,24 @@
         <v>5</v>
       </c>
       <c r="F65" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="H65" s="4" t="s">
         <v>347</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="H65" s="4" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>17</v>
@@ -4280,24 +4256,24 @@
         <v>5</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>187</v>
+        <v>350</v>
       </c>
       <c r="G66" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="H66" s="4" t="s">
         <v>352</v>
-      </c>
-      <c r="H66" s="4" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C67" s="4" t="s">
         <v>354</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>355</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>17</v>
@@ -4306,24 +4282,24 @@
         <v>5</v>
       </c>
       <c r="F67" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="H67" s="4" t="s">
         <v>356</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="H67" s="4" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>17</v>
@@ -4332,65 +4308,65 @@
         <v>5</v>
       </c>
       <c r="F68" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="H68" s="4" t="s">
         <v>361</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="H68" s="4" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B69" s="4" t="s">
         <v>363</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>300</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>364</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E69" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>198</v>
+        <v>365</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>300</v>
+        <v>363</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E70" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>371</v>
+        <v>82</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -4398,10 +4374,10 @@
         <v>372</v>
       </c>
       <c r="B71" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C71" s="4" t="s">
         <v>373</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>374</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>21</v>
@@ -4410,24 +4386,24 @@
         <v>5</v>
       </c>
       <c r="F71" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="G71" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="G71" s="4" t="s">
+      <c r="H71" s="4" t="s">
         <v>376</v>
-      </c>
-      <c r="H71" s="4" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C72" s="4" t="s">
         <v>378</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>379</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>21</v>
@@ -4436,24 +4412,24 @@
         <v>5</v>
       </c>
       <c r="F72" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="G72" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="G72" s="4" t="s">
+      <c r="H72" s="4" t="s">
         <v>381</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C73" s="4" t="s">
         <v>383</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>384</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>21</v>
@@ -4462,24 +4438,24 @@
         <v>5</v>
       </c>
       <c r="F73" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H73" s="4" t="s">
         <v>385</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C74" s="4" t="s">
         <v>387</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>388</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>21</v>
@@ -4488,24 +4464,24 @@
         <v>5</v>
       </c>
       <c r="F74" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="H74" s="4" t="s">
         <v>389</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>21</v>
@@ -4514,24 +4490,24 @@
         <v>5</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>394</v>
+        <v>199</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>51</v>
+        <v>392</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>21</v>
@@ -4540,24 +4516,24 @@
         <v>5</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>398</v>
+        <v>60</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>373</v>
+        <v>398</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>21</v>
@@ -4566,24 +4542,24 @@
         <v>5</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>373</v>
+        <v>398</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>21</v>
@@ -4592,24 +4568,24 @@
         <v>5</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>66</v>
+        <v>404</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>407</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>409</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>21</v>
@@ -4618,24 +4594,24 @@
         <v>5</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>222</v>
+        <v>75</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>21</v>
@@ -4644,24 +4620,24 @@
         <v>5</v>
       </c>
       <c r="F80" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="H80" s="4" t="s">
         <v>414</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="H80" s="4" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C81" s="4" t="s">
         <v>416</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>417</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>21</v>
@@ -4670,24 +4646,24 @@
         <v>5</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>418</v>
+        <v>91</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>21</v>
@@ -4696,24 +4672,24 @@
         <v>5</v>
       </c>
       <c r="F82" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="H82" s="4" t="s">
         <v>422</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="H82" s="4" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>21</v>
@@ -4722,24 +4698,24 @@
         <v>5</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>97</v>
+        <v>255</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>21</v>
@@ -4748,24 +4724,24 @@
         <v>5</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>430</v>
+        <v>106</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>395</v>
+        <v>429</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>21</v>
@@ -4774,24 +4750,24 @@
         <v>5</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>112</v>
+        <v>432</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C86" s="4" t="s">
         <v>435</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>436</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>21</v>
@@ -4800,24 +4776,24 @@
         <v>5</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>437</v>
+        <v>121</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="C87" s="4" t="s">
         <v>439</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>440</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>21</v>
@@ -4826,13 +4802,13 @@
         <v>5</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="G87" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="H87" s="4" t="s">
         <v>441</v>
-      </c>
-      <c r="H87" s="4" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -4840,7 +4816,7 @@
         <v>442</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>408</v>
+        <v>438</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>443</v>
@@ -4852,21 +4828,21 @@
         <v>5</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>127</v>
+        <v>444</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>447</v>
@@ -4878,7 +4854,7 @@
         <v>5</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>293</v>
+        <v>136</v>
       </c>
       <c r="G89" s="4" t="s">
         <v>448</v>
@@ -4892,10 +4868,10 @@
         <v>450</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>21</v>
@@ -4904,24 +4880,24 @@
         <v>5</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>141</v>
+        <v>454</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>21</v>
@@ -4930,24 +4906,24 @@
         <v>5</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>456</v>
+        <v>152</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>21</v>
@@ -4956,24 +4932,24 @@
         <v>5</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>21</v>
@@ -4982,24 +4958,24 @@
         <v>5</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>158</v>
+        <v>323</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>21</v>
@@ -5008,7 +4984,7 @@
         <v>5</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>468</v>
+        <v>169</v>
       </c>
       <c r="G94" s="4" t="s">
         <v>469</v>
@@ -5022,7 +4998,7 @@
         <v>471</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>472</v>
@@ -5034,24 +5010,24 @@
         <v>5</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>173</v>
+        <v>473</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>128</v>
+        <v>474</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>21</v>
@@ -5060,24 +5036,24 @@
         <v>5</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>475</v>
+        <v>184</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>21</v>
@@ -5086,24 +5062,24 @@
         <v>5</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>179</v>
+        <v>463</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>21</v>
@@ -5112,65 +5088,13 @@
         <v>5</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>188</v>
+        <v>483</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>458</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E99" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="G99" s="4" t="s">
-        <v>485</v>
-      </c>
-      <c r="H99" s="4" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>458</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E100" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="G100" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="H100" s="4" t="s">
-        <v>77</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -5194,13 +5118,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>32</v>
@@ -5209,18 +5133,18 @@
         <v>3</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>12</v>
@@ -5229,18 +5153,18 @@
         <v>13</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>17</v>
@@ -5249,7 +5173,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
@@ -5260,7 +5184,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -5272,1702 +5196,1668 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>43</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>48</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>53</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>58</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>63</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>83</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>89</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>99</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>104</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>109</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>114</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>119</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>124</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>129</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>134</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>537</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>506</v>
+        <v>531</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>532</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>507</v>
+        <v>533</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>504</v>
+        <v>534</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>507</v>
+        <v>536</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>504</v>
+        <v>534</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>540</v>
+        <v>537</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>500</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>205</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>219</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>548</v>
-      </c>
       <c r="D39" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>234</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>249</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>253</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>263</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>286</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>305</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>314</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>506</v>
+        <v>565</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>532</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>544</v>
+        <v>566</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>573</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>540</v>
+        <v>568</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>500</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>574</v>
+        <v>536</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>542</v>
+        <v>573</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>544</v>
+        <v>575</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>542</v>
+        <v>573</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>544</v>
+        <v>575</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>372</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="C75" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="B75" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>587</v>
-      </c>
       <c r="D75" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>442</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>450</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>471</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>611</v>
-      </c>
-      <c r="D99" s="5" t="s">
-        <v>506</v>
-      </c>
-      <c r="E99" s="4" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>612</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>506</v>
-      </c>
-      <c r="E100" s="4" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
   </sheetData>
@@ -6989,172 +6879,172 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
   </sheetData>
